--- a/annotators/preanno_parcor_coref/de/raw/bbc.242405.xlsx
+++ b/annotators/preanno_parcor_coref/de/raw/bbc.242405.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="368">
   <si>
     <t>ID</t>
   </si>
@@ -59,7 +59,7 @@
     <t>verfügbar</t>
   </si>
   <si>
-    <t>Royal Bank of Scotland für Kunden außerhalb Schottlands nicht mehr verfügbar Die Marke RBS soll laut dem Vorstandschef der Bank nurmehr auf eine Backoffice Rolle reduziert werden .</t>
+    <t>Royal Bank of Scotland für Kunden außerhalb Schottlands nicht mehr verfügbar</t>
   </si>
   <si>
     <t>file://conllu/de/bbc.242405.conllu#s1_0</t>
@@ -68,6 +68,21 @@
     <t>2</t>
   </si>
   <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>reduzieren</t>
+  </si>
+  <si>
+    <t>Die Marke RBS soll laut dem Vorstandschef der Bank nurmehr auf eine Backoffice Rolle reduziert werden .</t>
+  </si>
+  <si>
+    <t>file://conllu/de/bbc.242405.conllu#s2_0</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>14</t>
   </si>
   <si>
@@ -77,10 +92,10 @@
     <t>Die Royal Bank of Scotland wird für Kunden außerhalb Schottlands nicht mehr verfügbar sein .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242405.conllu#s2_0</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>file://conllu/de/bbc.242405.conllu#s3_0</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>teilen</t>
@@ -89,10 +104,10 @@
     <t>Ross McEwan teilte der BBC Scotland mit , dass die Marke RBS mit den globalen Ambitionen der Bank verbunden waren .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242405.conllu#s3_0</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>file://conllu/de/bbc.242405.conllu#s4_0</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
   <si>
     <t>6</t>
@@ -104,10 +119,7 @@
     <t>Die Bank hat sich seitdem distanziert , als sie vor acht Jahren fast kollabierte und gerettet werden musste .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242405.conllu#s4_0</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>file://conllu/de/bbc.242405.conllu#s5_0</t>
   </si>
   <si>
     <t>10</t>
@@ -122,7 +134,10 @@
     <t>In dieser Zeit haben Markenstrategen &amp;quot; RBS &amp;quot; dazu verwendet , andere Endverbraucherfinanzmarken zu schützen .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242405.conllu#s5_0</t>
+    <t>file://conllu/de/bbc.242405.conllu#s6_0</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
   <si>
     <t>unterstützen</t>
@@ -131,10 +146,10 @@
     <t>Sie unterstützte den internationalen Sport mit Millionen Pfund an Sponsoring , vom von dem Six Nations Rugby bis hin zum zu dem Wimbledon Sieger Andy Murray .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242405.conllu#s6_0</t>
-  </si>
-  <si>
-    <t>7</t>
+    <t>file://conllu/de/bbc.242405.conllu#s7_0</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
   <si>
     <t>entschieden</t>
@@ -143,10 +158,10 @@
     <t>Aber jetzt hat sie sich dazu entschieden , mehr nationale Marken in den Fokus zu rücken .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242405.conllu#s7_0</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>file://conllu/de/bbc.242405.conllu#s8_0</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
   <si>
     <t>13</t>
@@ -155,10 +170,7 @@
     <t>Die Royal Bank of Scotland wird nur für Kunden in Schottland verfügbar sein , aber wird nicht initialisiert werden .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242405.conllu#s8_0</t>
-  </si>
-  <si>
-    <t>9</t>
+    <t>file://conllu/de/bbc.242405.conllu#s9_0</t>
   </si>
   <si>
     <t>18</t>
@@ -170,7 +182,7 @@
     <t>In England und Wales werden alle RSB Referenzen , der dezentrale Hauptsitz und die Börsennotierung zu NatWest wechseln .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242405.conllu#s9_0</t>
+    <t>file://conllu/de/bbc.242405.conllu#s10_0</t>
   </si>
   <si>
     <t>15</t>
@@ -179,7 +191,10 @@
     <t>Die Marke Ulster Bank wird bereits für Kunden in der Republik Irland und Nordirland verwendet .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242405.conllu#s10_0</t>
+    <t>file://conllu/de/bbc.242405.conllu#s11_0</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
   <si>
     <t>geben</t>
@@ -188,10 +203,7 @@
     <t>Es gibt andere , kleinere Marken für das Privatkundengeschäft , die mehr Bedeutung erhalten werden Coutts , Adam &amp;amp; Co , Drummond und Holt's Military Bank .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242405.conllu#s11_0</t>
-  </si>
-  <si>
-    <t>12</t>
+    <t>file://conllu/de/bbc.242405.conllu#s12_0</t>
   </si>
   <si>
     <t>interviewen</t>
@@ -200,13 +212,13 @@
     <t>McEwan wurde während einer Besichtigungstour von Kunden und Mitarbeitern in Inverness-shire interviewt .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242405.conllu#s12_0</t>
+    <t>file://conllu/de/bbc.242405.conllu#s13_0</t>
   </si>
   <si>
     <t>Er teilte der BBC Scotland mit : &amp;quot; Die Marke RSB wird zu unserer Investorenmarke sowie zu der Marke , unter der unsere Mitarbeiter beschäftigt sein werden , da wir jetzt mehr zu einer Bank von Marken werden . &amp;quot;</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242405.conllu#s13_0</t>
+    <t>file://conllu/de/bbc.242405.conllu#s14_0</t>
   </si>
   <si>
     <t>werden</t>
@@ -215,7 +227,7 @@
     <t>Als die Bank selber zu einer globalen Marke wurde , wurde RBS zur zu der globalen Marke .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242405.conllu#s14_0</t>
+    <t>file://conllu/de/bbc.242405.conllu#s15_0</t>
   </si>
   <si>
     <t>sagen</t>
@@ -224,10 +236,10 @@
     <t>Ich sage jetzt , dass wir keine globalen Ziele , sondern lokale Ziele verfolgen .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242405.conllu#s15_0</t>
-  </si>
-  <si>
-    <t>16</t>
+    <t>file://conllu/de/bbc.242405.conllu#s16_0</t>
+  </si>
+  <si>
+    <t>17</t>
   </si>
   <si>
     <t>stehen</t>
@@ -236,10 +248,7 @@
     <t>Jede dieser Marken wird in ihren eigenen Gemeinden für etwas vollkommen anderes stehen und unsere Mitarbeiter werden unter diesen Marken mit den Kunden arbeiten .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242405.conllu#s16_0</t>
-  </si>
-  <si>
-    <t>17</t>
+    <t>file://conllu/de/bbc.242405.conllu#s17_0</t>
   </si>
   <si>
     <t>ausgesagen</t>
@@ -248,7 +257,10 @@
     <t>RBS hat bereits ausgesagt , dass es sein Six Nations Sponsoring nicht mehr fortführen wird und , dass es die Wahrnehmbarkeit der verschiedenen Marken in seinem Sport Sponsoring erhöhen wird .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242405.conllu#s17_0</t>
+    <t>file://conllu/de/bbc.242405.conllu#s18_0</t>
+  </si>
+  <si>
+    <t>19</t>
   </si>
   <si>
     <t>43</t>
@@ -257,10 +269,10 @@
     <t>&amp;quot; Es ist Zeit für uns , sich zur zu der Bank der Marken zu entwickeln , denn wie konzentrieren wir uns im in dem Inneren ( wir haben gefragt ) darauf , dies zu einer besseren Bank für Kunden zu machen ? &amp;quot; sagte der Vorstandschef .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242405.conllu#s18_0</t>
-  </si>
-  <si>
-    <t>19</t>
+    <t>file://conllu/de/bbc.242405.conllu#s19_0</t>
+  </si>
+  <si>
+    <t>20</t>
   </si>
   <si>
     <t>sein (sein zynisch)</t>
@@ -269,10 +281,10 @@
     <t>Es wäre vor drei Jahren sehr zynisch gewesen , wenn wir gesagt hätten , dass wir für unsere Kunden eine tolle Bank sein werden und diese Marken lanciert hätten .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242405.conllu#s19_0</t>
-  </si>
-  <si>
-    <t>20</t>
+    <t>file://conllu/de/bbc.242405.conllu#s20_0</t>
+  </si>
+  <si>
+    <t>21</t>
   </si>
   <si>
     <t>denken (denken sehen)</t>
@@ -281,10 +293,10 @@
     <t>Aber mit unserer Arbeit , dem Fokus auf Kundenbedürfnisse und nicht unsere eigenen , denke ich , wird man viele Veränderungen sehen .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242405.conllu#s20_0</t>
-  </si>
-  <si>
-    <t>21</t>
+    <t>file://conllu/de/bbc.242405.conllu#s21_0</t>
+  </si>
+  <si>
+    <t>22</t>
   </si>
   <si>
     <t>lancieren</t>
@@ -293,7 +305,7 @@
     <t>Wir können diese Marken wieder lancieren , daher denke ich , dass die Zeit gekommen ist .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242405.conllu#s21_0</t>
+    <t>file://conllu/de/bbc.242405.conllu#s22_0</t>
   </si>
   <si>
     <t>WORD</t>
@@ -329,7 +341,7 @@
     <t>REF_DIST_ANTE</t>
   </si>
   <si>
-    <t># text = Royal Bank of Scotland für Kunden außerhalb Schottlands nicht mehr verfügbar Die Marke RBS soll laut dem Vorstandschef der Bank nurmehr auf eine Backoffice-Rolle reduziert werden.</t>
+    <t># text = Royal Bank of Scotland für Kunden außerhalb Schottlands nicht mehr verfügbar</t>
   </si>
   <si>
     <t>Royal</t>
@@ -380,85 +392,88 @@
     <t>mehr</t>
   </si>
   <si>
+    <t># text = Die Marke RBS soll laut dem Vorstandschef der Bank nurmehr auf eine Backoffice-Rolle reduziert werden.</t>
+  </si>
+  <si>
     <t>Die</t>
   </si>
   <si>
     <t>Marke</t>
   </si>
   <si>
+    <t>def-np.the</t>
+  </si>
+  <si>
+    <t>RBS</t>
+  </si>
+  <si>
+    <t>soll</t>
+  </si>
+  <si>
+    <t>laut</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>Vorstandschef</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>der</t>
+  </si>
+  <si>
+    <t>nurmehr</t>
+  </si>
+  <si>
+    <t>auf</t>
+  </si>
+  <si>
+    <t>eine</t>
+  </si>
+  <si>
+    <t>Backoffice</t>
+  </si>
+  <si>
+    <t>Rolle</t>
+  </si>
+  <si>
+    <t>indef-np.a</t>
+  </si>
+  <si>
+    <t>reduziert</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t># text = Die Royal Bank of Scotland wird für Kunden außerhalb Schottlands nicht mehr verfügbar sein.</t>
+  </si>
+  <si>
+    <t>wird</t>
+  </si>
+  <si>
+    <t>sein</t>
+  </si>
+  <si>
+    <t># text = Ross McEwan teilte der BBC Scotland mit, dass die Marke RBS mit den globalen Ambitionen der Bank verbunden waren.</t>
+  </si>
+  <si>
+    <t>Ross</t>
+  </si>
+  <si>
+    <t>McEwan</t>
+  </si>
+  <si>
+    <t>teilte</t>
+  </si>
+  <si>
+    <t>BBC</t>
+  </si>
+  <si>
     <t>SBJ_2</t>
-  </si>
-  <si>
-    <t>def-np.the</t>
-  </si>
-  <si>
-    <t>RBS</t>
-  </si>
-  <si>
-    <t>soll</t>
-  </si>
-  <si>
-    <t>laut</t>
-  </si>
-  <si>
-    <t>dem</t>
-  </si>
-  <si>
-    <t>Vorstandschef</t>
-  </si>
-  <si>
-    <t>der</t>
-  </si>
-  <si>
-    <t>nurmehr</t>
-  </si>
-  <si>
-    <t>auf</t>
-  </si>
-  <si>
-    <t>eine</t>
-  </si>
-  <si>
-    <t>Backoffice</t>
-  </si>
-  <si>
-    <t>Rolle</t>
-  </si>
-  <si>
-    <t>indef-np.a</t>
-  </si>
-  <si>
-    <t>reduziert</t>
-  </si>
-  <si>
-    <t>.</t>
-  </si>
-  <si>
-    <t># text = Die Royal Bank of Scotland wird für Kunden außerhalb Schottlands nicht mehr verfügbar sein.</t>
-  </si>
-  <si>
-    <t>wird</t>
-  </si>
-  <si>
-    <t>other</t>
-  </si>
-  <si>
-    <t>sein</t>
-  </si>
-  <si>
-    <t># text = Ross McEwan teilte der BBC Scotland mit, dass die Marke RBS mit den globalen Ambitionen der Bank verbunden waren.</t>
-  </si>
-  <si>
-    <t>Ross</t>
-  </si>
-  <si>
-    <t>McEwan</t>
-  </si>
-  <si>
-    <t>teilte</t>
-  </si>
-  <si>
-    <t>BBC</t>
   </si>
   <si>
     <t>OBJ</t>
@@ -1579,7 +1594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="60" customHeight="1"/>
   <cols>
     <col min="2" max="3" width="0" hidden="1" customWidth="1"/>
@@ -1690,19 +1705,19 @@
         <v>21</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" s="9">
         <f>IF(A4=1,"_",IF(C4="_","???",C4))</f>
@@ -1718,10 +1733,10 @@
     </row>
     <row r="5" spans="1:10" ht="60" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>12</v>
@@ -1755,16 +1770,16 @@
         <v>31</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="F6" s="6" t="s">
         <v>34</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>35</v>
       </c>
       <c r="G6" s="9">
         <f>IF(A6=1,"_",IF(C6="_","???",C6))</f>
@@ -1780,22 +1795,22 @@
     </row>
     <row r="7" spans="1:10" ht="60" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G7" s="9">
         <f>IF(A7=1,"_",IF(C7="_","???",C7))</f>
@@ -1811,22 +1826,22 @@
     </row>
     <row r="8" spans="1:10" ht="60" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G8" s="9">
         <f>IF(A8=1,"_",IF(C8="_","???",C8))</f>
@@ -1842,22 +1857,22 @@
     </row>
     <row r="9" spans="1:10" ht="60" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G9" s="9">
         <f>IF(A9=1,"_",IF(C9="_","???",C9))</f>
@@ -1873,16 +1888,16 @@
     </row>
     <row r="10" spans="1:10" ht="60" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>50</v>
@@ -1904,7 +1919,7 @@
     </row>
     <row r="11" spans="1:10" ht="60" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>52</v>
@@ -1913,13 +1928,13 @@
         <v>12</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G11" s="9">
         <f>IF(A11=1,"_",IF(C11="_","???",C11))</f>
@@ -1938,19 +1953,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G12" s="9">
         <f>IF(A12=1,"_",IF(C12="_","???",C12))</f>
@@ -1966,22 +1981,22 @@
     </row>
     <row r="13" spans="1:10" ht="60" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G13" s="9">
         <f>IF(A13=1,"_",IF(C13="_","???",C13))</f>
@@ -1997,22 +2012,22 @@
     </row>
     <row r="14" spans="1:10" ht="60" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G14" s="9">
         <f>IF(A14=1,"_",IF(C14="_","???",C14))</f>
@@ -2028,22 +2043,22 @@
     </row>
     <row r="15" spans="1:10" ht="60" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G15" s="9">
         <f>IF(A15=1,"_",IF(C15="_","???",C15))</f>
@@ -2059,22 +2074,22 @@
     </row>
     <row r="16" spans="1:10" ht="60" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G16" s="9">
         <f>IF(A16=1,"_",IF(C16="_","???",C16))</f>
@@ -2090,10 +2105,10 @@
     </row>
     <row r="17" spans="1:10" ht="60" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>12</v>
@@ -2124,7 +2139,7 @@
         <v>74</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>12</v>
@@ -2152,16 +2167,16 @@
     </row>
     <row r="19" spans="1:10" ht="60" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>79</v>
@@ -2186,13 +2201,13 @@
         <v>81</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>83</v>
@@ -2217,7 +2232,7 @@
         <v>85</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>12</v>
@@ -2248,7 +2263,7 @@
         <v>89</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>12</v>
@@ -2273,6 +2288,37 @@
         <v>12</v>
       </c>
       <c r="J22" s="12"/>
+    </row>
+    <row r="23" spans="1:10" ht="60" customHeight="1">
+      <c r="A23" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="G23" s="9">
+        <f>IF(A23=1,"_",IF(C23="_","???",C23))</f>
+        <v/>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J23" s="12"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
@@ -2282,7 +2328,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L529"/>
+  <dimension ref="A1:L531"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2294,37 +2340,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="13" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="J1" s="18" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K1" s="18" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="L1" s="19" t="s">
         <v>9</v>
@@ -2332,21 +2378,21 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="20" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="20" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E3" s="22">
         <f>IF(D3="?OLD","!!!","")</f>
@@ -2380,7 +2426,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="20" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E4" s="22">
         <f>IF(D4="?OLD","!!!","")</f>
@@ -2414,7 +2460,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="20" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E5" s="22">
         <f>IF(D5="?OLD","!!!","")</f>
@@ -2448,7 +2494,7 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="20" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E6" s="22">
         <f>IF(D6="?OLD","!!!","")</f>
@@ -2482,7 +2528,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="20" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E7" s="22">
         <f>IF(D7="?OLD","!!!","")</f>
@@ -2516,16 +2562,16 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="20" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E8" s="22">
         <f>IF(D8="?OLD","!!!","")</f>
@@ -2559,7 +2605,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="20" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E9" s="22">
         <f>IF(D9="?OLD","!!!","")</f>
@@ -2593,16 +2639,16 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="20" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E10" s="22">
         <f>IF(D10="?OLD","!!!","")</f>
@@ -2636,7 +2682,7 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="20" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E11" s="22">
         <f>IF(D11="?OLD","!!!","")</f>
@@ -2670,7 +2716,7 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="20" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E12" s="22">
         <f>IF(D12="?OLD","!!!","")</f>
@@ -2737,94 +2783,16 @@
       <c r="L13" s="27"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="E14" s="22">
-        <f>IF(D14="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F14" s="23" t="str">
-        <f>IF(OR(E14="",E14="!!!"),"",IF(NOT(ISNA(VLOOKUP(E14,E$1:E13,1,FALSE()))),"OLD",IF(AND(E14&lt;&gt;"",E14&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G14" s="24" t="str">
-        <f>IF(OR(E14="",E14="!!!"),"",IF(OR(J14=0,AND(J14=1,K14=1),AND(J14=1,I14="SBJ"),AND(J14=1,I14=0)),"?IN_FOCUS",IF(J14&lt;=2,"?ACTIVATED",IF(J14&lt;&gt;"","?FAMILIAR",IF(F14="NEW",IF(ISNA(VLOOKUP(E14,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H14" s="25" t="str">
-        <f>IF(J14&lt;&gt;1,"",IF(I14="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I14" s="26" t="str">
-        <f>IF(OR(E14="",E14="!!!",F14="NEW"),"",INDEX(B13:B$2,-1+SUMPRODUCT(MAX(ROW(E13:E$2)*(E14=E13:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J14" s="26" t="str">
-        <f>IF(OR(E14="",E14="!!!",F14="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E14)*(E14=E$2:E14)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E13)*(E2=E$1:E13))))))</f>
-        <v> </v>
-      </c>
-      <c r="K14" s="26" t="str">
-        <f>IF(OR(E14="",E14="!!!",F14="NEW"),"",INDEX(J$1:J13,SUMPRODUCT(MAX(ROW(E$1:E13)*(E14=E$1:E13)))))</f>
-        <v> </v>
-      </c>
-      <c r="L14" s="27"/>
+      <c r="A14" s="20"/>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="E15" s="22">
-        <f>IF(D15="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F15" s="23" t="str">
-        <f>IF(OR(E15="",E15="!!!"),"",IF(NOT(ISNA(VLOOKUP(E15,E$1:E14,1,FALSE()))),"OLD",IF(AND(E15&lt;&gt;"",E15&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G15" s="24" t="str">
-        <f>IF(OR(E15="",E15="!!!"),"",IF(OR(J15=0,AND(J15=1,K15=1),AND(J15=1,I15="SBJ"),AND(J15=1,I15=0)),"?IN_FOCUS",IF(J15&lt;=2,"?ACTIVATED",IF(J15&lt;&gt;"","?FAMILIAR",IF(F15="NEW",IF(ISNA(VLOOKUP(E15,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H15" s="25" t="str">
-        <f>IF(J15&lt;&gt;1,"",IF(I15="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I15" s="26" t="str">
-        <f>IF(OR(E15="",E15="!!!",F15="NEW"),"",INDEX(B14:B$2,-1+SUMPRODUCT(MAX(ROW(E14:E$2)*(E15=E14:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J15" s="26" t="str">
-        <f>IF(OR(E15="",E15="!!!",F15="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E15)*(E15=E$2:E15)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E14)*(E2=E$1:E14))))))</f>
-        <v> </v>
-      </c>
-      <c r="K15" s="26" t="str">
-        <f>IF(OR(E15="",E15="!!!",F15="NEW"),"",INDEX(J$1:J14,SUMPRODUCT(MAX(ROW(E$1:E14)*(E15=E$1:E14)))))</f>
-        <v> </v>
-      </c>
-      <c r="L15" s="27"/>
+        <v>125</v>
+      </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="B16" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="E16" s="22">
         <f>IF(D16="?OLD","!!!","")</f>
@@ -2858,7 +2826,16 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E17" s="22">
         <f>IF(D17="?OLD","!!!","")</f>
@@ -2892,7 +2869,16 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="20" t="s">
-        <v>127</v>
+        <v>129</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E18" s="22">
         <f>IF(D18="?OLD","!!!","")</f>
@@ -2926,7 +2912,7 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="20" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E19" s="22">
         <f>IF(D19="?OLD","!!!","")</f>
@@ -2960,16 +2946,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="B20" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="E20" s="22">
         <f>IF(D20="?OLD","!!!","")</f>
@@ -3003,7 +2980,7 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="20" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E21" s="22">
         <f>IF(D21="?OLD","!!!","")</f>
@@ -3037,16 +3014,16 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="20" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E22" s="22">
         <f>IF(D22="?OLD","!!!","")</f>
@@ -3080,7 +3057,7 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="20" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E23" s="22">
         <f>IF(D23="?OLD","!!!","")</f>
@@ -3114,7 +3091,16 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="20" t="s">
-        <v>132</v>
+        <v>113</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E24" s="22">
         <f>IF(D24="?OLD","!!!","")</f>
@@ -3148,7 +3134,7 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="20" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E25" s="22">
         <f>IF(D25="?OLD","!!!","")</f>
@@ -3182,7 +3168,7 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="20" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E26" s="22">
         <f>IF(D26="?OLD","!!!","")</f>
@@ -3216,7 +3202,7 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="20" t="s">
-        <v>12</v>
+        <v>138</v>
       </c>
       <c r="E27" s="22">
         <f>IF(D27="?OLD","!!!","")</f>
@@ -3250,13 +3236,7 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="B28" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E28" s="22">
         <f>IF(D28="?OLD","!!!","")</f>
@@ -3290,7 +3270,7 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="20" t="s">
-        <v>137</v>
+        <v>12</v>
       </c>
       <c r="E29" s="22">
         <f>IF(D29="?OLD","!!!","")</f>
@@ -3324,7 +3304,13 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="20" t="s">
-        <v>64</v>
+        <v>140</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>141</v>
       </c>
       <c r="E30" s="22">
         <f>IF(D30="?OLD","!!!","")</f>
@@ -3358,7 +3344,7 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="20" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E31" s="22">
         <f>IF(D31="?OLD","!!!","")</f>
@@ -3391,93 +3377,84 @@
       <c r="L31" s="27"/>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="20"/>
+      <c r="A32" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E32" s="22">
+        <f>IF(D32="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F32" s="23" t="str">
+        <f>IF(OR(E32="",E32="!!!"),"",IF(NOT(ISNA(VLOOKUP(E32,E$1:E31,1,FALSE()))),"OLD",IF(AND(E32&lt;&gt;"",E32&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G32" s="24" t="str">
+        <f>IF(OR(E32="",E32="!!!"),"",IF(OR(J32=0,AND(J32=1,K32=1),AND(J32=1,I32="SBJ"),AND(J32=1,I32=0)),"?IN_FOCUS",IF(J32&lt;=2,"?ACTIVATED",IF(J32&lt;&gt;"","?FAMILIAR",IF(F32="NEW",IF(ISNA(VLOOKUP(E32,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H32" s="25" t="str">
+        <f>IF(J32&lt;&gt;1,"",IF(I32="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I32" s="26" t="str">
+        <f>IF(OR(E32="",E32="!!!",F32="NEW"),"",INDEX(B31:B$2,-1+SUMPRODUCT(MAX(ROW(E31:E$2)*(E32=E31:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J32" s="26" t="str">
+        <f>IF(OR(E32="",E32="!!!",F32="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E32)*(E32=E$2:E32)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E31)*(E2=E$1:E31))))))</f>
+        <v> </v>
+      </c>
+      <c r="K32" s="26" t="str">
+        <f>IF(OR(E32="",E32="!!!",F32="NEW"),"",INDEX(J$1:J31,SUMPRODUCT(MAX(ROW(E$1:E31)*(E32=E$1:E31)))))</f>
+        <v> </v>
+      </c>
+      <c r="L32" s="27"/>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="20" t="s">
-        <v>139</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="E33" s="22">
+        <f>IF(D33="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F33" s="23" t="str">
+        <f>IF(OR(E33="",E33="!!!"),"",IF(NOT(ISNA(VLOOKUP(E33,E$1:E32,1,FALSE()))),"OLD",IF(AND(E33&lt;&gt;"",E33&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G33" s="24" t="str">
+        <f>IF(OR(E33="",E33="!!!"),"",IF(OR(J33=0,AND(J33=1,K33=1),AND(J33=1,I33="SBJ"),AND(J33=1,I33=0)),"?IN_FOCUS",IF(J33&lt;=2,"?ACTIVATED",IF(J33&lt;&gt;"","?FAMILIAR",IF(F33="NEW",IF(ISNA(VLOOKUP(E33,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H33" s="25" t="str">
+        <f>IF(J33&lt;&gt;1,"",IF(I33="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I33" s="26" t="str">
+        <f>IF(OR(E33="",E33="!!!",F33="NEW"),"",INDEX(B32:B$2,-1+SUMPRODUCT(MAX(ROW(E32:E$2)*(E33=E32:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J33" s="26" t="str">
+        <f>IF(OR(E33="",E33="!!!",F33="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E33)*(E33=E$2:E33)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E32)*(E2=E$1:E32))))))</f>
+        <v> </v>
+      </c>
+      <c r="K33" s="26" t="str">
+        <f>IF(OR(E33="",E33="!!!",F33="NEW"),"",INDEX(J$1:J32,SUMPRODUCT(MAX(ROW(E$1:E32)*(E33=E$1:E32)))))</f>
+        <v> </v>
+      </c>
+      <c r="L33" s="27"/>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="E34" s="22">
-        <f>IF(D34="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F34" s="23" t="str">
-        <f>IF(OR(E34="",E34="!!!"),"",IF(NOT(ISNA(VLOOKUP(E34,E$1:E33,1,FALSE()))),"OLD",IF(AND(E34&lt;&gt;"",E34&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G34" s="24" t="str">
-        <f>IF(OR(E34="",E34="!!!"),"",IF(OR(J34=0,AND(J34=1,K34=1),AND(J34=1,I34="SBJ"),AND(J34=1,I34=0)),"?IN_FOCUS",IF(J34&lt;=2,"?ACTIVATED",IF(J34&lt;&gt;"","?FAMILIAR",IF(F34="NEW",IF(ISNA(VLOOKUP(E34,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H34" s="25" t="str">
-        <f>IF(J34&lt;&gt;1,"",IF(I34="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I34" s="26" t="str">
-        <f>IF(OR(E34="",E34="!!!",F34="NEW"),"",INDEX(B33:B$2,-1+SUMPRODUCT(MAX(ROW(E33:E$2)*(E34=E33:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J34" s="26" t="str">
-        <f>IF(OR(E34="",E34="!!!",F34="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E34)*(E34=E$2:E34)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E33)*(E2=E$1:E33))))))</f>
-        <v> </v>
-      </c>
-      <c r="K34" s="26" t="str">
-        <f>IF(OR(E34="",E34="!!!",F34="NEW"),"",INDEX(J$1:J33,SUMPRODUCT(MAX(ROW(E$1:E33)*(E34=E$1:E33)))))</f>
-        <v> </v>
-      </c>
-      <c r="L34" s="27"/>
+      <c r="A34" s="20"/>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="B35" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="C35" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D35" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="E35" s="22">
-        <f>IF(D35="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F35" s="23" t="str">
-        <f>IF(OR(E35="",E35="!!!"),"",IF(NOT(ISNA(VLOOKUP(E35,E$1:E34,1,FALSE()))),"OLD",IF(AND(E35&lt;&gt;"",E35&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G35" s="24" t="str">
-        <f>IF(OR(E35="",E35="!!!"),"",IF(OR(J35=0,AND(J35=1,K35=1),AND(J35=1,I35="SBJ"),AND(J35=1,I35=0)),"?IN_FOCUS",IF(J35&lt;=2,"?ACTIVATED",IF(J35&lt;&gt;"","?FAMILIAR",IF(F35="NEW",IF(ISNA(VLOOKUP(E35,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H35" s="25" t="str">
-        <f>IF(J35&lt;&gt;1,"",IF(I35="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I35" s="26" t="str">
-        <f>IF(OR(E35="",E35="!!!",F35="NEW"),"",INDEX(B34:B$2,-1+SUMPRODUCT(MAX(ROW(E34:E$2)*(E35=E34:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J35" s="26" t="str">
-        <f>IF(OR(E35="",E35="!!!",F35="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E35)*(E35=E$2:E35)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E34)*(E2=E$1:E34))))))</f>
-        <v> </v>
-      </c>
-      <c r="K35" s="26" t="str">
-        <f>IF(OR(E35="",E35="!!!",F35="NEW"),"",INDEX(J$1:J34,SUMPRODUCT(MAX(ROW(E$1:E34)*(E35=E$1:E34)))))</f>
-        <v> </v>
-      </c>
-      <c r="L35" s="27"/>
+        <v>144</v>
+      </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="20" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="E36" s="22">
         <f>IF(D36="?OLD","!!!","")</f>
@@ -3511,7 +3488,16 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B37" s="21" t="s">
         <v>110</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E37" s="22">
         <f>IF(D37="?OLD","!!!","")</f>
@@ -3545,7 +3531,7 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="20" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E38" s="22">
         <f>IF(D38="?OLD","!!!","")</f>
@@ -3579,7 +3565,7 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" s="20" t="s">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="E39" s="22">
         <f>IF(D39="?OLD","!!!","")</f>
@@ -3613,7 +3599,7 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" s="20" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E40" s="22">
         <f>IF(D40="?OLD","!!!","")</f>
@@ -3647,16 +3633,7 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="B41" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="C41" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="D41" s="21" t="s">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="E41" s="22">
         <f>IF(D41="?OLD","!!!","")</f>
@@ -3727,13 +3704,13 @@
         <v>117</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E43" s="22">
         <f>IF(D43="?OLD","!!!","")</f>
@@ -3767,7 +3744,7 @@
     </row>
     <row r="44" spans="1:12">
       <c r="A44" s="20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E44" s="22">
         <f>IF(D44="?OLD","!!!","")</f>
@@ -3801,7 +3778,16 @@
     </row>
     <row r="45" spans="1:12">
       <c r="A45" s="20" t="s">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D45" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E45" s="22">
         <f>IF(D45="?OLD","!!!","")</f>
@@ -3835,7 +3821,7 @@
     </row>
     <row r="46" spans="1:12">
       <c r="A46" s="20" t="s">
-        <v>13</v>
+        <v>123</v>
       </c>
       <c r="E46" s="22">
         <f>IF(D46="?OLD","!!!","")</f>
@@ -3869,7 +3855,7 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47" s="20" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="E47" s="22">
         <f>IF(D47="?OLD","!!!","")</f>
@@ -3903,7 +3889,7 @@
     </row>
     <row r="48" spans="1:12">
       <c r="A48" s="20" t="s">
-        <v>138</v>
+        <v>13</v>
       </c>
       <c r="E48" s="22">
         <f>IF(D48="?OLD","!!!","")</f>
@@ -3936,93 +3922,93 @@
       <c r="L48" s="27"/>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="20"/>
+      <c r="A49" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="E49" s="22">
+        <f>IF(D49="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F49" s="23" t="str">
+        <f>IF(OR(E49="",E49="!!!"),"",IF(NOT(ISNA(VLOOKUP(E49,E$1:E48,1,FALSE()))),"OLD",IF(AND(E49&lt;&gt;"",E49&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G49" s="24" t="str">
+        <f>IF(OR(E49="",E49="!!!"),"",IF(OR(J49=0,AND(J49=1,K49=1),AND(J49=1,I49="SBJ"),AND(J49=1,I49=0)),"?IN_FOCUS",IF(J49&lt;=2,"?ACTIVATED",IF(J49&lt;&gt;"","?FAMILIAR",IF(F49="NEW",IF(ISNA(VLOOKUP(E49,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H49" s="25" t="str">
+        <f>IF(J49&lt;&gt;1,"",IF(I49="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I49" s="26" t="str">
+        <f>IF(OR(E49="",E49="!!!",F49="NEW"),"",INDEX(B48:B$2,-1+SUMPRODUCT(MAX(ROW(E48:E$2)*(E49=E48:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J49" s="26" t="str">
+        <f>IF(OR(E49="",E49="!!!",F49="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E49)*(E49=E$2:E49)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E48)*(E2=E$1:E48))))))</f>
+        <v> </v>
+      </c>
+      <c r="K49" s="26" t="str">
+        <f>IF(OR(E49="",E49="!!!",F49="NEW"),"",INDEX(J$1:J48,SUMPRODUCT(MAX(ROW(E$1:E48)*(E49=E$1:E48)))))</f>
+        <v> </v>
+      </c>
+      <c r="L49" s="27"/>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" s="20" t="s">
         <v>143</v>
       </c>
+      <c r="E50" s="22">
+        <f>IF(D50="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F50" s="23" t="str">
+        <f>IF(OR(E50="",E50="!!!"),"",IF(NOT(ISNA(VLOOKUP(E50,E$1:E49,1,FALSE()))),"OLD",IF(AND(E50&lt;&gt;"",E50&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G50" s="24" t="str">
+        <f>IF(OR(E50="",E50="!!!"),"",IF(OR(J50=0,AND(J50=1,K50=1),AND(J50=1,I50="SBJ"),AND(J50=1,I50=0)),"?IN_FOCUS",IF(J50&lt;=2,"?ACTIVATED",IF(J50&lt;&gt;"","?FAMILIAR",IF(F50="NEW",IF(ISNA(VLOOKUP(E50,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H50" s="25" t="str">
+        <f>IF(J50&lt;&gt;1,"",IF(I50="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I50" s="26" t="str">
+        <f>IF(OR(E50="",E50="!!!",F50="NEW"),"",INDEX(B49:B$2,-1+SUMPRODUCT(MAX(ROW(E49:E$2)*(E50=E49:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J50" s="26" t="str">
+        <f>IF(OR(E50="",E50="!!!",F50="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E50)*(E50=E$2:E50)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E49)*(E2=E$1:E49))))))</f>
+        <v> </v>
+      </c>
+      <c r="K50" s="26" t="str">
+        <f>IF(OR(E50="",E50="!!!",F50="NEW"),"",INDEX(J$1:J49,SUMPRODUCT(MAX(ROW(E$1:E49)*(E50=E$1:E49)))))</f>
+        <v> </v>
+      </c>
+      <c r="L50" s="27"/>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="B51" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="C51" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="E51" s="22">
-        <f>IF(D51="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F51" s="23" t="str">
-        <f>IF(OR(E51="",E51="!!!"),"",IF(NOT(ISNA(VLOOKUP(E51,E$1:E50,1,FALSE()))),"OLD",IF(AND(E51&lt;&gt;"",E51&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G51" s="24" t="str">
-        <f>IF(OR(E51="",E51="!!!"),"",IF(OR(J51=0,AND(J51=1,K51=1),AND(J51=1,I51="SBJ"),AND(J51=1,I51=0)),"?IN_FOCUS",IF(J51&lt;=2,"?ACTIVATED",IF(J51&lt;&gt;"","?FAMILIAR",IF(F51="NEW",IF(ISNA(VLOOKUP(E51,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H51" s="25" t="str">
-        <f>IF(J51&lt;&gt;1,"",IF(I51="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I51" s="26" t="str">
-        <f>IF(OR(E51="",E51="!!!",F51="NEW"),"",INDEX(B50:B$2,-1+SUMPRODUCT(MAX(ROW(E50:E$2)*(E51=E50:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J51" s="26" t="str">
-        <f>IF(OR(E51="",E51="!!!",F51="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E51)*(E51=E$2:E51)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E50)*(E2=E$1:E50))))))</f>
-        <v> </v>
-      </c>
-      <c r="K51" s="26" t="str">
-        <f>IF(OR(E51="",E51="!!!",F51="NEW"),"",INDEX(J$1:J50,SUMPRODUCT(MAX(ROW(E$1:E50)*(E51=E$1:E50)))))</f>
-        <v> </v>
-      </c>
-      <c r="L51" s="27"/>
+      <c r="A51" s="20"/>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="E52" s="22">
-        <f>IF(D52="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F52" s="23" t="str">
-        <f>IF(OR(E52="",E52="!!!"),"",IF(NOT(ISNA(VLOOKUP(E52,E$1:E51,1,FALSE()))),"OLD",IF(AND(E52&lt;&gt;"",E52&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G52" s="24" t="str">
-        <f>IF(OR(E52="",E52="!!!"),"",IF(OR(J52=0,AND(J52=1,K52=1),AND(J52=1,I52="SBJ"),AND(J52=1,I52=0)),"?IN_FOCUS",IF(J52&lt;=2,"?ACTIVATED",IF(J52&lt;&gt;"","?FAMILIAR",IF(F52="NEW",IF(ISNA(VLOOKUP(E52,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H52" s="25" t="str">
-        <f>IF(J52&lt;&gt;1,"",IF(I52="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I52" s="26" t="str">
-        <f>IF(OR(E52="",E52="!!!",F52="NEW"),"",INDEX(B51:B$2,-1+SUMPRODUCT(MAX(ROW(E51:E$2)*(E52=E51:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J52" s="26" t="str">
-        <f>IF(OR(E52="",E52="!!!",F52="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E52)*(E52=E$2:E52)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E51)*(E2=E$1:E51))))))</f>
-        <v> </v>
-      </c>
-      <c r="K52" s="26" t="str">
-        <f>IF(OR(E52="",E52="!!!",F52="NEW"),"",INDEX(J$1:J51,SUMPRODUCT(MAX(ROW(E$1:E51)*(E52=E$1:E51)))))</f>
-        <v> </v>
-      </c>
-      <c r="L52" s="27"/>
+        <v>147</v>
+      </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" s="20" t="s">
-        <v>146</v>
+        <v>148</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C53" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D53" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E53" s="22">
         <f>IF(D53="?OLD","!!!","")</f>
@@ -4056,7 +4042,7 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="20" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="E54" s="22">
         <f>IF(D54="?OLD","!!!","")</f>
@@ -4090,16 +4076,7 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="B55" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="C55" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D55" s="21" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="E55" s="22">
         <f>IF(D55="?OLD","!!!","")</f>
@@ -4133,16 +4110,7 @@
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="B56" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="C56" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D56" s="21" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="E56" s="22">
         <f>IF(D56="?OLD","!!!","")</f>
@@ -4176,7 +4144,16 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="20" t="s">
-        <v>149</v>
+        <v>151</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="C57" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D57" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E57" s="22">
         <f>IF(D57="?OLD","!!!","")</f>
@@ -4210,7 +4187,16 @@
     </row>
     <row r="58" spans="1:12">
       <c r="A58" s="20" t="s">
-        <v>150</v>
+        <v>115</v>
+      </c>
+      <c r="B58" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="C58" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D58" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E58" s="22">
         <f>IF(D58="?OLD","!!!","")</f>
@@ -4244,7 +4230,7 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="20" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E59" s="22">
         <f>IF(D59="?OLD","!!!","")</f>
@@ -4278,7 +4264,7 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" s="20" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E60" s="22">
         <f>IF(D60="?OLD","!!!","")</f>
@@ -4312,16 +4298,7 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="B61" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="C61" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D61" s="21" t="s">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="E61" s="22">
         <f>IF(D61="?OLD","!!!","")</f>
@@ -4355,16 +4332,7 @@
     </row>
     <row r="62" spans="1:12">
       <c r="A62" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="B62" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="C62" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D62" s="21" t="s">
-        <v>108</v>
+        <v>157</v>
       </c>
       <c r="E62" s="22">
         <f>IF(D62="?OLD","!!!","")</f>
@@ -4398,7 +4366,16 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63" s="20" t="s">
-        <v>149</v>
+        <v>127</v>
+      </c>
+      <c r="B63" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="C63" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E63" s="22">
         <f>IF(D63="?OLD","!!!","")</f>
@@ -4432,7 +4409,16 @@
     </row>
     <row r="64" spans="1:12">
       <c r="A64" s="20" t="s">
-        <v>153</v>
+        <v>129</v>
+      </c>
+      <c r="B64" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="C64" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D64" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E64" s="22">
         <f>IF(D64="?OLD","!!!","")</f>
@@ -4500,16 +4486,7 @@
     </row>
     <row r="66" spans="1:12">
       <c r="A66" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B66" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C66" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D66" s="21" t="s">
-        <v>108</v>
+        <v>158</v>
       </c>
       <c r="E66" s="22">
         <f>IF(D66="?OLD","!!!","")</f>
@@ -4543,7 +4520,7 @@
     </row>
     <row r="67" spans="1:12">
       <c r="A67" s="20" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="E67" s="22">
         <f>IF(D67="?OLD","!!!","")</f>
@@ -4577,16 +4554,16 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68" s="20" t="s">
-        <v>109</v>
+        <v>160</v>
       </c>
       <c r="B68" s="21" t="s">
         <v>118</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D68" s="21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E68" s="22">
         <f>IF(D68="?OLD","!!!","")</f>
@@ -4620,7 +4597,7 @@
     </row>
     <row r="69" spans="1:12">
       <c r="A69" s="20" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="E69" s="22">
         <f>IF(D69="?OLD","!!!","")</f>
@@ -4654,7 +4631,16 @@
     </row>
     <row r="70" spans="1:12">
       <c r="A70" s="20" t="s">
-        <v>157</v>
+        <v>113</v>
+      </c>
+      <c r="B70" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="C70" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D70" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E70" s="22">
         <f>IF(D70="?OLD","!!!","")</f>
@@ -4688,7 +4674,7 @@
     </row>
     <row r="71" spans="1:12">
       <c r="A71" s="20" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="E71" s="22">
         <f>IF(D71="?OLD","!!!","")</f>
@@ -4721,93 +4707,84 @@
       <c r="L71" s="27"/>
     </row>
     <row r="72" spans="1:12">
-      <c r="A72" s="20"/>
+      <c r="A72" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="E72" s="22">
+        <f>IF(D72="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F72" s="23" t="str">
+        <f>IF(OR(E72="",E72="!!!"),"",IF(NOT(ISNA(VLOOKUP(E72,E$1:E71,1,FALSE()))),"OLD",IF(AND(E72&lt;&gt;"",E72&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G72" s="24" t="str">
+        <f>IF(OR(E72="",E72="!!!"),"",IF(OR(J72=0,AND(J72=1,K72=1),AND(J72=1,I72="SBJ"),AND(J72=1,I72=0)),"?IN_FOCUS",IF(J72&lt;=2,"?ACTIVATED",IF(J72&lt;&gt;"","?FAMILIAR",IF(F72="NEW",IF(ISNA(VLOOKUP(E72,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H72" s="25" t="str">
+        <f>IF(J72&lt;&gt;1,"",IF(I72="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I72" s="26" t="str">
+        <f>IF(OR(E72="",E72="!!!",F72="NEW"),"",INDEX(B71:B$2,-1+SUMPRODUCT(MAX(ROW(E71:E$2)*(E72=E71:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J72" s="26" t="str">
+        <f>IF(OR(E72="",E72="!!!",F72="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E72)*(E72=E$2:E72)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E71)*(E2=E$1:E71))))))</f>
+        <v> </v>
+      </c>
+      <c r="K72" s="26" t="str">
+        <f>IF(OR(E72="",E72="!!!",F72="NEW"),"",INDEX(J$1:J71,SUMPRODUCT(MAX(ROW(E$1:E71)*(E72=E$1:E71)))))</f>
+        <v> </v>
+      </c>
+      <c r="L72" s="27"/>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" s="20" t="s">
-        <v>158</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="E73" s="22">
+        <f>IF(D73="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F73" s="23" t="str">
+        <f>IF(OR(E73="",E73="!!!"),"",IF(NOT(ISNA(VLOOKUP(E73,E$1:E72,1,FALSE()))),"OLD",IF(AND(E73&lt;&gt;"",E73&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G73" s="24" t="str">
+        <f>IF(OR(E73="",E73="!!!"),"",IF(OR(J73=0,AND(J73=1,K73=1),AND(J73=1,I73="SBJ"),AND(J73=1,I73=0)),"?IN_FOCUS",IF(J73&lt;=2,"?ACTIVATED",IF(J73&lt;&gt;"","?FAMILIAR",IF(F73="NEW",IF(ISNA(VLOOKUP(E73,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H73" s="25" t="str">
+        <f>IF(J73&lt;&gt;1,"",IF(I73="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I73" s="26" t="str">
+        <f>IF(OR(E73="",E73="!!!",F73="NEW"),"",INDEX(B72:B$2,-1+SUMPRODUCT(MAX(ROW(E72:E$2)*(E73=E72:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J73" s="26" t="str">
+        <f>IF(OR(E73="",E73="!!!",F73="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E73)*(E73=E$2:E73)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E72)*(E2=E$1:E72))))))</f>
+        <v> </v>
+      </c>
+      <c r="K73" s="26" t="str">
+        <f>IF(OR(E73="",E73="!!!",F73="NEW"),"",INDEX(J$1:J72,SUMPRODUCT(MAX(ROW(E$1:E72)*(E73=E$1:E72)))))</f>
+        <v> </v>
+      </c>
+      <c r="L73" s="27"/>
     </row>
     <row r="74" spans="1:12">
-      <c r="A74" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="E74" s="22">
-        <f>IF(D74="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F74" s="23" t="str">
-        <f>IF(OR(E74="",E74="!!!"),"",IF(NOT(ISNA(VLOOKUP(E74,E$1:E73,1,FALSE()))),"OLD",IF(AND(E74&lt;&gt;"",E74&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G74" s="24" t="str">
-        <f>IF(OR(E74="",E74="!!!"),"",IF(OR(J74=0,AND(J74=1,K74=1),AND(J74=1,I74="SBJ"),AND(J74=1,I74=0)),"?IN_FOCUS",IF(J74&lt;=2,"?ACTIVATED",IF(J74&lt;&gt;"","?FAMILIAR",IF(F74="NEW",IF(ISNA(VLOOKUP(E74,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H74" s="25" t="str">
-        <f>IF(J74&lt;&gt;1,"",IF(I74="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I74" s="26" t="str">
-        <f>IF(OR(E74="",E74="!!!",F74="NEW"),"",INDEX(B73:B$2,-1+SUMPRODUCT(MAX(ROW(E73:E$2)*(E74=E73:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J74" s="26" t="str">
-        <f>IF(OR(E74="",E74="!!!",F74="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E74)*(E74=E$2:E74)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E73)*(E2=E$1:E73))))))</f>
-        <v> </v>
-      </c>
-      <c r="K74" s="26" t="str">
-        <f>IF(OR(E74="",E74="!!!",F74="NEW"),"",INDEX(J$1:J73,SUMPRODUCT(MAX(ROW(E$1:E73)*(E74=E$1:E73)))))</f>
-        <v> </v>
-      </c>
-      <c r="L74" s="27"/>
+      <c r="A74" s="20"/>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="B75" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="C75" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D75" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="E75" s="22">
-        <f>IF(D75="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F75" s="23" t="str">
-        <f>IF(OR(E75="",E75="!!!"),"",IF(NOT(ISNA(VLOOKUP(E75,E$1:E74,1,FALSE()))),"OLD",IF(AND(E75&lt;&gt;"",E75&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G75" s="24" t="str">
-        <f>IF(OR(E75="",E75="!!!"),"",IF(OR(J75=0,AND(J75=1,K75=1),AND(J75=1,I75="SBJ"),AND(J75=1,I75=0)),"?IN_FOCUS",IF(J75&lt;=2,"?ACTIVATED",IF(J75&lt;&gt;"","?FAMILIAR",IF(F75="NEW",IF(ISNA(VLOOKUP(E75,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H75" s="25" t="str">
-        <f>IF(J75&lt;&gt;1,"",IF(I75="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I75" s="26" t="str">
-        <f>IF(OR(E75="",E75="!!!",F75="NEW"),"",INDEX(B74:B$2,-1+SUMPRODUCT(MAX(ROW(E74:E$2)*(E75=E74:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J75" s="26" t="str">
-        <f>IF(OR(E75="",E75="!!!",F75="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E75)*(E75=E$2:E75)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E74)*(E2=E$1:E74))))))</f>
-        <v> </v>
-      </c>
-      <c r="K75" s="26" t="str">
-        <f>IF(OR(E75="",E75="!!!",F75="NEW"),"",INDEX(J$1:J74,SUMPRODUCT(MAX(ROW(E$1:E74)*(E75=E$1:E74)))))</f>
-        <v> </v>
-      </c>
-      <c r="L75" s="27"/>
+        <v>163</v>
+      </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" s="20" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="E76" s="22">
         <f>IF(D76="?OLD","!!!","")</f>
@@ -4841,10 +4818,16 @@
     </row>
     <row r="77" spans="1:12">
       <c r="A77" s="20" t="s">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="B77" s="21" t="s">
-        <v>148</v>
+        <v>110</v>
+      </c>
+      <c r="C77" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D77" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E77" s="22">
         <f>IF(D77="?OLD","!!!","")</f>
@@ -4878,7 +4861,7 @@
     </row>
     <row r="78" spans="1:12">
       <c r="A78" s="20" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E78" s="22">
         <f>IF(D78="?OLD","!!!","")</f>
@@ -4912,7 +4895,10 @@
     </row>
     <row r="79" spans="1:12">
       <c r="A79" s="20" t="s">
-        <v>162</v>
+        <v>165</v>
+      </c>
+      <c r="B79" s="21" t="s">
+        <v>153</v>
       </c>
       <c r="E79" s="22">
         <f>IF(D79="?OLD","!!!","")</f>
@@ -4946,7 +4932,7 @@
     </row>
     <row r="80" spans="1:12">
       <c r="A80" s="20" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="E80" s="22">
         <f>IF(D80="?OLD","!!!","")</f>
@@ -4980,7 +4966,7 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81" s="20" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E81" s="22">
         <f>IF(D81="?OLD","!!!","")</f>
@@ -5014,16 +5000,7 @@
     </row>
     <row r="82" spans="1:12">
       <c r="A82" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="B82" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="C82" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="D82" s="21" t="s">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="E82" s="22">
         <f>IF(D82="?OLD","!!!","")</f>
@@ -5057,7 +5034,7 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83" s="20" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E83" s="22">
         <f>IF(D83="?OLD","!!!","")</f>
@@ -5091,7 +5068,16 @@
     </row>
     <row r="84" spans="1:12">
       <c r="A84" s="20" t="s">
-        <v>167</v>
+        <v>169</v>
+      </c>
+      <c r="B84" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="C84" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="D84" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E84" s="22">
         <f>IF(D84="?OLD","!!!","")</f>
@@ -5125,13 +5111,7 @@
     </row>
     <row r="85" spans="1:12">
       <c r="A85" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="B85" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C85" s="21" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E85" s="22">
         <f>IF(D85="?OLD","!!!","")</f>
@@ -5165,7 +5145,7 @@
     </row>
     <row r="86" spans="1:12">
       <c r="A86" s="20" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E86" s="22">
         <f>IF(D86="?OLD","!!!","")</f>
@@ -5199,7 +5179,13 @@
     </row>
     <row r="87" spans="1:12">
       <c r="A87" s="20" t="s">
-        <v>171</v>
+        <v>173</v>
+      </c>
+      <c r="B87" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C87" s="21" t="s">
+        <v>174</v>
       </c>
       <c r="E87" s="22">
         <f>IF(D87="?OLD","!!!","")</f>
@@ -5233,7 +5219,7 @@
     </row>
     <row r="88" spans="1:12">
       <c r="A88" s="20" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E88" s="22">
         <f>IF(D88="?OLD","!!!","")</f>
@@ -5267,7 +5253,7 @@
     </row>
     <row r="89" spans="1:12">
       <c r="A89" s="20" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E89" s="22">
         <f>IF(D89="?OLD","!!!","")</f>
@@ -5301,7 +5287,7 @@
     </row>
     <row r="90" spans="1:12">
       <c r="A90" s="20" t="s">
-        <v>64</v>
+        <v>177</v>
       </c>
       <c r="E90" s="22">
         <f>IF(D90="?OLD","!!!","")</f>
@@ -5335,7 +5321,7 @@
     </row>
     <row r="91" spans="1:12">
       <c r="A91" s="20" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E91" s="22">
         <f>IF(D91="?OLD","!!!","")</f>
@@ -5369,7 +5355,7 @@
     </row>
     <row r="92" spans="1:12">
       <c r="A92" s="20" t="s">
-        <v>138</v>
+        <v>68</v>
       </c>
       <c r="E92" s="22">
         <f>IF(D92="?OLD","!!!","")</f>
@@ -5402,11 +5388,42 @@
       <c r="L92" s="27"/>
     </row>
     <row r="93" spans="1:12">
-      <c r="A93" s="20"/>
+      <c r="A93" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="E93" s="22">
+        <f>IF(D93="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F93" s="23" t="str">
+        <f>IF(OR(E93="",E93="!!!"),"",IF(NOT(ISNA(VLOOKUP(E93,E$1:E92,1,FALSE()))),"OLD",IF(AND(E93&lt;&gt;"",E93&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G93" s="24" t="str">
+        <f>IF(OR(E93="",E93="!!!"),"",IF(OR(J93=0,AND(J93=1,K93=1),AND(J93=1,I93="SBJ"),AND(J93=1,I93=0)),"?IN_FOCUS",IF(J93&lt;=2,"?ACTIVATED",IF(J93&lt;&gt;"","?FAMILIAR",IF(F93="NEW",IF(ISNA(VLOOKUP(E93,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H93" s="25" t="str">
+        <f>IF(J93&lt;&gt;1,"",IF(I93="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I93" s="26" t="str">
+        <f>IF(OR(E93="",E93="!!!",F93="NEW"),"",INDEX(B92:B$2,-1+SUMPRODUCT(MAX(ROW(E92:E$2)*(E93=E92:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J93" s="26" t="str">
+        <f>IF(OR(E93="",E93="!!!",F93="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E93)*(E93=E$2:E93)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E92)*(E2=E$1:E92))))))</f>
+        <v> </v>
+      </c>
+      <c r="K93" s="26" t="str">
+        <f>IF(OR(E93="",E93="!!!",F93="NEW"),"",INDEX(J$1:J92,SUMPRODUCT(MAX(ROW(E$1:E92)*(E93=E$1:E92)))))</f>
+        <v> </v>
+      </c>
+      <c r="L93" s="27"/>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" s="20" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="E94" s="22">
         <f>IF(D94="?OLD","!!!","")</f>
@@ -5439,13 +5456,11 @@
       <c r="L94" s="27"/>
     </row>
     <row r="95" spans="1:12">
-      <c r="A95" s="20" t="s">
-        <v>176</v>
-      </c>
+      <c r="A95" s="20"/>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" s="20" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E96" s="22">
         <f>IF(D96="?OLD","!!!","")</f>
@@ -5479,59 +5494,12 @@
     </row>
     <row r="97" spans="1:12">
       <c r="A97" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="B97" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C97" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="D97" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="E97" s="22">
-        <f>IF(D97="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F97" s="23" t="str">
-        <f>IF(OR(E97="",E97="!!!"),"",IF(NOT(ISNA(VLOOKUP(E97,E$1:E96,1,FALSE()))),"OLD",IF(AND(E97&lt;&gt;"",E97&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G97" s="24" t="str">
-        <f>IF(OR(E97="",E97="!!!"),"",IF(OR(J97=0,AND(J97=1,K97=1),AND(J97=1,I97="SBJ"),AND(J97=1,I97=0)),"?IN_FOCUS",IF(J97&lt;=2,"?ACTIVATED",IF(J97&lt;&gt;"","?FAMILIAR",IF(F97="NEW",IF(ISNA(VLOOKUP(E97,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H97" s="25" t="str">
-        <f>IF(J97&lt;&gt;1,"",IF(I97="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I97" s="26" t="str">
-        <f>IF(OR(E97="",E97="!!!",F97="NEW"),"",INDEX(B96:B$2,-1+SUMPRODUCT(MAX(ROW(E96:E$2)*(E97=E96:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J97" s="26" t="str">
-        <f>IF(OR(E97="",E97="!!!",F97="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E97)*(E97=E$2:E97)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E96)*(E2=E$1:E96))))))</f>
-        <v> </v>
-      </c>
-      <c r="K97" s="26" t="str">
-        <f>IF(OR(E97="",E97="!!!",F97="NEW"),"",INDEX(J$1:J96,SUMPRODUCT(MAX(ROW(E$1:E96)*(E97=E$1:E96)))))</f>
-        <v> </v>
-      </c>
-      <c r="L97" s="27"/>
+        <v>181</v>
+      </c>
     </row>
     <row r="98" spans="1:12">
       <c r="A98" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="B98" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="C98" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="D98" s="21" t="s">
-        <v>108</v>
+        <v>182</v>
       </c>
       <c r="E98" s="22">
         <f>IF(D98="?OLD","!!!","")</f>
@@ -5565,7 +5533,16 @@
     </row>
     <row r="99" spans="1:12">
       <c r="A99" s="20" t="s">
-        <v>182</v>
+        <v>183</v>
+      </c>
+      <c r="B99" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C99" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D99" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E99" s="22">
         <f>IF(D99="?OLD","!!!","")</f>
@@ -5599,16 +5576,16 @@
     </row>
     <row r="100" spans="1:12">
       <c r="A100" s="20" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B100" s="21" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="C100" s="21" t="s">
-        <v>107</v>
+        <v>186</v>
       </c>
       <c r="D100" s="21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E100" s="22">
         <f>IF(D100="?OLD","!!!","")</f>
@@ -5642,7 +5619,7 @@
     </row>
     <row r="101" spans="1:12">
       <c r="A101" s="20" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E101" s="22">
         <f>IF(D101="?OLD","!!!","")</f>
@@ -5676,16 +5653,16 @@
     </row>
     <row r="102" spans="1:12">
       <c r="A102" s="20" t="s">
-        <v>125</v>
+        <v>188</v>
       </c>
       <c r="B102" s="21" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C102" s="21" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D102" s="21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E102" s="22">
         <f>IF(D102="?OLD","!!!","")</f>
@@ -5719,7 +5696,7 @@
     </row>
     <row r="103" spans="1:12">
       <c r="A103" s="20" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E103" s="22">
         <f>IF(D103="?OLD","!!!","")</f>
@@ -5753,16 +5730,16 @@
     </row>
     <row r="104" spans="1:12">
       <c r="A104" s="20" t="s">
-        <v>185</v>
+        <v>129</v>
       </c>
       <c r="B104" s="21" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="C104" s="21" t="s">
-        <v>186</v>
+        <v>111</v>
       </c>
       <c r="D104" s="21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E104" s="22">
         <f>IF(D104="?OLD","!!!","")</f>
@@ -5796,7 +5773,7 @@
     </row>
     <row r="105" spans="1:12">
       <c r="A105" s="20" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E105" s="22">
         <f>IF(D105="?OLD","!!!","")</f>
@@ -5830,7 +5807,16 @@
     </row>
     <row r="106" spans="1:12">
       <c r="A106" s="20" t="s">
-        <v>150</v>
+        <v>190</v>
+      </c>
+      <c r="B106" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C106" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="D106" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E106" s="22">
         <f>IF(D106="?OLD","!!!","")</f>
@@ -5864,7 +5850,7 @@
     </row>
     <row r="107" spans="1:12">
       <c r="A107" s="20" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E107" s="22">
         <f>IF(D107="?OLD","!!!","")</f>
@@ -5898,13 +5884,7 @@
     </row>
     <row r="108" spans="1:12">
       <c r="A108" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="B108" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="C108" s="21" t="s">
-        <v>191</v>
+        <v>155</v>
       </c>
       <c r="E108" s="22">
         <f>IF(D108="?OLD","!!!","")</f>
@@ -5938,7 +5918,7 @@
     </row>
     <row r="109" spans="1:12">
       <c r="A109" s="20" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E109" s="22">
         <f>IF(D109="?OLD","!!!","")</f>
@@ -5972,7 +5952,13 @@
     </row>
     <row r="110" spans="1:12">
       <c r="A110" s="20" t="s">
-        <v>193</v>
+        <v>194</v>
+      </c>
+      <c r="B110" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="C110" s="21" t="s">
+        <v>196</v>
       </c>
       <c r="E110" s="22">
         <f>IF(D110="?OLD","!!!","")</f>
@@ -6006,7 +5992,7 @@
     </row>
     <row r="111" spans="1:12">
       <c r="A111" s="20" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="E111" s="22">
         <f>IF(D111="?OLD","!!!","")</f>
@@ -6039,93 +6025,93 @@
       <c r="L111" s="27"/>
     </row>
     <row r="112" spans="1:12">
-      <c r="A112" s="20"/>
+      <c r="A112" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="E112" s="22">
+        <f>IF(D112="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F112" s="23" t="str">
+        <f>IF(OR(E112="",E112="!!!"),"",IF(NOT(ISNA(VLOOKUP(E112,E$1:E111,1,FALSE()))),"OLD",IF(AND(E112&lt;&gt;"",E112&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G112" s="24" t="str">
+        <f>IF(OR(E112="",E112="!!!"),"",IF(OR(J112=0,AND(J112=1,K112=1),AND(J112=1,I112="SBJ"),AND(J112=1,I112=0)),"?IN_FOCUS",IF(J112&lt;=2,"?ACTIVATED",IF(J112&lt;&gt;"","?FAMILIAR",IF(F112="NEW",IF(ISNA(VLOOKUP(E112,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H112" s="25" t="str">
+        <f>IF(J112&lt;&gt;1,"",IF(I112="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I112" s="26" t="str">
+        <f>IF(OR(E112="",E112="!!!",F112="NEW"),"",INDEX(B111:B$2,-1+SUMPRODUCT(MAX(ROW(E111:E$2)*(E112=E111:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J112" s="26" t="str">
+        <f>IF(OR(E112="",E112="!!!",F112="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E112)*(E112=E$2:E112)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E111)*(E2=E$1:E111))))))</f>
+        <v> </v>
+      </c>
+      <c r="K112" s="26" t="str">
+        <f>IF(OR(E112="",E112="!!!",F112="NEW"),"",INDEX(J$1:J111,SUMPRODUCT(MAX(ROW(E$1:E111)*(E112=E$1:E111)))))</f>
+        <v> </v>
+      </c>
+      <c r="L112" s="27"/>
     </row>
     <row r="113" spans="1:12">
       <c r="A113" s="20" t="s">
-        <v>194</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="E113" s="22">
+        <f>IF(D113="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F113" s="23" t="str">
+        <f>IF(OR(E113="",E113="!!!"),"",IF(NOT(ISNA(VLOOKUP(E113,E$1:E112,1,FALSE()))),"OLD",IF(AND(E113&lt;&gt;"",E113&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G113" s="24" t="str">
+        <f>IF(OR(E113="",E113="!!!"),"",IF(OR(J113=0,AND(J113=1,K113=1),AND(J113=1,I113="SBJ"),AND(J113=1,I113=0)),"?IN_FOCUS",IF(J113&lt;=2,"?ACTIVATED",IF(J113&lt;&gt;"","?FAMILIAR",IF(F113="NEW",IF(ISNA(VLOOKUP(E113,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H113" s="25" t="str">
+        <f>IF(J113&lt;&gt;1,"",IF(I113="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I113" s="26" t="str">
+        <f>IF(OR(E113="",E113="!!!",F113="NEW"),"",INDEX(B112:B$2,-1+SUMPRODUCT(MAX(ROW(E112:E$2)*(E113=E112:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J113" s="26" t="str">
+        <f>IF(OR(E113="",E113="!!!",F113="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E113)*(E113=E$2:E113)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E112)*(E2=E$1:E112))))))</f>
+        <v> </v>
+      </c>
+      <c r="K113" s="26" t="str">
+        <f>IF(OR(E113="",E113="!!!",F113="NEW"),"",INDEX(J$1:J112,SUMPRODUCT(MAX(ROW(E$1:E112)*(E113=E$1:E112)))))</f>
+        <v> </v>
+      </c>
+      <c r="L113" s="27"/>
     </row>
     <row r="114" spans="1:12">
-      <c r="A114" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="B114" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="C114" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="D114" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="E114" s="22">
-        <f>IF(D114="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F114" s="23" t="str">
-        <f>IF(OR(E114="",E114="!!!"),"",IF(NOT(ISNA(VLOOKUP(E114,E$1:E113,1,FALSE()))),"OLD",IF(AND(E114&lt;&gt;"",E114&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G114" s="24" t="str">
-        <f>IF(OR(E114="",E114="!!!"),"",IF(OR(J114=0,AND(J114=1,K114=1),AND(J114=1,I114="SBJ"),AND(J114=1,I114=0)),"?IN_FOCUS",IF(J114&lt;=2,"?ACTIVATED",IF(J114&lt;&gt;"","?FAMILIAR",IF(F114="NEW",IF(ISNA(VLOOKUP(E114,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H114" s="25" t="str">
-        <f>IF(J114&lt;&gt;1,"",IF(I114="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I114" s="26" t="str">
-        <f>IF(OR(E114="",E114="!!!",F114="NEW"),"",INDEX(B113:B$2,-1+SUMPRODUCT(MAX(ROW(E113:E$2)*(E114=E113:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J114" s="26" t="str">
-        <f>IF(OR(E114="",E114="!!!",F114="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E114)*(E114=E$2:E114)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E113)*(E2=E$1:E113))))))</f>
-        <v> </v>
-      </c>
-      <c r="K114" s="26" t="str">
-        <f>IF(OR(E114="",E114="!!!",F114="NEW"),"",INDEX(J$1:J113,SUMPRODUCT(MAX(ROW(E$1:E113)*(E114=E$1:E113)))))</f>
-        <v> </v>
-      </c>
-      <c r="L114" s="27"/>
+      <c r="A114" s="20"/>
     </row>
     <row r="115" spans="1:12">
       <c r="A115" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="E115" s="22">
-        <f>IF(D115="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F115" s="23" t="str">
-        <f>IF(OR(E115="",E115="!!!"),"",IF(NOT(ISNA(VLOOKUP(E115,E$1:E114,1,FALSE()))),"OLD",IF(AND(E115&lt;&gt;"",E115&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G115" s="24" t="str">
-        <f>IF(OR(E115="",E115="!!!"),"",IF(OR(J115=0,AND(J115=1,K115=1),AND(J115=1,I115="SBJ"),AND(J115=1,I115=0)),"?IN_FOCUS",IF(J115&lt;=2,"?ACTIVATED",IF(J115&lt;&gt;"","?FAMILIAR",IF(F115="NEW",IF(ISNA(VLOOKUP(E115,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H115" s="25" t="str">
-        <f>IF(J115&lt;&gt;1,"",IF(I115="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I115" s="26" t="str">
-        <f>IF(OR(E115="",E115="!!!",F115="NEW"),"",INDEX(B114:B$2,-1+SUMPRODUCT(MAX(ROW(E114:E$2)*(E115=E114:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J115" s="26" t="str">
-        <f>IF(OR(E115="",E115="!!!",F115="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E115)*(E115=E$2:E115)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E114)*(E2=E$1:E114))))))</f>
-        <v> </v>
-      </c>
-      <c r="K115" s="26" t="str">
-        <f>IF(OR(E115="",E115="!!!",F115="NEW"),"",INDEX(J$1:J114,SUMPRODUCT(MAX(ROW(E$1:E114)*(E115=E$1:E114)))))</f>
-        <v> </v>
-      </c>
-      <c r="L115" s="27"/>
+        <v>199</v>
+      </c>
     </row>
     <row r="116" spans="1:12">
       <c r="A116" s="20" t="s">
-        <v>153</v>
+        <v>200</v>
+      </c>
+      <c r="B116" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C116" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="D116" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E116" s="22">
         <f>IF(D116="?OLD","!!!","")</f>
@@ -6159,7 +6145,7 @@
     </row>
     <row r="117" spans="1:12">
       <c r="A117" s="20" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E117" s="22">
         <f>IF(D117="?OLD","!!!","")</f>
@@ -6193,16 +6179,7 @@
     </row>
     <row r="118" spans="1:12">
       <c r="A118" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="B118" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="C118" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D118" s="21" t="s">
-        <v>108</v>
+        <v>158</v>
       </c>
       <c r="E118" s="22">
         <f>IF(D118="?OLD","!!!","")</f>
@@ -6236,7 +6213,7 @@
     </row>
     <row r="119" spans="1:12">
       <c r="A119" s="20" t="s">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="E119" s="22">
         <f>IF(D119="?OLD","!!!","")</f>
@@ -6270,13 +6247,16 @@
     </row>
     <row r="120" spans="1:12">
       <c r="A120" s="20" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B120" s="21" t="s">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="C120" s="21" t="s">
-        <v>191</v>
+        <v>128</v>
+      </c>
+      <c r="D120" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E120" s="22">
         <f>IF(D120="?OLD","!!!","")</f>
@@ -6310,16 +6290,7 @@
     </row>
     <row r="121" spans="1:12">
       <c r="A121" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="B121" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C121" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D121" s="21" t="s">
-        <v>108</v>
+        <v>154</v>
       </c>
       <c r="E121" s="22">
         <f>IF(D121="?OLD","!!!","")</f>
@@ -6353,7 +6324,13 @@
     </row>
     <row r="122" spans="1:12">
       <c r="A122" s="20" t="s">
-        <v>202</v>
+        <v>205</v>
+      </c>
+      <c r="B122" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="C122" s="21" t="s">
+        <v>196</v>
       </c>
       <c r="E122" s="22">
         <f>IF(D122="?OLD","!!!","")</f>
@@ -6387,16 +6364,16 @@
     </row>
     <row r="123" spans="1:12">
       <c r="A123" s="20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B123" s="21" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="C123" s="21" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D123" s="21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E123" s="22">
         <f>IF(D123="?OLD","!!!","")</f>
@@ -6430,7 +6407,7 @@
     </row>
     <row r="124" spans="1:12">
       <c r="A124" s="20" t="s">
-        <v>150</v>
+        <v>207</v>
       </c>
       <c r="E124" s="22">
         <f>IF(D124="?OLD","!!!","")</f>
@@ -6464,7 +6441,16 @@
     </row>
     <row r="125" spans="1:12">
       <c r="A125" s="20" t="s">
-        <v>204</v>
+        <v>208</v>
+      </c>
+      <c r="B125" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C125" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D125" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E125" s="22">
         <f>IF(D125="?OLD","!!!","")</f>
@@ -6498,7 +6484,7 @@
     </row>
     <row r="126" spans="1:12">
       <c r="A126" s="20" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="E126" s="22">
         <f>IF(D126="?OLD","!!!","")</f>
@@ -6532,16 +6518,7 @@
     </row>
     <row r="127" spans="1:12">
       <c r="A127" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="B127" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="C127" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D127" s="21" t="s">
-        <v>108</v>
+        <v>209</v>
       </c>
       <c r="E127" s="22">
         <f>IF(D127="?OLD","!!!","")</f>
@@ -6575,7 +6552,7 @@
     </row>
     <row r="128" spans="1:12">
       <c r="A128" s="20" t="s">
-        <v>206</v>
+        <v>132</v>
       </c>
       <c r="E128" s="22">
         <f>IF(D128="?OLD","!!!","")</f>
@@ -6609,7 +6586,16 @@
     </row>
     <row r="129" spans="1:12">
       <c r="A129" s="20" t="s">
-        <v>207</v>
+        <v>210</v>
+      </c>
+      <c r="B129" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C129" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D129" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E129" s="22">
         <f>IF(D129="?OLD","!!!","")</f>
@@ -6643,7 +6629,7 @@
     </row>
     <row r="130" spans="1:12">
       <c r="A130" s="20" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E130" s="22">
         <f>IF(D130="?OLD","!!!","")</f>
@@ -6677,7 +6663,7 @@
     </row>
     <row r="131" spans="1:12">
       <c r="A131" s="20" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E131" s="22">
         <f>IF(D131="?OLD","!!!","")</f>
@@ -6711,13 +6697,7 @@
     </row>
     <row r="132" spans="1:12">
       <c r="A132" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="B132" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C132" s="21" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E132" s="22">
         <f>IF(D132="?OLD","!!!","")</f>
@@ -6751,7 +6731,7 @@
     </row>
     <row r="133" spans="1:12">
       <c r="A133" s="20" t="s">
-        <v>128</v>
+        <v>214</v>
       </c>
       <c r="E133" s="22">
         <f>IF(D133="?OLD","!!!","")</f>
@@ -6785,16 +6765,13 @@
     </row>
     <row r="134" spans="1:12">
       <c r="A134" s="20" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="B134" s="21" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="C134" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D134" s="21" t="s">
-        <v>108</v>
+        <v>215</v>
       </c>
       <c r="E134" s="22">
         <f>IF(D134="?OLD","!!!","")</f>
@@ -6828,7 +6805,7 @@
     </row>
     <row r="135" spans="1:12">
       <c r="A135" s="20" t="s">
-        <v>212</v>
+        <v>132</v>
       </c>
       <c r="E135" s="22">
         <f>IF(D135="?OLD","!!!","")</f>
@@ -6862,7 +6839,16 @@
     </row>
     <row r="136" spans="1:12">
       <c r="A136" s="20" t="s">
-        <v>213</v>
+        <v>216</v>
+      </c>
+      <c r="B136" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C136" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D136" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E136" s="22">
         <f>IF(D136="?OLD","!!!","")</f>
@@ -6896,7 +6882,7 @@
     </row>
     <row r="137" spans="1:12">
       <c r="A137" s="20" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E137" s="22">
         <f>IF(D137="?OLD","!!!","")</f>
@@ -6930,7 +6916,7 @@
     </row>
     <row r="138" spans="1:12">
       <c r="A138" s="20" t="s">
-        <v>138</v>
+        <v>218</v>
       </c>
       <c r="E138" s="22">
         <f>IF(D138="?OLD","!!!","")</f>
@@ -6963,84 +6949,84 @@
       <c r="L138" s="27"/>
     </row>
     <row r="139" spans="1:12">
-      <c r="A139" s="20"/>
+      <c r="A139" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="E139" s="22">
+        <f>IF(D139="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F139" s="23" t="str">
+        <f>IF(OR(E139="",E139="!!!"),"",IF(NOT(ISNA(VLOOKUP(E139,E$1:E138,1,FALSE()))),"OLD",IF(AND(E139&lt;&gt;"",E139&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G139" s="24" t="str">
+        <f>IF(OR(E139="",E139="!!!"),"",IF(OR(J139=0,AND(J139=1,K139=1),AND(J139=1,I139="SBJ"),AND(J139=1,I139=0)),"?IN_FOCUS",IF(J139&lt;=2,"?ACTIVATED",IF(J139&lt;&gt;"","?FAMILIAR",IF(F139="NEW",IF(ISNA(VLOOKUP(E139,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H139" s="25" t="str">
+        <f>IF(J139&lt;&gt;1,"",IF(I139="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I139" s="26" t="str">
+        <f>IF(OR(E139="",E139="!!!",F139="NEW"),"",INDEX(B138:B$2,-1+SUMPRODUCT(MAX(ROW(E138:E$2)*(E139=E138:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J139" s="26" t="str">
+        <f>IF(OR(E139="",E139="!!!",F139="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E139)*(E139=E$2:E139)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E138)*(E2=E$1:E138))))))</f>
+        <v> </v>
+      </c>
+      <c r="K139" s="26" t="str">
+        <f>IF(OR(E139="",E139="!!!",F139="NEW"),"",INDEX(J$1:J138,SUMPRODUCT(MAX(ROW(E$1:E138)*(E139=E$1:E138)))))</f>
+        <v> </v>
+      </c>
+      <c r="L139" s="27"/>
     </row>
     <row r="140" spans="1:12">
       <c r="A140" s="20" t="s">
-        <v>215</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="E140" s="22">
+        <f>IF(D140="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F140" s="23" t="str">
+        <f>IF(OR(E140="",E140="!!!"),"",IF(NOT(ISNA(VLOOKUP(E140,E$1:E139,1,FALSE()))),"OLD",IF(AND(E140&lt;&gt;"",E140&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G140" s="24" t="str">
+        <f>IF(OR(E140="",E140="!!!"),"",IF(OR(J140=0,AND(J140=1,K140=1),AND(J140=1,I140="SBJ"),AND(J140=1,I140=0)),"?IN_FOCUS",IF(J140&lt;=2,"?ACTIVATED",IF(J140&lt;&gt;"","?FAMILIAR",IF(F140="NEW",IF(ISNA(VLOOKUP(E140,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H140" s="25" t="str">
+        <f>IF(J140&lt;&gt;1,"",IF(I140="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I140" s="26" t="str">
+        <f>IF(OR(E140="",E140="!!!",F140="NEW"),"",INDEX(B139:B$2,-1+SUMPRODUCT(MAX(ROW(E139:E$2)*(E140=E139:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J140" s="26" t="str">
+        <f>IF(OR(E140="",E140="!!!",F140="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E140)*(E140=E$2:E140)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E139)*(E2=E$1:E139))))))</f>
+        <v> </v>
+      </c>
+      <c r="K140" s="26" t="str">
+        <f>IF(OR(E140="",E140="!!!",F140="NEW"),"",INDEX(J$1:J139,SUMPRODUCT(MAX(ROW(E$1:E139)*(E140=E$1:E139)))))</f>
+        <v> </v>
+      </c>
+      <c r="L140" s="27"/>
     </row>
     <row r="141" spans="1:12">
-      <c r="A141" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="E141" s="22">
-        <f>IF(D141="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F141" s="23" t="str">
-        <f>IF(OR(E141="",E141="!!!"),"",IF(NOT(ISNA(VLOOKUP(E141,E$1:E140,1,FALSE()))),"OLD",IF(AND(E141&lt;&gt;"",E141&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G141" s="24" t="str">
-        <f>IF(OR(E141="",E141="!!!"),"",IF(OR(J141=0,AND(J141=1,K141=1),AND(J141=1,I141="SBJ"),AND(J141=1,I141=0)),"?IN_FOCUS",IF(J141&lt;=2,"?ACTIVATED",IF(J141&lt;&gt;"","?FAMILIAR",IF(F141="NEW",IF(ISNA(VLOOKUP(E141,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H141" s="25" t="str">
-        <f>IF(J141&lt;&gt;1,"",IF(I141="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I141" s="26" t="str">
-        <f>IF(OR(E141="",E141="!!!",F141="NEW"),"",INDEX(B140:B$2,-1+SUMPRODUCT(MAX(ROW(E140:E$2)*(E141=E140:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J141" s="26" t="str">
-        <f>IF(OR(E141="",E141="!!!",F141="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E141)*(E141=E$2:E141)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E140)*(E2=E$1:E140))))))</f>
-        <v> </v>
-      </c>
-      <c r="K141" s="26" t="str">
-        <f>IF(OR(E141="",E141="!!!",F141="NEW"),"",INDEX(J$1:J140,SUMPRODUCT(MAX(ROW(E$1:E140)*(E141=E$1:E140)))))</f>
-        <v> </v>
-      </c>
-      <c r="L141" s="27"/>
+      <c r="A141" s="20"/>
     </row>
     <row r="142" spans="1:12">
       <c r="A142" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="E142" s="22">
-        <f>IF(D142="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F142" s="23" t="str">
-        <f>IF(OR(E142="",E142="!!!"),"",IF(NOT(ISNA(VLOOKUP(E142,E$1:E141,1,FALSE()))),"OLD",IF(AND(E142&lt;&gt;"",E142&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G142" s="24" t="str">
-        <f>IF(OR(E142="",E142="!!!"),"",IF(OR(J142=0,AND(J142=1,K142=1),AND(J142=1,I142="SBJ"),AND(J142=1,I142=0)),"?IN_FOCUS",IF(J142&lt;=2,"?ACTIVATED",IF(J142&lt;&gt;"","?FAMILIAR",IF(F142="NEW",IF(ISNA(VLOOKUP(E142,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H142" s="25" t="str">
-        <f>IF(J142&lt;&gt;1,"",IF(I142="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I142" s="26" t="str">
-        <f>IF(OR(E142="",E142="!!!",F142="NEW"),"",INDEX(B141:B$2,-1+SUMPRODUCT(MAX(ROW(E141:E$2)*(E142=E141:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J142" s="26" t="str">
-        <f>IF(OR(E142="",E142="!!!",F142="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E142)*(E142=E$2:E142)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E141)*(E2=E$1:E141))))))</f>
-        <v> </v>
-      </c>
-      <c r="K142" s="26" t="str">
-        <f>IF(OR(E142="",E142="!!!",F142="NEW"),"",INDEX(J$1:J141,SUMPRODUCT(MAX(ROW(E$1:E141)*(E142=E$1:E141)))))</f>
-        <v> </v>
-      </c>
-      <c r="L142" s="27"/>
+        <v>220</v>
+      </c>
     </row>
     <row r="143" spans="1:12">
       <c r="A143" s="20" t="s">
-        <v>159</v>
+        <v>221</v>
       </c>
       <c r="E143" s="22">
         <f>IF(D143="?OLD","!!!","")</f>
@@ -7074,16 +7060,7 @@
     </row>
     <row r="144" spans="1:12">
       <c r="A144" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="B144" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="C144" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="D144" s="21" t="s">
-        <v>108</v>
+        <v>222</v>
       </c>
       <c r="E144" s="22">
         <f>IF(D144="?OLD","!!!","")</f>
@@ -7117,10 +7094,7 @@
     </row>
     <row r="145" spans="1:12">
       <c r="A145" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="B145" s="21" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="E145" s="22">
         <f>IF(D145="?OLD","!!!","")</f>
@@ -7154,16 +7128,16 @@
     </row>
     <row r="146" spans="1:12">
       <c r="A146" s="20" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="B146" s="21" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="C146" s="21" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="D146" s="21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E146" s="22">
         <f>IF(D146="?OLD","!!!","")</f>
@@ -7197,7 +7171,10 @@
     </row>
     <row r="147" spans="1:12">
       <c r="A147" s="20" t="s">
-        <v>40</v>
+        <v>165</v>
+      </c>
+      <c r="B147" s="21" t="s">
+        <v>153</v>
       </c>
       <c r="E147" s="22">
         <f>IF(D147="?OLD","!!!","")</f>
@@ -7231,7 +7208,16 @@
     </row>
     <row r="148" spans="1:12">
       <c r="A148" s="20" t="s">
-        <v>150</v>
+        <v>190</v>
+      </c>
+      <c r="B148" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C148" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="D148" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E148" s="22">
         <f>IF(D148="?OLD","!!!","")</f>
@@ -7265,7 +7251,7 @@
     </row>
     <row r="149" spans="1:12">
       <c r="A149" s="20" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="E149" s="22">
         <f>IF(D149="?OLD","!!!","")</f>
@@ -7299,7 +7285,7 @@
     </row>
     <row r="150" spans="1:12">
       <c r="A150" s="20" t="s">
-        <v>218</v>
+        <v>155</v>
       </c>
       <c r="E150" s="22">
         <f>IF(D150="?OLD","!!!","")</f>
@@ -7333,13 +7319,7 @@
     </row>
     <row r="151" spans="1:12">
       <c r="A151" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="B151" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="C151" s="21" t="s">
-        <v>191</v>
+        <v>124</v>
       </c>
       <c r="E151" s="22">
         <f>IF(D151="?OLD","!!!","")</f>
@@ -7373,7 +7353,7 @@
     </row>
     <row r="152" spans="1:12">
       <c r="A152" s="20" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E152" s="22">
         <f>IF(D152="?OLD","!!!","")</f>
@@ -7407,7 +7387,13 @@
     </row>
     <row r="153" spans="1:12">
       <c r="A153" s="20" t="s">
-        <v>153</v>
+        <v>224</v>
+      </c>
+      <c r="B153" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="C153" s="21" t="s">
+        <v>196</v>
       </c>
       <c r="E153" s="22">
         <f>IF(D153="?OLD","!!!","")</f>
@@ -7441,16 +7427,7 @@
     </row>
     <row r="154" spans="1:12">
       <c r="A154" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="B154" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C154" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D154" s="21" t="s">
-        <v>108</v>
+        <v>225</v>
       </c>
       <c r="E154" s="22">
         <f>IF(D154="?OLD","!!!","")</f>
@@ -7484,7 +7461,7 @@
     </row>
     <row r="155" spans="1:12">
       <c r="A155" s="20" t="s">
-        <v>192</v>
+        <v>158</v>
       </c>
       <c r="E155" s="22">
         <f>IF(D155="?OLD","!!!","")</f>
@@ -7518,7 +7495,16 @@
     </row>
     <row r="156" spans="1:12">
       <c r="A156" s="20" t="s">
-        <v>222</v>
+        <v>226</v>
+      </c>
+      <c r="B156" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C156" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D156" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E156" s="22">
         <f>IF(D156="?OLD","!!!","")</f>
@@ -7552,7 +7538,7 @@
     </row>
     <row r="157" spans="1:12">
       <c r="A157" s="20" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="E157" s="22">
         <f>IF(D157="?OLD","!!!","")</f>
@@ -7585,93 +7571,84 @@
       <c r="L157" s="27"/>
     </row>
     <row r="158" spans="1:12">
-      <c r="A158" s="20"/>
+      <c r="A158" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="E158" s="22">
+        <f>IF(D158="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F158" s="23" t="str">
+        <f>IF(OR(E158="",E158="!!!"),"",IF(NOT(ISNA(VLOOKUP(E158,E$1:E157,1,FALSE()))),"OLD",IF(AND(E158&lt;&gt;"",E158&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G158" s="24" t="str">
+        <f>IF(OR(E158="",E158="!!!"),"",IF(OR(J158=0,AND(J158=1,K158=1),AND(J158=1,I158="SBJ"),AND(J158=1,I158=0)),"?IN_FOCUS",IF(J158&lt;=2,"?ACTIVATED",IF(J158&lt;&gt;"","?FAMILIAR",IF(F158="NEW",IF(ISNA(VLOOKUP(E158,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H158" s="25" t="str">
+        <f>IF(J158&lt;&gt;1,"",IF(I158="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I158" s="26" t="str">
+        <f>IF(OR(E158="",E158="!!!",F158="NEW"),"",INDEX(B157:B$2,-1+SUMPRODUCT(MAX(ROW(E157:E$2)*(E158=E157:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J158" s="26" t="str">
+        <f>IF(OR(E158="",E158="!!!",F158="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E158)*(E158=E$2:E158)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E157)*(E2=E$1:E157))))))</f>
+        <v> </v>
+      </c>
+      <c r="K158" s="26" t="str">
+        <f>IF(OR(E158="",E158="!!!",F158="NEW"),"",INDEX(J$1:J157,SUMPRODUCT(MAX(ROW(E$1:E157)*(E158=E$1:E157)))))</f>
+        <v> </v>
+      </c>
+      <c r="L158" s="27"/>
     </row>
     <row r="159" spans="1:12">
       <c r="A159" s="20" t="s">
-        <v>223</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="E159" s="22">
+        <f>IF(D159="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F159" s="23" t="str">
+        <f>IF(OR(E159="",E159="!!!"),"",IF(NOT(ISNA(VLOOKUP(E159,E$1:E158,1,FALSE()))),"OLD",IF(AND(E159&lt;&gt;"",E159&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G159" s="24" t="str">
+        <f>IF(OR(E159="",E159="!!!"),"",IF(OR(J159=0,AND(J159=1,K159=1),AND(J159=1,I159="SBJ"),AND(J159=1,I159=0)),"?IN_FOCUS",IF(J159&lt;=2,"?ACTIVATED",IF(J159&lt;&gt;"","?FAMILIAR",IF(F159="NEW",IF(ISNA(VLOOKUP(E159,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H159" s="25" t="str">
+        <f>IF(J159&lt;&gt;1,"",IF(I159="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I159" s="26" t="str">
+        <f>IF(OR(E159="",E159="!!!",F159="NEW"),"",INDEX(B158:B$2,-1+SUMPRODUCT(MAX(ROW(E158:E$2)*(E159=E158:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J159" s="26" t="str">
+        <f>IF(OR(E159="",E159="!!!",F159="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E159)*(E159=E$2:E159)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E158)*(E2=E$1:E158))))))</f>
+        <v> </v>
+      </c>
+      <c r="K159" s="26" t="str">
+        <f>IF(OR(E159="",E159="!!!",F159="NEW"),"",INDEX(J$1:J158,SUMPRODUCT(MAX(ROW(E$1:E158)*(E159=E$1:E158)))))</f>
+        <v> </v>
+      </c>
+      <c r="L159" s="27"/>
     </row>
     <row r="160" spans="1:12">
-      <c r="A160" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="E160" s="22">
-        <f>IF(D160="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F160" s="23" t="str">
-        <f>IF(OR(E160="",E160="!!!"),"",IF(NOT(ISNA(VLOOKUP(E160,E$1:E159,1,FALSE()))),"OLD",IF(AND(E160&lt;&gt;"",E160&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G160" s="24" t="str">
-        <f>IF(OR(E160="",E160="!!!"),"",IF(OR(J160=0,AND(J160=1,K160=1),AND(J160=1,I160="SBJ"),AND(J160=1,I160=0)),"?IN_FOCUS",IF(J160&lt;=2,"?ACTIVATED",IF(J160&lt;&gt;"","?FAMILIAR",IF(F160="NEW",IF(ISNA(VLOOKUP(E160,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H160" s="25" t="str">
-        <f>IF(J160&lt;&gt;1,"",IF(I160="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I160" s="26" t="str">
-        <f>IF(OR(E160="",E160="!!!",F160="NEW"),"",INDEX(B159:B$2,-1+SUMPRODUCT(MAX(ROW(E159:E$2)*(E160=E159:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J160" s="26" t="str">
-        <f>IF(OR(E160="",E160="!!!",F160="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E160)*(E160=E$2:E160)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E159)*(E2=E$1:E159))))))</f>
-        <v> </v>
-      </c>
-      <c r="K160" s="26" t="str">
-        <f>IF(OR(E160="",E160="!!!",F160="NEW"),"",INDEX(J$1:J159,SUMPRODUCT(MAX(ROW(E$1:E159)*(E160=E$1:E159)))))</f>
-        <v> </v>
-      </c>
-      <c r="L160" s="27"/>
+      <c r="A160" s="20"/>
     </row>
     <row r="161" spans="1:12">
       <c r="A161" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="B161" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="C161" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D161" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="E161" s="22">
-        <f>IF(D161="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F161" s="23" t="str">
-        <f>IF(OR(E161="",E161="!!!"),"",IF(NOT(ISNA(VLOOKUP(E161,E$1:E160,1,FALSE()))),"OLD",IF(AND(E161&lt;&gt;"",E161&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G161" s="24" t="str">
-        <f>IF(OR(E161="",E161="!!!"),"",IF(OR(J161=0,AND(J161=1,K161=1),AND(J161=1,I161="SBJ"),AND(J161=1,I161=0)),"?IN_FOCUS",IF(J161&lt;=2,"?ACTIVATED",IF(J161&lt;&gt;"","?FAMILIAR",IF(F161="NEW",IF(ISNA(VLOOKUP(E161,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H161" s="25" t="str">
-        <f>IF(J161&lt;&gt;1,"",IF(I161="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I161" s="26" t="str">
-        <f>IF(OR(E161="",E161="!!!",F161="NEW"),"",INDEX(B160:B$2,-1+SUMPRODUCT(MAX(ROW(E160:E$2)*(E161=E160:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J161" s="26" t="str">
-        <f>IF(OR(E161="",E161="!!!",F161="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E161)*(E161=E$2:E161)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E160)*(E2=E$1:E160))))))</f>
-        <v> </v>
-      </c>
-      <c r="K161" s="26" t="str">
-        <f>IF(OR(E161="",E161="!!!",F161="NEW"),"",INDEX(J$1:J160,SUMPRODUCT(MAX(ROW(E$1:E160)*(E161=E$1:E160)))))</f>
-        <v> </v>
-      </c>
-      <c r="L161" s="27"/>
+        <v>228</v>
+      </c>
     </row>
     <row r="162" spans="1:12">
       <c r="A162" s="20" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="E162" s="22">
         <f>IF(D162="?OLD","!!!","")</f>
@@ -7705,7 +7682,16 @@
     </row>
     <row r="163" spans="1:12">
       <c r="A163" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B163" s="21" t="s">
         <v>110</v>
+      </c>
+      <c r="C163" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D163" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E163" s="22">
         <f>IF(D163="?OLD","!!!","")</f>
@@ -7739,7 +7725,7 @@
     </row>
     <row r="164" spans="1:12">
       <c r="A164" s="20" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E164" s="22">
         <f>IF(D164="?OLD","!!!","")</f>
@@ -7773,7 +7759,7 @@
     </row>
     <row r="165" spans="1:12">
       <c r="A165" s="20" t="s">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="E165" s="22">
         <f>IF(D165="?OLD","!!!","")</f>
@@ -7807,7 +7793,7 @@
     </row>
     <row r="166" spans="1:12">
       <c r="A166" s="20" t="s">
-        <v>224</v>
+        <v>115</v>
       </c>
       <c r="E166" s="22">
         <f>IF(D166="?OLD","!!!","")</f>
@@ -7841,7 +7827,7 @@
     </row>
     <row r="167" spans="1:12">
       <c r="A167" s="20" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="E167" s="22">
         <f>IF(D167="?OLD","!!!","")</f>
@@ -7875,13 +7861,7 @@
     </row>
     <row r="168" spans="1:12">
       <c r="A168" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="B168" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="C168" s="21" t="s">
-        <v>191</v>
+        <v>229</v>
       </c>
       <c r="E168" s="22">
         <f>IF(D168="?OLD","!!!","")</f>
@@ -7915,7 +7895,7 @@
     </row>
     <row r="169" spans="1:12">
       <c r="A169" s="20" t="s">
-        <v>220</v>
+        <v>116</v>
       </c>
       <c r="E169" s="22">
         <f>IF(D169="?OLD","!!!","")</f>
@@ -7949,16 +7929,13 @@
     </row>
     <row r="170" spans="1:12">
       <c r="A170" s="20" t="s">
-        <v>225</v>
+        <v>117</v>
       </c>
       <c r="B170" s="21" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="C170" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D170" s="21" t="s">
-        <v>108</v>
+        <v>196</v>
       </c>
       <c r="E170" s="22">
         <f>IF(D170="?OLD","!!!","")</f>
@@ -7992,7 +7969,7 @@
     </row>
     <row r="171" spans="1:12">
       <c r="A171" s="20" t="s">
-        <v>13</v>
+        <v>225</v>
       </c>
       <c r="E171" s="22">
         <f>IF(D171="?OLD","!!!","")</f>
@@ -8026,7 +8003,16 @@
     </row>
     <row r="172" spans="1:12">
       <c r="A172" s="20" t="s">
-        <v>142</v>
+        <v>230</v>
+      </c>
+      <c r="B172" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C172" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D172" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E172" s="22">
         <f>IF(D172="?OLD","!!!","")</f>
@@ -8060,7 +8046,7 @@
     </row>
     <row r="173" spans="1:12">
       <c r="A173" s="20" t="s">
-        <v>150</v>
+        <v>13</v>
       </c>
       <c r="E173" s="22">
         <f>IF(D173="?OLD","!!!","")</f>
@@ -8094,7 +8080,7 @@
     </row>
     <row r="174" spans="1:12">
       <c r="A174" s="20" t="s">
-        <v>226</v>
+        <v>146</v>
       </c>
       <c r="E174" s="22">
         <f>IF(D174="?OLD","!!!","")</f>
@@ -8128,7 +8114,7 @@
     </row>
     <row r="175" spans="1:12">
       <c r="A175" s="20" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="E175" s="22">
         <f>IF(D175="?OLD","!!!","")</f>
@@ -8162,7 +8148,7 @@
     </row>
     <row r="176" spans="1:12">
       <c r="A176" s="20" t="s">
-        <v>119</v>
+        <v>231</v>
       </c>
       <c r="E176" s="22">
         <f>IF(D176="?OLD","!!!","")</f>
@@ -8196,7 +8182,7 @@
     </row>
     <row r="177" spans="1:12">
       <c r="A177" s="20" t="s">
-        <v>227</v>
+        <v>145</v>
       </c>
       <c r="E177" s="22">
         <f>IF(D177="?OLD","!!!","")</f>
@@ -8230,7 +8216,7 @@
     </row>
     <row r="178" spans="1:12">
       <c r="A178" s="20" t="s">
-        <v>64</v>
+        <v>123</v>
       </c>
       <c r="E178" s="22">
         <f>IF(D178="?OLD","!!!","")</f>
@@ -8264,7 +8250,7 @@
     </row>
     <row r="179" spans="1:12">
       <c r="A179" s="20" t="s">
-        <v>138</v>
+        <v>232</v>
       </c>
       <c r="E179" s="22">
         <f>IF(D179="?OLD","!!!","")</f>
@@ -8297,93 +8283,84 @@
       <c r="L179" s="27"/>
     </row>
     <row r="180" spans="1:12">
-      <c r="A180" s="20"/>
+      <c r="A180" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E180" s="22">
+        <f>IF(D180="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F180" s="23" t="str">
+        <f>IF(OR(E180="",E180="!!!"),"",IF(NOT(ISNA(VLOOKUP(E180,E$1:E179,1,FALSE()))),"OLD",IF(AND(E180&lt;&gt;"",E180&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G180" s="24" t="str">
+        <f>IF(OR(E180="",E180="!!!"),"",IF(OR(J180=0,AND(J180=1,K180=1),AND(J180=1,I180="SBJ"),AND(J180=1,I180=0)),"?IN_FOCUS",IF(J180&lt;=2,"?ACTIVATED",IF(J180&lt;&gt;"","?FAMILIAR",IF(F180="NEW",IF(ISNA(VLOOKUP(E180,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H180" s="25" t="str">
+        <f>IF(J180&lt;&gt;1,"",IF(I180="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I180" s="26" t="str">
+        <f>IF(OR(E180="",E180="!!!",F180="NEW"),"",INDEX(B179:B$2,-1+SUMPRODUCT(MAX(ROW(E179:E$2)*(E180=E179:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J180" s="26" t="str">
+        <f>IF(OR(E180="",E180="!!!",F180="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E180)*(E180=E$2:E180)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E179)*(E2=E$1:E179))))))</f>
+        <v> </v>
+      </c>
+      <c r="K180" s="26" t="str">
+        <f>IF(OR(E180="",E180="!!!",F180="NEW"),"",INDEX(J$1:J179,SUMPRODUCT(MAX(ROW(E$1:E179)*(E180=E$1:E179)))))</f>
+        <v> </v>
+      </c>
+      <c r="L180" s="27"/>
     </row>
     <row r="181" spans="1:12">
       <c r="A181" s="20" t="s">
-        <v>228</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="E181" s="22">
+        <f>IF(D181="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F181" s="23" t="str">
+        <f>IF(OR(E181="",E181="!!!"),"",IF(NOT(ISNA(VLOOKUP(E181,E$1:E180,1,FALSE()))),"OLD",IF(AND(E181&lt;&gt;"",E181&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G181" s="24" t="str">
+        <f>IF(OR(E181="",E181="!!!"),"",IF(OR(J181=0,AND(J181=1,K181=1),AND(J181=1,I181="SBJ"),AND(J181=1,I181=0)),"?IN_FOCUS",IF(J181&lt;=2,"?ACTIVATED",IF(J181&lt;&gt;"","?FAMILIAR",IF(F181="NEW",IF(ISNA(VLOOKUP(E181,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H181" s="25" t="str">
+        <f>IF(J181&lt;&gt;1,"",IF(I181="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I181" s="26" t="str">
+        <f>IF(OR(E181="",E181="!!!",F181="NEW"),"",INDEX(B180:B$2,-1+SUMPRODUCT(MAX(ROW(E180:E$2)*(E181=E180:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J181" s="26" t="str">
+        <f>IF(OR(E181="",E181="!!!",F181="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E181)*(E181=E$2:E181)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E180)*(E2=E$1:E180))))))</f>
+        <v> </v>
+      </c>
+      <c r="K181" s="26" t="str">
+        <f>IF(OR(E181="",E181="!!!",F181="NEW"),"",INDEX(J$1:J180,SUMPRODUCT(MAX(ROW(E$1:E180)*(E181=E$1:E180)))))</f>
+        <v> </v>
+      </c>
+      <c r="L181" s="27"/>
     </row>
     <row r="182" spans="1:12">
-      <c r="A182" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="E182" s="22">
-        <f>IF(D182="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F182" s="23" t="str">
-        <f>IF(OR(E182="",E182="!!!"),"",IF(NOT(ISNA(VLOOKUP(E182,E$1:E181,1,FALSE()))),"OLD",IF(AND(E182&lt;&gt;"",E182&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G182" s="24" t="str">
-        <f>IF(OR(E182="",E182="!!!"),"",IF(OR(J182=0,AND(J182=1,K182=1),AND(J182=1,I182="SBJ"),AND(J182=1,I182=0)),"?IN_FOCUS",IF(J182&lt;=2,"?ACTIVATED",IF(J182&lt;&gt;"","?FAMILIAR",IF(F182="NEW",IF(ISNA(VLOOKUP(E182,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H182" s="25" t="str">
-        <f>IF(J182&lt;&gt;1,"",IF(I182="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I182" s="26" t="str">
-        <f>IF(OR(E182="",E182="!!!",F182="NEW"),"",INDEX(B181:B$2,-1+SUMPRODUCT(MAX(ROW(E181:E$2)*(E182=E181:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J182" s="26" t="str">
-        <f>IF(OR(E182="",E182="!!!",F182="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E182)*(E182=E$2:E182)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E181)*(E2=E$1:E181))))))</f>
-        <v> </v>
-      </c>
-      <c r="K182" s="26" t="str">
-        <f>IF(OR(E182="",E182="!!!",F182="NEW"),"",INDEX(J$1:J181,SUMPRODUCT(MAX(ROW(E$1:E181)*(E182=E$1:E181)))))</f>
-        <v> </v>
-      </c>
-      <c r="L182" s="27"/>
+      <c r="A182" s="20"/>
     </row>
     <row r="183" spans="1:12">
       <c r="A183" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="B183" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="C183" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D183" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="E183" s="22">
-        <f>IF(D183="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F183" s="23" t="str">
-        <f>IF(OR(E183="",E183="!!!"),"",IF(NOT(ISNA(VLOOKUP(E183,E$1:E182,1,FALSE()))),"OLD",IF(AND(E183&lt;&gt;"",E183&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G183" s="24" t="str">
-        <f>IF(OR(E183="",E183="!!!"),"",IF(OR(J183=0,AND(J183=1,K183=1),AND(J183=1,I183="SBJ"),AND(J183=1,I183=0)),"?IN_FOCUS",IF(J183&lt;=2,"?ACTIVATED",IF(J183&lt;&gt;"","?FAMILIAR",IF(F183="NEW",IF(ISNA(VLOOKUP(E183,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H183" s="25" t="str">
-        <f>IF(J183&lt;&gt;1,"",IF(I183="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I183" s="26" t="str">
-        <f>IF(OR(E183="",E183="!!!",F183="NEW"),"",INDEX(B182:B$2,-1+SUMPRODUCT(MAX(ROW(E182:E$2)*(E183=E182:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J183" s="26" t="str">
-        <f>IF(OR(E183="",E183="!!!",F183="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E183)*(E183=E$2:E183)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E182)*(E2=E$1:E182))))))</f>
-        <v> </v>
-      </c>
-      <c r="K183" s="26" t="str">
-        <f>IF(OR(E183="",E183="!!!",F183="NEW"),"",INDEX(J$1:J182,SUMPRODUCT(MAX(ROW(E$1:E182)*(E183=E$1:E182)))))</f>
-        <v> </v>
-      </c>
-      <c r="L183" s="27"/>
+        <v>233</v>
+      </c>
     </row>
     <row r="184" spans="1:12">
       <c r="A184" s="20" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="E184" s="22">
         <f>IF(D184="?OLD","!!!","")</f>
@@ -8417,16 +8394,16 @@
     </row>
     <row r="185" spans="1:12">
       <c r="A185" s="20" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B185" s="21" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="C185" s="21" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D185" s="21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E185" s="22">
         <f>IF(D185="?OLD","!!!","")</f>
@@ -8460,7 +8437,7 @@
     </row>
     <row r="186" spans="1:12">
       <c r="A186" s="20" t="s">
-        <v>64</v>
+        <v>177</v>
       </c>
       <c r="E186" s="22">
         <f>IF(D186="?OLD","!!!","")</f>
@@ -8494,13 +8471,16 @@
     </row>
     <row r="187" spans="1:12">
       <c r="A187" s="20" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B187" s="21" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C187" s="21" t="s">
-        <v>210</v>
+        <v>111</v>
+      </c>
+      <c r="D187" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E187" s="22">
         <f>IF(D187="?OLD","!!!","")</f>
@@ -8534,16 +8514,7 @@
     </row>
     <row r="188" spans="1:12">
       <c r="A188" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="B188" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="C188" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D188" s="21" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="E188" s="22">
         <f>IF(D188="?OLD","!!!","")</f>
@@ -8577,7 +8548,13 @@
     </row>
     <row r="189" spans="1:12">
       <c r="A189" s="20" t="s">
-        <v>233</v>
+        <v>236</v>
+      </c>
+      <c r="B189" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C189" s="21" t="s">
+        <v>215</v>
       </c>
       <c r="E189" s="22">
         <f>IF(D189="?OLD","!!!","")</f>
@@ -8611,7 +8588,16 @@
     </row>
     <row r="190" spans="1:12">
       <c r="A190" s="20" t="s">
-        <v>150</v>
+        <v>237</v>
+      </c>
+      <c r="B190" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="C190" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D190" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E190" s="22">
         <f>IF(D190="?OLD","!!!","")</f>
@@ -8645,7 +8631,7 @@
     </row>
     <row r="191" spans="1:12">
       <c r="A191" s="20" t="s">
-        <v>130</v>
+        <v>238</v>
       </c>
       <c r="E191" s="22">
         <f>IF(D191="?OLD","!!!","")</f>
@@ -8679,7 +8665,7 @@
     </row>
     <row r="192" spans="1:12">
       <c r="A192" s="20" t="s">
-        <v>234</v>
+        <v>155</v>
       </c>
       <c r="E192" s="22">
         <f>IF(D192="?OLD","!!!","")</f>
@@ -8713,16 +8699,7 @@
     </row>
     <row r="193" spans="1:12">
       <c r="A193" s="20" t="s">
-        <v>235</v>
-      </c>
-      <c r="B193" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C193" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D193" s="21" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="E193" s="22">
         <f>IF(D193="?OLD","!!!","")</f>
@@ -8756,7 +8733,7 @@
     </row>
     <row r="194" spans="1:12">
       <c r="A194" s="20" t="s">
-        <v>172</v>
+        <v>239</v>
       </c>
       <c r="E194" s="22">
         <f>IF(D194="?OLD","!!!","")</f>
@@ -8790,7 +8767,16 @@
     </row>
     <row r="195" spans="1:12">
       <c r="A195" s="20" t="s">
-        <v>152</v>
+        <v>240</v>
+      </c>
+      <c r="B195" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C195" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D195" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E195" s="22">
         <f>IF(D195="?OLD","!!!","")</f>
@@ -8824,16 +8810,7 @@
     </row>
     <row r="196" spans="1:12">
       <c r="A196" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="B196" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C196" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D196" s="21" t="s">
-        <v>108</v>
+        <v>177</v>
       </c>
       <c r="E196" s="22">
         <f>IF(D196="?OLD","!!!","")</f>
@@ -8867,13 +8844,7 @@
     </row>
     <row r="197" spans="1:12">
       <c r="A197" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="B197" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C197" s="21" t="s">
-        <v>210</v>
+        <v>157</v>
       </c>
       <c r="E197" s="22">
         <f>IF(D197="?OLD","!!!","")</f>
@@ -8907,16 +8878,16 @@
     </row>
     <row r="198" spans="1:12">
       <c r="A198" s="20" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B198" s="21" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="C198" s="21" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="D198" s="21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E198" s="22">
         <f>IF(D198="?OLD","!!!","")</f>
@@ -8950,7 +8921,13 @@
     </row>
     <row r="199" spans="1:12">
       <c r="A199" s="20" t="s">
-        <v>49</v>
+        <v>197</v>
+      </c>
+      <c r="B199" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C199" s="21" t="s">
+        <v>215</v>
       </c>
       <c r="E199" s="22">
         <f>IF(D199="?OLD","!!!","")</f>
@@ -8984,7 +8961,16 @@
     </row>
     <row r="200" spans="1:12">
       <c r="A200" s="20" t="s">
-        <v>138</v>
+        <v>242</v>
+      </c>
+      <c r="B200" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C200" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D200" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E200" s="22">
         <f>IF(D200="?OLD","!!!","")</f>
@@ -9017,102 +9003,84 @@
       <c r="L200" s="27"/>
     </row>
     <row r="201" spans="1:12">
-      <c r="A201" s="20"/>
+      <c r="A201" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E201" s="22">
+        <f>IF(D201="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F201" s="23" t="str">
+        <f>IF(OR(E201="",E201="!!!"),"",IF(NOT(ISNA(VLOOKUP(E201,E$1:E200,1,FALSE()))),"OLD",IF(AND(E201&lt;&gt;"",E201&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G201" s="24" t="str">
+        <f>IF(OR(E201="",E201="!!!"),"",IF(OR(J201=0,AND(J201=1,K201=1),AND(J201=1,I201="SBJ"),AND(J201=1,I201=0)),"?IN_FOCUS",IF(J201&lt;=2,"?ACTIVATED",IF(J201&lt;&gt;"","?FAMILIAR",IF(F201="NEW",IF(ISNA(VLOOKUP(E201,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H201" s="25" t="str">
+        <f>IF(J201&lt;&gt;1,"",IF(I201="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I201" s="26" t="str">
+        <f>IF(OR(E201="",E201="!!!",F201="NEW"),"",INDEX(B200:B$2,-1+SUMPRODUCT(MAX(ROW(E200:E$2)*(E201=E200:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J201" s="26" t="str">
+        <f>IF(OR(E201="",E201="!!!",F201="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E201)*(E201=E$2:E201)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E200)*(E2=E$1:E200))))))</f>
+        <v> </v>
+      </c>
+      <c r="K201" s="26" t="str">
+        <f>IF(OR(E201="",E201="!!!",F201="NEW"),"",INDEX(J$1:J200,SUMPRODUCT(MAX(ROW(E$1:E200)*(E201=E$1:E200)))))</f>
+        <v> </v>
+      </c>
+      <c r="L201" s="27"/>
     </row>
     <row r="202" spans="1:12">
       <c r="A202" s="20" t="s">
-        <v>238</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="E202" s="22">
+        <f>IF(D202="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F202" s="23" t="str">
+        <f>IF(OR(E202="",E202="!!!"),"",IF(NOT(ISNA(VLOOKUP(E202,E$1:E201,1,FALSE()))),"OLD",IF(AND(E202&lt;&gt;"",E202&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G202" s="24" t="str">
+        <f>IF(OR(E202="",E202="!!!"),"",IF(OR(J202=0,AND(J202=1,K202=1),AND(J202=1,I202="SBJ"),AND(J202=1,I202=0)),"?IN_FOCUS",IF(J202&lt;=2,"?ACTIVATED",IF(J202&lt;&gt;"","?FAMILIAR",IF(F202="NEW",IF(ISNA(VLOOKUP(E202,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H202" s="25" t="str">
+        <f>IF(J202&lt;&gt;1,"",IF(I202="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I202" s="26" t="str">
+        <f>IF(OR(E202="",E202="!!!",F202="NEW"),"",INDEX(B201:B$2,-1+SUMPRODUCT(MAX(ROW(E201:E$2)*(E202=E201:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J202" s="26" t="str">
+        <f>IF(OR(E202="",E202="!!!",F202="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E202)*(E202=E$2:E202)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E201)*(E2=E$1:E201))))))</f>
+        <v> </v>
+      </c>
+      <c r="K202" s="26" t="str">
+        <f>IF(OR(E202="",E202="!!!",F202="NEW"),"",INDEX(J$1:J201,SUMPRODUCT(MAX(ROW(E$1:E201)*(E202=E$1:E201)))))</f>
+        <v> </v>
+      </c>
+      <c r="L202" s="27"/>
     </row>
     <row r="203" spans="1:12">
-      <c r="A203" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="E203" s="22">
-        <f>IF(D203="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F203" s="23" t="str">
-        <f>IF(OR(E203="",E203="!!!"),"",IF(NOT(ISNA(VLOOKUP(E203,E$1:E202,1,FALSE()))),"OLD",IF(AND(E203&lt;&gt;"",E203&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G203" s="24" t="str">
-        <f>IF(OR(E203="",E203="!!!"),"",IF(OR(J203=0,AND(J203=1,K203=1),AND(J203=1,I203="SBJ"),AND(J203=1,I203=0)),"?IN_FOCUS",IF(J203&lt;=2,"?ACTIVATED",IF(J203&lt;&gt;"","?FAMILIAR",IF(F203="NEW",IF(ISNA(VLOOKUP(E203,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H203" s="25" t="str">
-        <f>IF(J203&lt;&gt;1,"",IF(I203="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I203" s="26" t="str">
-        <f>IF(OR(E203="",E203="!!!",F203="NEW"),"",INDEX(B202:B$2,-1+SUMPRODUCT(MAX(ROW(E202:E$2)*(E203=E202:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J203" s="26" t="str">
-        <f>IF(OR(E203="",E203="!!!",F203="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E203)*(E203=E$2:E203)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E202)*(E2=E$1:E202))))))</f>
-        <v> </v>
-      </c>
-      <c r="K203" s="26" t="str">
-        <f>IF(OR(E203="",E203="!!!",F203="NEW"),"",INDEX(J$1:J202,SUMPRODUCT(MAX(ROW(E$1:E202)*(E203=E$1:E202)))))</f>
-        <v> </v>
-      </c>
-      <c r="L203" s="27"/>
+      <c r="A203" s="20"/>
     </row>
     <row r="204" spans="1:12">
       <c r="A204" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="B204" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="C204" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D204" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="E204" s="22">
-        <f>IF(D204="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F204" s="23" t="str">
-        <f>IF(OR(E204="",E204="!!!"),"",IF(NOT(ISNA(VLOOKUP(E204,E$1:E203,1,FALSE()))),"OLD",IF(AND(E204&lt;&gt;"",E204&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G204" s="24" t="str">
-        <f>IF(OR(E204="",E204="!!!"),"",IF(OR(J204=0,AND(J204=1,K204=1),AND(J204=1,I204="SBJ"),AND(J204=1,I204=0)),"?IN_FOCUS",IF(J204&lt;=2,"?ACTIVATED",IF(J204&lt;&gt;"","?FAMILIAR",IF(F204="NEW",IF(ISNA(VLOOKUP(E204,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H204" s="25" t="str">
-        <f>IF(J204&lt;&gt;1,"",IF(I204="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I204" s="26" t="str">
-        <f>IF(OR(E204="",E204="!!!",F204="NEW"),"",INDEX(B203:B$2,-1+SUMPRODUCT(MAX(ROW(E203:E$2)*(E204=E203:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J204" s="26" t="str">
-        <f>IF(OR(E204="",E204="!!!",F204="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E204)*(E204=E$2:E204)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E203)*(E2=E$1:E203))))))</f>
-        <v> </v>
-      </c>
-      <c r="K204" s="26" t="str">
-        <f>IF(OR(E204="",E204="!!!",F204="NEW"),"",INDEX(J$1:J203,SUMPRODUCT(MAX(ROW(E$1:E203)*(E204=E$1:E203)))))</f>
-        <v> </v>
-      </c>
-      <c r="L204" s="27"/>
+        <v>243</v>
+      </c>
     </row>
     <row r="205" spans="1:12">
       <c r="A205" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="B205" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C205" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D205" s="21" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="E205" s="22">
         <f>IF(D205="?OLD","!!!","")</f>
@@ -9146,7 +9114,16 @@
     </row>
     <row r="206" spans="1:12">
       <c r="A206" s="20" t="s">
-        <v>109</v>
+        <v>127</v>
+      </c>
+      <c r="B206" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C206" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D206" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E206" s="22">
         <f>IF(D206="?OLD","!!!","")</f>
@@ -9180,7 +9157,16 @@
     </row>
     <row r="207" spans="1:12">
       <c r="A207" s="20" t="s">
-        <v>140</v>
+        <v>244</v>
+      </c>
+      <c r="B207" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C207" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D207" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E207" s="22">
         <f>IF(D207="?OLD","!!!","")</f>
@@ -9214,7 +9200,7 @@
     </row>
     <row r="208" spans="1:12">
       <c r="A208" s="20" t="s">
-        <v>240</v>
+        <v>113</v>
       </c>
       <c r="E208" s="22">
         <f>IF(D208="?OLD","!!!","")</f>
@@ -9248,7 +9234,7 @@
     </row>
     <row r="209" spans="1:12">
       <c r="A209" s="20" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="E209" s="22">
         <f>IF(D209="?OLD","!!!","")</f>
@@ -9282,13 +9268,7 @@
     </row>
     <row r="210" spans="1:12">
       <c r="A210" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="B210" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C210" s="21" t="s">
-        <v>191</v>
+        <v>245</v>
       </c>
       <c r="E210" s="22">
         <f>IF(D210="?OLD","!!!","")</f>
@@ -9322,7 +9302,7 @@
     </row>
     <row r="211" spans="1:12">
       <c r="A211" s="20" t="s">
-        <v>220</v>
+        <v>116</v>
       </c>
       <c r="E211" s="22">
         <f>IF(D211="?OLD","!!!","")</f>
@@ -9356,7 +9336,13 @@
     </row>
     <row r="212" spans="1:12">
       <c r="A212" s="20" t="s">
-        <v>130</v>
+        <v>117</v>
+      </c>
+      <c r="B212" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C212" s="21" t="s">
+        <v>196</v>
       </c>
       <c r="E212" s="22">
         <f>IF(D212="?OLD","!!!","")</f>
@@ -9390,16 +9376,7 @@
     </row>
     <row r="213" spans="1:12">
       <c r="A213" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="B213" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="C213" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D213" s="21" t="s">
-        <v>108</v>
+        <v>225</v>
       </c>
       <c r="E213" s="22">
         <f>IF(D213="?OLD","!!!","")</f>
@@ -9433,16 +9410,7 @@
     </row>
     <row r="214" spans="1:12">
       <c r="A214" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="B214" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C214" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D214" s="21" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="E214" s="22">
         <f>IF(D214="?OLD","!!!","")</f>
@@ -9476,7 +9444,16 @@
     </row>
     <row r="215" spans="1:12">
       <c r="A215" s="20" t="s">
-        <v>172</v>
+        <v>246</v>
+      </c>
+      <c r="B215" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C215" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D215" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E215" s="22">
         <f>IF(D215="?OLD","!!!","")</f>
@@ -9510,16 +9487,16 @@
     </row>
     <row r="216" spans="1:12">
       <c r="A216" s="20" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B216" s="21" t="s">
         <v>118</v>
       </c>
       <c r="C216" s="21" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D216" s="21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E216" s="22">
         <f>IF(D216="?OLD","!!!","")</f>
@@ -9553,7 +9530,7 @@
     </row>
     <row r="217" spans="1:12">
       <c r="A217" s="20" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="E217" s="22">
         <f>IF(D217="?OLD","!!!","")</f>
@@ -9587,7 +9564,16 @@
     </row>
     <row r="218" spans="1:12">
       <c r="A218" s="20" t="s">
-        <v>138</v>
+        <v>248</v>
+      </c>
+      <c r="B218" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="C218" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D218" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E218" s="22">
         <f>IF(D218="?OLD","!!!","")</f>
@@ -9620,93 +9606,84 @@
       <c r="L218" s="27"/>
     </row>
     <row r="219" spans="1:12">
-      <c r="A219" s="20"/>
+      <c r="A219" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="E219" s="22">
+        <f>IF(D219="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F219" s="23" t="str">
+        <f>IF(OR(E219="",E219="!!!"),"",IF(NOT(ISNA(VLOOKUP(E219,E$1:E218,1,FALSE()))),"OLD",IF(AND(E219&lt;&gt;"",E219&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G219" s="24" t="str">
+        <f>IF(OR(E219="",E219="!!!"),"",IF(OR(J219=0,AND(J219=1,K219=1),AND(J219=1,I219="SBJ"),AND(J219=1,I219=0)),"?IN_FOCUS",IF(J219&lt;=2,"?ACTIVATED",IF(J219&lt;&gt;"","?FAMILIAR",IF(F219="NEW",IF(ISNA(VLOOKUP(E219,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H219" s="25" t="str">
+        <f>IF(J219&lt;&gt;1,"",IF(I219="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I219" s="26" t="str">
+        <f>IF(OR(E219="",E219="!!!",F219="NEW"),"",INDEX(B218:B$2,-1+SUMPRODUCT(MAX(ROW(E218:E$2)*(E219=E218:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J219" s="26" t="str">
+        <f>IF(OR(E219="",E219="!!!",F219="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E219)*(E219=E$2:E219)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E218)*(E2=E$1:E218))))))</f>
+        <v> </v>
+      </c>
+      <c r="K219" s="26" t="str">
+        <f>IF(OR(E219="",E219="!!!",F219="NEW"),"",INDEX(J$1:J218,SUMPRODUCT(MAX(ROW(E$1:E218)*(E219=E$1:E218)))))</f>
+        <v> </v>
+      </c>
+      <c r="L219" s="27"/>
     </row>
     <row r="220" spans="1:12">
       <c r="A220" s="20" t="s">
-        <v>244</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="E220" s="22">
+        <f>IF(D220="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F220" s="23" t="str">
+        <f>IF(OR(E220="",E220="!!!"),"",IF(NOT(ISNA(VLOOKUP(E220,E$1:E219,1,FALSE()))),"OLD",IF(AND(E220&lt;&gt;"",E220&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G220" s="24" t="str">
+        <f>IF(OR(E220="",E220="!!!"),"",IF(OR(J220=0,AND(J220=1,K220=1),AND(J220=1,I220="SBJ"),AND(J220=1,I220=0)),"?IN_FOCUS",IF(J220&lt;=2,"?ACTIVATED",IF(J220&lt;&gt;"","?FAMILIAR",IF(F220="NEW",IF(ISNA(VLOOKUP(E220,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H220" s="25" t="str">
+        <f>IF(J220&lt;&gt;1,"",IF(I220="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I220" s="26" t="str">
+        <f>IF(OR(E220="",E220="!!!",F220="NEW"),"",INDEX(B219:B$2,-1+SUMPRODUCT(MAX(ROW(E219:E$2)*(E220=E219:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J220" s="26" t="str">
+        <f>IF(OR(E220="",E220="!!!",F220="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E220)*(E220=E$2:E220)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E219)*(E2=E$1:E219))))))</f>
+        <v> </v>
+      </c>
+      <c r="K220" s="26" t="str">
+        <f>IF(OR(E220="",E220="!!!",F220="NEW"),"",INDEX(J$1:J219,SUMPRODUCT(MAX(ROW(E$1:E219)*(E220=E$1:E219)))))</f>
+        <v> </v>
+      </c>
+      <c r="L220" s="27"/>
     </row>
     <row r="221" spans="1:12">
-      <c r="A221" s="20" t="s">
-        <v>245</v>
-      </c>
-      <c r="E221" s="22">
-        <f>IF(D221="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F221" s="23" t="str">
-        <f>IF(OR(E221="",E221="!!!"),"",IF(NOT(ISNA(VLOOKUP(E221,E$1:E220,1,FALSE()))),"OLD",IF(AND(E221&lt;&gt;"",E221&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G221" s="24" t="str">
-        <f>IF(OR(E221="",E221="!!!"),"",IF(OR(J221=0,AND(J221=1,K221=1),AND(J221=1,I221="SBJ"),AND(J221=1,I221=0)),"?IN_FOCUS",IF(J221&lt;=2,"?ACTIVATED",IF(J221&lt;&gt;"","?FAMILIAR",IF(F221="NEW",IF(ISNA(VLOOKUP(E221,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H221" s="25" t="str">
-        <f>IF(J221&lt;&gt;1,"",IF(I221="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I221" s="26" t="str">
-        <f>IF(OR(E221="",E221="!!!",F221="NEW"),"",INDEX(B220:B$2,-1+SUMPRODUCT(MAX(ROW(E220:E$2)*(E221=E220:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J221" s="26" t="str">
-        <f>IF(OR(E221="",E221="!!!",F221="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E221)*(E221=E$2:E221)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E220)*(E2=E$1:E220))))))</f>
-        <v> </v>
-      </c>
-      <c r="K221" s="26" t="str">
-        <f>IF(OR(E221="",E221="!!!",F221="NEW"),"",INDEX(J$1:J220,SUMPRODUCT(MAX(ROW(E$1:E220)*(E221=E$1:E220)))))</f>
-        <v> </v>
-      </c>
-      <c r="L221" s="27"/>
+      <c r="A221" s="20"/>
     </row>
     <row r="222" spans="1:12">
       <c r="A222" s="20" t="s">
-        <v>246</v>
-      </c>
-      <c r="E222" s="22">
-        <f>IF(D222="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F222" s="23" t="str">
-        <f>IF(OR(E222="",E222="!!!"),"",IF(NOT(ISNA(VLOOKUP(E222,E$1:E221,1,FALSE()))),"OLD",IF(AND(E222&lt;&gt;"",E222&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G222" s="24" t="str">
-        <f>IF(OR(E222="",E222="!!!"),"",IF(OR(J222=0,AND(J222=1,K222=1),AND(J222=1,I222="SBJ"),AND(J222=1,I222=0)),"?IN_FOCUS",IF(J222&lt;=2,"?ACTIVATED",IF(J222&lt;&gt;"","?FAMILIAR",IF(F222="NEW",IF(ISNA(VLOOKUP(E222,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H222" s="25" t="str">
-        <f>IF(J222&lt;&gt;1,"",IF(I222="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I222" s="26" t="str">
-        <f>IF(OR(E222="",E222="!!!",F222="NEW"),"",INDEX(B221:B$2,-1+SUMPRODUCT(MAX(ROW(E221:E$2)*(E222=E221:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J222" s="26" t="str">
-        <f>IF(OR(E222="",E222="!!!",F222="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E222)*(E222=E$2:E222)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E221)*(E2=E$1:E221))))))</f>
-        <v> </v>
-      </c>
-      <c r="K222" s="26" t="str">
-        <f>IF(OR(E222="",E222="!!!",F222="NEW"),"",INDEX(J$1:J221,SUMPRODUCT(MAX(ROW(E$1:E221)*(E222=E$1:E221)))))</f>
-        <v> </v>
-      </c>
-      <c r="L222" s="27"/>
+        <v>249</v>
+      </c>
     </row>
     <row r="223" spans="1:12">
       <c r="A223" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="B223" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C223" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="D223" s="21" t="s">
-        <v>108</v>
+        <v>250</v>
       </c>
       <c r="E223" s="22">
         <f>IF(D223="?OLD","!!!","")</f>
@@ -9740,7 +9717,7 @@
     </row>
     <row r="224" spans="1:12">
       <c r="A224" s="20" t="s">
-        <v>150</v>
+        <v>251</v>
       </c>
       <c r="E224" s="22">
         <f>IF(D224="?OLD","!!!","")</f>
@@ -9774,7 +9751,16 @@
     </row>
     <row r="225" spans="1:12">
       <c r="A225" s="20" t="s">
-        <v>247</v>
+        <v>193</v>
+      </c>
+      <c r="B225" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C225" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="D225" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E225" s="22">
         <f>IF(D225="?OLD","!!!","")</f>
@@ -9808,13 +9794,7 @@
     </row>
     <row r="226" spans="1:12">
       <c r="A226" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="B226" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="C226" s="21" t="s">
-        <v>191</v>
+        <v>155</v>
       </c>
       <c r="E226" s="22">
         <f>IF(D226="?OLD","!!!","")</f>
@@ -9848,7 +9828,7 @@
     </row>
     <row r="227" spans="1:12">
       <c r="A227" s="20" t="s">
-        <v>112</v>
+        <v>252</v>
       </c>
       <c r="E227" s="22">
         <f>IF(D227="?OLD","!!!","")</f>
@@ -9882,7 +9862,13 @@
     </row>
     <row r="228" spans="1:12">
       <c r="A228" s="20" t="s">
-        <v>248</v>
+        <v>224</v>
+      </c>
+      <c r="B228" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C228" s="21" t="s">
+        <v>196</v>
       </c>
       <c r="E228" s="22">
         <f>IF(D228="?OLD","!!!","")</f>
@@ -9916,16 +9902,7 @@
     </row>
     <row r="229" spans="1:12">
       <c r="A229" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="B229" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C229" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D229" s="21" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="E229" s="22">
         <f>IF(D229="?OLD","!!!","")</f>
@@ -9959,7 +9936,7 @@
     </row>
     <row r="230" spans="1:12">
       <c r="A230" s="20" t="s">
-        <v>150</v>
+        <v>253</v>
       </c>
       <c r="E230" s="22">
         <f>IF(D230="?OLD","!!!","")</f>
@@ -9993,10 +9970,16 @@
     </row>
     <row r="231" spans="1:12">
       <c r="A231" s="20" t="s">
-        <v>152</v>
+        <v>254</v>
       </c>
       <c r="B231" s="21" t="s">
-        <v>250</v>
+        <v>118</v>
+      </c>
+      <c r="C231" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D231" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E231" s="22">
         <f>IF(D231="?OLD","!!!","")</f>
@@ -10030,7 +10013,7 @@
     </row>
     <row r="232" spans="1:12">
       <c r="A232" s="20" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="E232" s="22">
         <f>IF(D232="?OLD","!!!","")</f>
@@ -10064,13 +10047,10 @@
     </row>
     <row r="233" spans="1:12">
       <c r="A233" s="20" t="s">
-        <v>251</v>
+        <v>157</v>
       </c>
       <c r="B233" s="21" t="s">
-        <v>252</v>
-      </c>
-      <c r="C233" s="21" t="s">
-        <v>191</v>
+        <v>255</v>
       </c>
       <c r="E233" s="22">
         <f>IF(D233="?OLD","!!!","")</f>
@@ -10104,7 +10084,7 @@
     </row>
     <row r="234" spans="1:12">
       <c r="A234" s="20" t="s">
-        <v>253</v>
+        <v>124</v>
       </c>
       <c r="E234" s="22">
         <f>IF(D234="?OLD","!!!","")</f>
@@ -10138,7 +10118,13 @@
     </row>
     <row r="235" spans="1:12">
       <c r="A235" s="20" t="s">
-        <v>64</v>
+        <v>256</v>
+      </c>
+      <c r="B235" s="21" t="s">
+        <v>257</v>
+      </c>
+      <c r="C235" s="21" t="s">
+        <v>196</v>
       </c>
       <c r="E235" s="22">
         <f>IF(D235="?OLD","!!!","")</f>
@@ -10172,7 +10158,7 @@
     </row>
     <row r="236" spans="1:12">
       <c r="A236" s="20" t="s">
-        <v>12</v>
+        <v>258</v>
       </c>
       <c r="E236" s="22">
         <f>IF(D236="?OLD","!!!","")</f>
@@ -10206,7 +10192,7 @@
     </row>
     <row r="237" spans="1:12">
       <c r="A237" s="20" t="s">
-        <v>254</v>
+        <v>68</v>
       </c>
       <c r="E237" s="22">
         <f>IF(D237="?OLD","!!!","")</f>
@@ -10240,7 +10226,7 @@
     </row>
     <row r="238" spans="1:12">
       <c r="A238" s="20" t="s">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="E238" s="22">
         <f>IF(D238="?OLD","!!!","")</f>
@@ -10274,16 +10260,7 @@
     </row>
     <row r="239" spans="1:12">
       <c r="A239" s="20" t="s">
-        <v>255</v>
-      </c>
-      <c r="B239" s="21" t="s">
-        <v>256</v>
-      </c>
-      <c r="C239" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D239" s="21" t="s">
-        <v>108</v>
+        <v>259</v>
       </c>
       <c r="E239" s="22">
         <f>IF(D239="?OLD","!!!","")</f>
@@ -10317,7 +10294,7 @@
     </row>
     <row r="240" spans="1:12">
       <c r="A240" s="20" t="s">
-        <v>257</v>
+        <v>155</v>
       </c>
       <c r="E240" s="22">
         <f>IF(D240="?OLD","!!!","")</f>
@@ -10351,16 +10328,16 @@
     </row>
     <row r="241" spans="1:12">
       <c r="A241" s="20" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B241" s="21" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C241" s="21" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D241" s="21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E241" s="22">
         <f>IF(D241="?OLD","!!!","")</f>
@@ -10394,7 +10371,7 @@
     </row>
     <row r="242" spans="1:12">
       <c r="A242" s="20" t="s">
-        <v>150</v>
+        <v>262</v>
       </c>
       <c r="E242" s="22">
         <f>IF(D242="?OLD","!!!","")</f>
@@ -10428,16 +10405,16 @@
     </row>
     <row r="243" spans="1:12">
       <c r="A243" s="20" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B243" s="21" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="C243" s="21" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D243" s="21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E243" s="22">
         <f>IF(D243="?OLD","!!!","")</f>
@@ -10471,7 +10448,7 @@
     </row>
     <row r="244" spans="1:12">
       <c r="A244" s="20" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="E244" s="22">
         <f>IF(D244="?OLD","!!!","")</f>
@@ -10505,16 +10482,16 @@
     </row>
     <row r="245" spans="1:12">
       <c r="A245" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="B245" s="21" t="s">
         <v>261</v>
       </c>
-      <c r="B245" s="21" t="s">
-        <v>256</v>
-      </c>
       <c r="C245" s="21" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D245" s="21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E245" s="22">
         <f>IF(D245="?OLD","!!!","")</f>
@@ -10548,7 +10525,7 @@
     </row>
     <row r="246" spans="1:12">
       <c r="A246" s="20" t="s">
-        <v>262</v>
+        <v>177</v>
       </c>
       <c r="E246" s="22">
         <f>IF(D246="?OLD","!!!","")</f>
@@ -10582,16 +10559,16 @@
     </row>
     <row r="247" spans="1:12">
       <c r="A247" s="20" t="s">
-        <v>109</v>
+        <v>266</v>
       </c>
       <c r="B247" s="21" t="s">
-        <v>118</v>
+        <v>261</v>
       </c>
       <c r="C247" s="21" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D247" s="21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E247" s="22">
         <f>IF(D247="?OLD","!!!","")</f>
@@ -10625,7 +10602,7 @@
     </row>
     <row r="248" spans="1:12">
       <c r="A248" s="20" t="s">
-        <v>138</v>
+        <v>267</v>
       </c>
       <c r="E248" s="22">
         <f>IF(D248="?OLD","!!!","")</f>
@@ -10658,93 +10635,102 @@
       <c r="L248" s="27"/>
     </row>
     <row r="249" spans="1:12">
-      <c r="A249" s="20"/>
+      <c r="A249" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="B249" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="C249" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D249" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="E249" s="22">
+        <f>IF(D249="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F249" s="23" t="str">
+        <f>IF(OR(E249="",E249="!!!"),"",IF(NOT(ISNA(VLOOKUP(E249,E$1:E248,1,FALSE()))),"OLD",IF(AND(E249&lt;&gt;"",E249&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G249" s="24" t="str">
+        <f>IF(OR(E249="",E249="!!!"),"",IF(OR(J249=0,AND(J249=1,K249=1),AND(J249=1,I249="SBJ"),AND(J249=1,I249=0)),"?IN_FOCUS",IF(J249&lt;=2,"?ACTIVATED",IF(J249&lt;&gt;"","?FAMILIAR",IF(F249="NEW",IF(ISNA(VLOOKUP(E249,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H249" s="25" t="str">
+        <f>IF(J249&lt;&gt;1,"",IF(I249="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I249" s="26" t="str">
+        <f>IF(OR(E249="",E249="!!!",F249="NEW"),"",INDEX(B248:B$2,-1+SUMPRODUCT(MAX(ROW(E248:E$2)*(E249=E248:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J249" s="26" t="str">
+        <f>IF(OR(E249="",E249="!!!",F249="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E249)*(E249=E$2:E249)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E248)*(E2=E$1:E248))))))</f>
+        <v> </v>
+      </c>
+      <c r="K249" s="26" t="str">
+        <f>IF(OR(E249="",E249="!!!",F249="NEW"),"",INDEX(J$1:J248,SUMPRODUCT(MAX(ROW(E$1:E248)*(E249=E$1:E248)))))</f>
+        <v> </v>
+      </c>
+      <c r="L249" s="27"/>
     </row>
     <row r="250" spans="1:12">
       <c r="A250" s="20" t="s">
-        <v>263</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="E250" s="22">
+        <f>IF(D250="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F250" s="23" t="str">
+        <f>IF(OR(E250="",E250="!!!"),"",IF(NOT(ISNA(VLOOKUP(E250,E$1:E249,1,FALSE()))),"OLD",IF(AND(E250&lt;&gt;"",E250&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G250" s="24" t="str">
+        <f>IF(OR(E250="",E250="!!!"),"",IF(OR(J250=0,AND(J250=1,K250=1),AND(J250=1,I250="SBJ"),AND(J250=1,I250=0)),"?IN_FOCUS",IF(J250&lt;=2,"?ACTIVATED",IF(J250&lt;&gt;"","?FAMILIAR",IF(F250="NEW",IF(ISNA(VLOOKUP(E250,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H250" s="25" t="str">
+        <f>IF(J250&lt;&gt;1,"",IF(I250="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I250" s="26" t="str">
+        <f>IF(OR(E250="",E250="!!!",F250="NEW"),"",INDEX(B249:B$2,-1+SUMPRODUCT(MAX(ROW(E249:E$2)*(E250=E249:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J250" s="26" t="str">
+        <f>IF(OR(E250="",E250="!!!",F250="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E250)*(E250=E$2:E250)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E249)*(E2=E$1:E249))))))</f>
+        <v> </v>
+      </c>
+      <c r="K250" s="26" t="str">
+        <f>IF(OR(E250="",E250="!!!",F250="NEW"),"",INDEX(J$1:J249,SUMPRODUCT(MAX(ROW(E$1:E249)*(E250=E$1:E249)))))</f>
+        <v> </v>
+      </c>
+      <c r="L250" s="27"/>
     </row>
     <row r="251" spans="1:12">
-      <c r="A251" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="B251" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="C251" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D251" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="E251" s="22">
-        <f>IF(D251="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F251" s="23" t="str">
-        <f>IF(OR(E251="",E251="!!!"),"",IF(NOT(ISNA(VLOOKUP(E251,E$1:E250,1,FALSE()))),"OLD",IF(AND(E251&lt;&gt;"",E251&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G251" s="24" t="str">
-        <f>IF(OR(E251="",E251="!!!"),"",IF(OR(J251=0,AND(J251=1,K251=1),AND(J251=1,I251="SBJ"),AND(J251=1,I251=0)),"?IN_FOCUS",IF(J251&lt;=2,"?ACTIVATED",IF(J251&lt;&gt;"","?FAMILIAR",IF(F251="NEW",IF(ISNA(VLOOKUP(E251,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H251" s="25" t="str">
-        <f>IF(J251&lt;&gt;1,"",IF(I251="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I251" s="26" t="str">
-        <f>IF(OR(E251="",E251="!!!",F251="NEW"),"",INDEX(B250:B$2,-1+SUMPRODUCT(MAX(ROW(E250:E$2)*(E251=E250:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J251" s="26" t="str">
-        <f>IF(OR(E251="",E251="!!!",F251="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E251)*(E251=E$2:E251)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E250)*(E2=E$1:E250))))))</f>
-        <v> </v>
-      </c>
-      <c r="K251" s="26" t="str">
-        <f>IF(OR(E251="",E251="!!!",F251="NEW"),"",INDEX(J$1:J250,SUMPRODUCT(MAX(ROW(E$1:E250)*(E251=E$1:E250)))))</f>
-        <v> </v>
-      </c>
-      <c r="L251" s="27"/>
+      <c r="A251" s="20"/>
     </row>
     <row r="252" spans="1:12">
       <c r="A252" s="20" t="s">
-        <v>264</v>
-      </c>
-      <c r="E252" s="22">
-        <f>IF(D252="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F252" s="23" t="str">
-        <f>IF(OR(E252="",E252="!!!"),"",IF(NOT(ISNA(VLOOKUP(E252,E$1:E251,1,FALSE()))),"OLD",IF(AND(E252&lt;&gt;"",E252&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G252" s="24" t="str">
-        <f>IF(OR(E252="",E252="!!!"),"",IF(OR(J252=0,AND(J252=1,K252=1),AND(J252=1,I252="SBJ"),AND(J252=1,I252=0)),"?IN_FOCUS",IF(J252&lt;=2,"?ACTIVATED",IF(J252&lt;&gt;"","?FAMILIAR",IF(F252="NEW",IF(ISNA(VLOOKUP(E252,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H252" s="25" t="str">
-        <f>IF(J252&lt;&gt;1,"",IF(I252="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I252" s="26" t="str">
-        <f>IF(OR(E252="",E252="!!!",F252="NEW"),"",INDEX(B251:B$2,-1+SUMPRODUCT(MAX(ROW(E251:E$2)*(E252=E251:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J252" s="26" t="str">
-        <f>IF(OR(E252="",E252="!!!",F252="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E252)*(E252=E$2:E252)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E251)*(E2=E$1:E251))))))</f>
-        <v> </v>
-      </c>
-      <c r="K252" s="26" t="str">
-        <f>IF(OR(E252="",E252="!!!",F252="NEW"),"",INDEX(J$1:J251,SUMPRODUCT(MAX(ROW(E$1:E251)*(E252=E$1:E251)))))</f>
-        <v> </v>
-      </c>
-      <c r="L252" s="27"/>
+        <v>268</v>
+      </c>
     </row>
     <row r="253" spans="1:12">
       <c r="A253" s="20" t="s">
-        <v>265</v>
+        <v>149</v>
+      </c>
+      <c r="B253" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C253" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D253" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E253" s="22">
         <f>IF(D253="?OLD","!!!","")</f>
@@ -10778,7 +10764,7 @@
     </row>
     <row r="254" spans="1:12">
       <c r="A254" s="20" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E254" s="22">
         <f>IF(D254="?OLD","!!!","")</f>
@@ -10812,13 +10798,7 @@
     </row>
     <row r="255" spans="1:12">
       <c r="A255" s="20" t="s">
-        <v>267</v>
-      </c>
-      <c r="B255" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="C255" s="21" t="s">
-        <v>136</v>
+        <v>270</v>
       </c>
       <c r="E255" s="22">
         <f>IF(D255="?OLD","!!!","")</f>
@@ -10852,7 +10832,7 @@
     </row>
     <row r="256" spans="1:12">
       <c r="A256" s="20" t="s">
-        <v>204</v>
+        <v>271</v>
       </c>
       <c r="E256" s="22">
         <f>IF(D256="?OLD","!!!","")</f>
@@ -10886,13 +10866,13 @@
     </row>
     <row r="257" spans="1:12">
       <c r="A257" s="20" t="s">
-        <v>113</v>
+        <v>272</v>
       </c>
       <c r="B257" s="21" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="C257" s="21" t="s">
-        <v>191</v>
+        <v>141</v>
       </c>
       <c r="E257" s="22">
         <f>IF(D257="?OLD","!!!","")</f>
@@ -10926,7 +10906,7 @@
     </row>
     <row r="258" spans="1:12">
       <c r="A258" s="20" t="s">
-        <v>172</v>
+        <v>209</v>
       </c>
       <c r="E258" s="22">
         <f>IF(D258="?OLD","!!!","")</f>
@@ -10960,13 +10940,13 @@
     </row>
     <row r="259" spans="1:12">
       <c r="A259" s="20" t="s">
-        <v>268</v>
+        <v>117</v>
       </c>
       <c r="B259" s="21" t="s">
         <v>118</v>
       </c>
       <c r="C259" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E259" s="22">
         <f>IF(D259="?OLD","!!!","")</f>
@@ -11000,7 +10980,7 @@
     </row>
     <row r="260" spans="1:12">
       <c r="A260" s="20" t="s">
-        <v>220</v>
+        <v>177</v>
       </c>
       <c r="E260" s="22">
         <f>IF(D260="?OLD","!!!","")</f>
@@ -11034,16 +11014,13 @@
     </row>
     <row r="261" spans="1:12">
       <c r="A261" s="20" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B261" s="21" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="C261" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D261" s="21" t="s">
-        <v>108</v>
+        <v>196</v>
       </c>
       <c r="E261" s="22">
         <f>IF(D261="?OLD","!!!","")</f>
@@ -11077,7 +11054,7 @@
     </row>
     <row r="262" spans="1:12">
       <c r="A262" s="20" t="s">
-        <v>270</v>
+        <v>225</v>
       </c>
       <c r="E262" s="22">
         <f>IF(D262="?OLD","!!!","")</f>
@@ -11111,7 +11088,16 @@
     </row>
     <row r="263" spans="1:12">
       <c r="A263" s="20" t="s">
-        <v>138</v>
+        <v>274</v>
+      </c>
+      <c r="B263" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C263" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D263" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E263" s="22">
         <f>IF(D263="?OLD","!!!","")</f>
@@ -11144,11 +11130,42 @@
       <c r="L263" s="27"/>
     </row>
     <row r="264" spans="1:12">
-      <c r="A264" s="20"/>
+      <c r="A264" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="E264" s="22">
+        <f>IF(D264="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F264" s="23" t="str">
+        <f>IF(OR(E264="",E264="!!!"),"",IF(NOT(ISNA(VLOOKUP(E264,E$1:E263,1,FALSE()))),"OLD",IF(AND(E264&lt;&gt;"",E264&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G264" s="24" t="str">
+        <f>IF(OR(E264="",E264="!!!"),"",IF(OR(J264=0,AND(J264=1,K264=1),AND(J264=1,I264="SBJ"),AND(J264=1,I264=0)),"?IN_FOCUS",IF(J264&lt;=2,"?ACTIVATED",IF(J264&lt;&gt;"","?FAMILIAR",IF(F264="NEW",IF(ISNA(VLOOKUP(E264,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H264" s="25" t="str">
+        <f>IF(J264&lt;&gt;1,"",IF(I264="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I264" s="26" t="str">
+        <f>IF(OR(E264="",E264="!!!",F264="NEW"),"",INDEX(B263:B$2,-1+SUMPRODUCT(MAX(ROW(E263:E$2)*(E264=E263:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J264" s="26" t="str">
+        <f>IF(OR(E264="",E264="!!!",F264="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E264)*(E264=E$2:E264)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E263)*(E2=E$1:E263))))))</f>
+        <v> </v>
+      </c>
+      <c r="K264" s="26" t="str">
+        <f>IF(OR(E264="",E264="!!!",F264="NEW"),"",INDEX(J$1:J263,SUMPRODUCT(MAX(ROW(E$1:E263)*(E264=E$1:E263)))))</f>
+        <v> </v>
+      </c>
+      <c r="L264" s="27"/>
     </row>
     <row r="265" spans="1:12">
       <c r="A265" s="20" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="E265" s="22">
         <f>IF(D265="?OLD","!!!","")</f>
@@ -11181,22 +11198,11 @@
       <c r="L265" s="27"/>
     </row>
     <row r="266" spans="1:12">
-      <c r="A266" s="20" t="s">
-        <v>271</v>
-      </c>
+      <c r="A266" s="20"/>
     </row>
     <row r="267" spans="1:12">
       <c r="A267" s="20" t="s">
-        <v>272</v>
-      </c>
-      <c r="B267" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="C267" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="D267" s="21" t="s">
-        <v>108</v>
+        <v>180</v>
       </c>
       <c r="E267" s="22">
         <f>IF(D267="?OLD","!!!","")</f>
@@ -11230,41 +11236,21 @@
     </row>
     <row r="268" spans="1:12">
       <c r="A268" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="E268" s="22">
-        <f>IF(D268="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F268" s="23" t="str">
-        <f>IF(OR(E268="",E268="!!!"),"",IF(NOT(ISNA(VLOOKUP(E268,E$1:E267,1,FALSE()))),"OLD",IF(AND(E268&lt;&gt;"",E268&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G268" s="24" t="str">
-        <f>IF(OR(E268="",E268="!!!"),"",IF(OR(J268=0,AND(J268=1,K268=1),AND(J268=1,I268="SBJ"),AND(J268=1,I268=0)),"?IN_FOCUS",IF(J268&lt;=2,"?ACTIVATED",IF(J268&lt;&gt;"","?FAMILIAR",IF(F268="NEW",IF(ISNA(VLOOKUP(E268,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H268" s="25" t="str">
-        <f>IF(J268&lt;&gt;1,"",IF(I268="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I268" s="26" t="str">
-        <f>IF(OR(E268="",E268="!!!",F268="NEW"),"",INDEX(B267:B$2,-1+SUMPRODUCT(MAX(ROW(E267:E$2)*(E268=E267:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J268" s="26" t="str">
-        <f>IF(OR(E268="",E268="!!!",F268="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E268)*(E268=E$2:E268)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E267)*(E2=E$1:E267))))))</f>
-        <v> </v>
-      </c>
-      <c r="K268" s="26" t="str">
-        <f>IF(OR(E268="",E268="!!!",F268="NEW"),"",INDEX(J$1:J267,SUMPRODUCT(MAX(ROW(E$1:E267)*(E268=E$1:E267)))))</f>
-        <v> </v>
-      </c>
-      <c r="L268" s="27"/>
+        <v>276</v>
+      </c>
     </row>
     <row r="269" spans="1:12">
       <c r="A269" s="20" t="s">
-        <v>130</v>
+        <v>277</v>
+      </c>
+      <c r="B269" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C269" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="D269" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E269" s="22">
         <f>IF(D269="?OLD","!!!","")</f>
@@ -11298,16 +11284,7 @@
     </row>
     <row r="270" spans="1:12">
       <c r="A270" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="B270" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="C270" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D270" s="21" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="E270" s="22">
         <f>IF(D270="?OLD","!!!","")</f>
@@ -11341,7 +11318,7 @@
     </row>
     <row r="271" spans="1:12">
       <c r="A271" s="20" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="E271" s="22">
         <f>IF(D271="?OLD","!!!","")</f>
@@ -11375,7 +11352,16 @@
     </row>
     <row r="272" spans="1:12">
       <c r="A272" s="20" t="s">
-        <v>149</v>
+        <v>151</v>
+      </c>
+      <c r="B272" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="C272" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D272" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E272" s="22">
         <f>IF(D272="?OLD","!!!","")</f>
@@ -11409,7 +11395,7 @@
     </row>
     <row r="273" spans="1:12">
       <c r="A273" s="20" t="s">
-        <v>273</v>
+        <v>115</v>
       </c>
       <c r="E273" s="22">
         <f>IF(D273="?OLD","!!!","")</f>
@@ -11443,7 +11429,7 @@
     </row>
     <row r="274" spans="1:12">
       <c r="A274" s="20" t="s">
-        <v>184</v>
+        <v>154</v>
       </c>
       <c r="E274" s="22">
         <f>IF(D274="?OLD","!!!","")</f>
@@ -11477,7 +11463,7 @@
     </row>
     <row r="275" spans="1:12">
       <c r="A275" s="20" t="s">
-        <v>121</v>
+        <v>278</v>
       </c>
       <c r="E275" s="22">
         <f>IF(D275="?OLD","!!!","")</f>
@@ -11511,16 +11497,7 @@
     </row>
     <row r="276" spans="1:12">
       <c r="A276" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="B276" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="C276" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D276" s="21" t="s">
-        <v>108</v>
+        <v>189</v>
       </c>
       <c r="E276" s="22">
         <f>IF(D276="?OLD","!!!","")</f>
@@ -11554,7 +11531,7 @@
     </row>
     <row r="277" spans="1:12">
       <c r="A277" s="20" t="s">
-        <v>232</v>
+        <v>126</v>
       </c>
       <c r="E277" s="22">
         <f>IF(D277="?OLD","!!!","")</f>
@@ -11588,7 +11565,16 @@
     </row>
     <row r="278" spans="1:12">
       <c r="A278" s="20" t="s">
-        <v>140</v>
+        <v>127</v>
+      </c>
+      <c r="B278" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="C278" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D278" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E278" s="22">
         <f>IF(D278="?OLD","!!!","")</f>
@@ -11622,13 +11608,7 @@
     </row>
     <row r="279" spans="1:12">
       <c r="A279" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="B279" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="C279" s="21" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="E279" s="22">
         <f>IF(D279="?OLD","!!!","")</f>
@@ -11662,16 +11642,7 @@
     </row>
     <row r="280" spans="1:12">
       <c r="A280" s="20" t="s">
-        <v>274</v>
-      </c>
-      <c r="B280" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="C280" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="D280" s="21" t="s">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="E280" s="22">
         <f>IF(D280="?OLD","!!!","")</f>
@@ -11705,13 +11676,13 @@
     </row>
     <row r="281" spans="1:12">
       <c r="A281" s="20" t="s">
-        <v>276</v>
+        <v>197</v>
       </c>
       <c r="B281" s="21" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C281" s="21" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="E281" s="22">
         <f>IF(D281="?OLD","!!!","")</f>
@@ -11745,7 +11716,16 @@
     </row>
     <row r="282" spans="1:12">
       <c r="A282" s="20" t="s">
-        <v>277</v>
+        <v>279</v>
+      </c>
+      <c r="B282" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="C282" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="D282" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E282" s="22">
         <f>IF(D282="?OLD","!!!","")</f>
@@ -11779,7 +11759,13 @@
     </row>
     <row r="283" spans="1:12">
       <c r="A283" s="20" t="s">
-        <v>192</v>
+        <v>281</v>
+      </c>
+      <c r="B283" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C283" s="21" t="s">
+        <v>196</v>
       </c>
       <c r="E283" s="22">
         <f>IF(D283="?OLD","!!!","")</f>
@@ -11813,7 +11799,7 @@
     </row>
     <row r="284" spans="1:12">
       <c r="A284" s="20" t="s">
-        <v>130</v>
+        <v>282</v>
       </c>
       <c r="E284" s="22">
         <f>IF(D284="?OLD","!!!","")</f>
@@ -11847,16 +11833,7 @@
     </row>
     <row r="285" spans="1:12">
       <c r="A285" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="B285" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="C285" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D285" s="21" t="s">
-        <v>108</v>
+        <v>197</v>
       </c>
       <c r="E285" s="22">
         <f>IF(D285="?OLD","!!!","")</f>
@@ -11890,7 +11867,7 @@
     </row>
     <row r="286" spans="1:12">
       <c r="A286" s="20" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="E286" s="22">
         <f>IF(D286="?OLD","!!!","")</f>
@@ -11924,7 +11901,16 @@
     </row>
     <row r="287" spans="1:12">
       <c r="A287" s="20" t="s">
-        <v>278</v>
+        <v>127</v>
+      </c>
+      <c r="B287" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="C287" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D287" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E287" s="22">
         <f>IF(D287="?OLD","!!!","")</f>
@@ -11958,16 +11944,7 @@
     </row>
     <row r="288" spans="1:12">
       <c r="A288" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="B288" s="21" t="s">
-        <v>256</v>
-      </c>
-      <c r="C288" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="D288" s="21" t="s">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="E288" s="22">
         <f>IF(D288="?OLD","!!!","")</f>
@@ -12001,16 +11978,7 @@
     </row>
     <row r="289" spans="1:12">
       <c r="A289" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="B289" s="21" t="s">
-        <v>259</v>
-      </c>
-      <c r="C289" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="D289" s="21" t="s">
-        <v>108</v>
+        <v>283</v>
       </c>
       <c r="E289" s="22">
         <f>IF(D289="?OLD","!!!","")</f>
@@ -12044,13 +12012,16 @@
     </row>
     <row r="290" spans="1:12">
       <c r="A290" s="20" t="s">
-        <v>280</v>
+        <v>135</v>
       </c>
       <c r="B290" s="21" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="C290" s="21" t="s">
-        <v>191</v>
+        <v>170</v>
+      </c>
+      <c r="D290" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E290" s="22">
         <f>IF(D290="?OLD","!!!","")</f>
@@ -12084,7 +12055,16 @@
     </row>
     <row r="291" spans="1:12">
       <c r="A291" s="20" t="s">
-        <v>281</v>
+        <v>284</v>
+      </c>
+      <c r="B291" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="C291" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="D291" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E291" s="22">
         <f>IF(D291="?OLD","!!!","")</f>
@@ -12118,7 +12098,13 @@
     </row>
     <row r="292" spans="1:12">
       <c r="A292" s="20" t="s">
-        <v>142</v>
+        <v>285</v>
+      </c>
+      <c r="B292" s="21" t="s">
+        <v>257</v>
+      </c>
+      <c r="C292" s="21" t="s">
+        <v>196</v>
       </c>
       <c r="E292" s="22">
         <f>IF(D292="?OLD","!!!","")</f>
@@ -12152,7 +12138,7 @@
     </row>
     <row r="293" spans="1:12">
       <c r="A293" s="20" t="s">
-        <v>64</v>
+        <v>286</v>
       </c>
       <c r="E293" s="22">
         <f>IF(D293="?OLD","!!!","")</f>
@@ -12186,7 +12172,7 @@
     </row>
     <row r="294" spans="1:12">
       <c r="A294" s="20" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E294" s="22">
         <f>IF(D294="?OLD","!!!","")</f>
@@ -12220,7 +12206,7 @@
     </row>
     <row r="295" spans="1:12">
       <c r="A295" s="20" t="s">
-        <v>282</v>
+        <v>68</v>
       </c>
       <c r="E295" s="22">
         <f>IF(D295="?OLD","!!!","")</f>
@@ -12254,16 +12240,7 @@
     </row>
     <row r="296" spans="1:12">
       <c r="A296" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="B296" s="21" t="s">
-        <v>284</v>
-      </c>
-      <c r="C296" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="D296" s="21" t="s">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="E296" s="22">
         <f>IF(D296="?OLD","!!!","")</f>
@@ -12297,7 +12274,7 @@
     </row>
     <row r="297" spans="1:12">
       <c r="A297" s="20" t="s">
-        <v>217</v>
+        <v>287</v>
       </c>
       <c r="E297" s="22">
         <f>IF(D297="?OLD","!!!","")</f>
@@ -12331,7 +12308,16 @@
     </row>
     <row r="298" spans="1:12">
       <c r="A298" s="20" t="s">
-        <v>120</v>
+        <v>288</v>
+      </c>
+      <c r="B298" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="C298" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="D298" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E298" s="22">
         <f>IF(D298="?OLD","!!!","")</f>
@@ -12365,13 +12351,7 @@
     </row>
     <row r="299" spans="1:12">
       <c r="A299" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="B299" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="C299" s="21" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="E299" s="22">
         <f>IF(D299="?OLD","!!!","")</f>
@@ -12405,7 +12385,7 @@
     </row>
     <row r="300" spans="1:12">
       <c r="A300" s="20" t="s">
-        <v>266</v>
+        <v>124</v>
       </c>
       <c r="E300" s="22">
         <f>IF(D300="?OLD","!!!","")</f>
@@ -12439,13 +12419,13 @@
     </row>
     <row r="301" spans="1:12">
       <c r="A301" s="20" t="s">
-        <v>109</v>
+        <v>197</v>
       </c>
       <c r="B301" s="21" t="s">
-        <v>118</v>
+        <v>290</v>
       </c>
       <c r="C301" s="21" t="s">
-        <v>136</v>
+        <v>215</v>
       </c>
       <c r="E301" s="22">
         <f>IF(D301="?OLD","!!!","")</f>
@@ -12479,7 +12459,7 @@
     </row>
     <row r="302" spans="1:12">
       <c r="A302" s="20" t="s">
-        <v>204</v>
+        <v>271</v>
       </c>
       <c r="E302" s="22">
         <f>IF(D302="?OLD","!!!","")</f>
@@ -12513,13 +12493,13 @@
     </row>
     <row r="303" spans="1:12">
       <c r="A303" s="20" t="s">
-        <v>219</v>
+        <v>113</v>
       </c>
       <c r="B303" s="21" t="s">
-        <v>285</v>
+        <v>122</v>
       </c>
       <c r="C303" s="21" t="s">
-        <v>191</v>
+        <v>141</v>
       </c>
       <c r="E303" s="22">
         <f>IF(D303="?OLD","!!!","")</f>
@@ -12553,7 +12533,7 @@
     </row>
     <row r="304" spans="1:12">
       <c r="A304" s="20" t="s">
-        <v>64</v>
+        <v>209</v>
       </c>
       <c r="E304" s="22">
         <f>IF(D304="?OLD","!!!","")</f>
@@ -12587,7 +12567,13 @@
     </row>
     <row r="305" spans="1:12">
       <c r="A305" s="20" t="s">
-        <v>138</v>
+        <v>224</v>
+      </c>
+      <c r="B305" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="C305" s="21" t="s">
+        <v>196</v>
       </c>
       <c r="E305" s="22">
         <f>IF(D305="?OLD","!!!","")</f>
@@ -12621,7 +12607,7 @@
     </row>
     <row r="306" spans="1:12">
       <c r="A306" s="20" t="s">
-        <v>184</v>
+        <v>68</v>
       </c>
       <c r="E306" s="22">
         <f>IF(D306="?OLD","!!!","")</f>
@@ -12654,93 +12640,84 @@
       <c r="L306" s="27"/>
     </row>
     <row r="307" spans="1:12">
-      <c r="A307" s="20"/>
+      <c r="A307" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E307" s="22">
+        <f>IF(D307="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F307" s="23" t="str">
+        <f>IF(OR(E307="",E307="!!!"),"",IF(NOT(ISNA(VLOOKUP(E307,E$1:E306,1,FALSE()))),"OLD",IF(AND(E307&lt;&gt;"",E307&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G307" s="24" t="str">
+        <f>IF(OR(E307="",E307="!!!"),"",IF(OR(J307=0,AND(J307=1,K307=1),AND(J307=1,I307="SBJ"),AND(J307=1,I307=0)),"?IN_FOCUS",IF(J307&lt;=2,"?ACTIVATED",IF(J307&lt;&gt;"","?FAMILIAR",IF(F307="NEW",IF(ISNA(VLOOKUP(E307,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H307" s="25" t="str">
+        <f>IF(J307&lt;&gt;1,"",IF(I307="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I307" s="26" t="str">
+        <f>IF(OR(E307="",E307="!!!",F307="NEW"),"",INDEX(B306:B$2,-1+SUMPRODUCT(MAX(ROW(E306:E$2)*(E307=E306:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J307" s="26" t="str">
+        <f>IF(OR(E307="",E307="!!!",F307="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E307)*(E307=E$2:E307)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E306)*(E2=E$1:E306))))))</f>
+        <v> </v>
+      </c>
+      <c r="K307" s="26" t="str">
+        <f>IF(OR(E307="",E307="!!!",F307="NEW"),"",INDEX(J$1:J306,SUMPRODUCT(MAX(ROW(E$1:E306)*(E307=E$1:E306)))))</f>
+        <v> </v>
+      </c>
+      <c r="L307" s="27"/>
     </row>
     <row r="308" spans="1:12">
       <c r="A308" s="20" t="s">
-        <v>286</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="E308" s="22">
+        <f>IF(D308="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F308" s="23" t="str">
+        <f>IF(OR(E308="",E308="!!!"),"",IF(NOT(ISNA(VLOOKUP(E308,E$1:E307,1,FALSE()))),"OLD",IF(AND(E308&lt;&gt;"",E308&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G308" s="24" t="str">
+        <f>IF(OR(E308="",E308="!!!"),"",IF(OR(J308=0,AND(J308=1,K308=1),AND(J308=1,I308="SBJ"),AND(J308=1,I308=0)),"?IN_FOCUS",IF(J308&lt;=2,"?ACTIVATED",IF(J308&lt;&gt;"","?FAMILIAR",IF(F308="NEW",IF(ISNA(VLOOKUP(E308,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H308" s="25" t="str">
+        <f>IF(J308&lt;&gt;1,"",IF(I308="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I308" s="26" t="str">
+        <f>IF(OR(E308="",E308="!!!",F308="NEW"),"",INDEX(B307:B$2,-1+SUMPRODUCT(MAX(ROW(E307:E$2)*(E308=E307:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J308" s="26" t="str">
+        <f>IF(OR(E308="",E308="!!!",F308="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E308)*(E308=E$2:E308)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E307)*(E2=E$1:E307))))))</f>
+        <v> </v>
+      </c>
+      <c r="K308" s="26" t="str">
+        <f>IF(OR(E308="",E308="!!!",F308="NEW"),"",INDEX(J$1:J307,SUMPRODUCT(MAX(ROW(E$1:E307)*(E308=E$1:E307)))))</f>
+        <v> </v>
+      </c>
+      <c r="L308" s="27"/>
     </row>
     <row r="309" spans="1:12">
-      <c r="A309" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="E309" s="22">
-        <f>IF(D309="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F309" s="23" t="str">
-        <f>IF(OR(E309="",E309="!!!"),"",IF(NOT(ISNA(VLOOKUP(E309,E$1:E308,1,FALSE()))),"OLD",IF(AND(E309&lt;&gt;"",E309&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G309" s="24" t="str">
-        <f>IF(OR(E309="",E309="!!!"),"",IF(OR(J309=0,AND(J309=1,K309=1),AND(J309=1,I309="SBJ"),AND(J309=1,I309=0)),"?IN_FOCUS",IF(J309&lt;=2,"?ACTIVATED",IF(J309&lt;&gt;"","?FAMILIAR",IF(F309="NEW",IF(ISNA(VLOOKUP(E309,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H309" s="25" t="str">
-        <f>IF(J309&lt;&gt;1,"",IF(I309="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I309" s="26" t="str">
-        <f>IF(OR(E309="",E309="!!!",F309="NEW"),"",INDEX(B308:B$2,-1+SUMPRODUCT(MAX(ROW(E308:E$2)*(E309=E308:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J309" s="26" t="str">
-        <f>IF(OR(E309="",E309="!!!",F309="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E309)*(E309=E$2:E309)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E308)*(E2=E$1:E308))))))</f>
-        <v> </v>
-      </c>
-      <c r="K309" s="26" t="str">
-        <f>IF(OR(E309="",E309="!!!",F309="NEW"),"",INDEX(J$1:J308,SUMPRODUCT(MAX(ROW(E$1:E308)*(E309=E$1:E308)))))</f>
-        <v> </v>
-      </c>
-      <c r="L309" s="27"/>
+      <c r="A309" s="20"/>
     </row>
     <row r="310" spans="1:12">
       <c r="A310" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="E310" s="22">
-        <f>IF(D310="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F310" s="23" t="str">
-        <f>IF(OR(E310="",E310="!!!"),"",IF(NOT(ISNA(VLOOKUP(E310,E$1:E309,1,FALSE()))),"OLD",IF(AND(E310&lt;&gt;"",E310&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G310" s="24" t="str">
-        <f>IF(OR(E310="",E310="!!!"),"",IF(OR(J310=0,AND(J310=1,K310=1),AND(J310=1,I310="SBJ"),AND(J310=1,I310=0)),"?IN_FOCUS",IF(J310&lt;=2,"?ACTIVATED",IF(J310&lt;&gt;"","?FAMILIAR",IF(F310="NEW",IF(ISNA(VLOOKUP(E310,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H310" s="25" t="str">
-        <f>IF(J310&lt;&gt;1,"",IF(I310="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I310" s="26" t="str">
-        <f>IF(OR(E310="",E310="!!!",F310="NEW"),"",INDEX(B309:B$2,-1+SUMPRODUCT(MAX(ROW(E309:E$2)*(E310=E309:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J310" s="26" t="str">
-        <f>IF(OR(E310="",E310="!!!",F310="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E310)*(E310=E$2:E310)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E309)*(E2=E$1:E309))))))</f>
-        <v> </v>
-      </c>
-      <c r="K310" s="26" t="str">
-        <f>IF(OR(E310="",E310="!!!",F310="NEW"),"",INDEX(J$1:J309,SUMPRODUCT(MAX(ROW(E$1:E309)*(E310=E$1:E309)))))</f>
-        <v> </v>
-      </c>
-      <c r="L310" s="27"/>
+        <v>291</v>
+      </c>
     </row>
     <row r="311" spans="1:12">
       <c r="A311" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="B311" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="C311" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D311" s="21" t="s">
-        <v>108</v>
+        <v>292</v>
       </c>
       <c r="E311" s="22">
         <f>IF(D311="?OLD","!!!","")</f>
@@ -12774,7 +12751,7 @@
     </row>
     <row r="312" spans="1:12">
       <c r="A312" s="20" t="s">
-        <v>288</v>
+        <v>157</v>
       </c>
       <c r="E312" s="22">
         <f>IF(D312="?OLD","!!!","")</f>
@@ -12808,7 +12785,16 @@
     </row>
     <row r="313" spans="1:12">
       <c r="A313" s="20" t="s">
-        <v>192</v>
+        <v>113</v>
+      </c>
+      <c r="B313" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="C313" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D313" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E313" s="22">
         <f>IF(D313="?OLD","!!!","")</f>
@@ -12842,7 +12828,7 @@
     </row>
     <row r="314" spans="1:12">
       <c r="A314" s="20" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="E314" s="22">
         <f>IF(D314="?OLD","!!!","")</f>
@@ -12876,7 +12862,7 @@
     </row>
     <row r="315" spans="1:12">
       <c r="A315" s="20" t="s">
-        <v>154</v>
+        <v>197</v>
       </c>
       <c r="E315" s="22">
         <f>IF(D315="?OLD","!!!","")</f>
@@ -12910,13 +12896,7 @@
     </row>
     <row r="316" spans="1:12">
       <c r="A316" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="B316" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C316" s="21" t="s">
-        <v>136</v>
+        <v>271</v>
       </c>
       <c r="E316" s="22">
         <f>IF(D316="?OLD","!!!","")</f>
@@ -12950,7 +12930,7 @@
     </row>
     <row r="317" spans="1:12">
       <c r="A317" s="20" t="s">
-        <v>264</v>
+        <v>159</v>
       </c>
       <c r="E317" s="22">
         <f>IF(D317="?OLD","!!!","")</f>
@@ -12984,7 +12964,13 @@
     </row>
     <row r="318" spans="1:12">
       <c r="A318" s="20" t="s">
-        <v>150</v>
+        <v>127</v>
+      </c>
+      <c r="B318" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C318" s="21" t="s">
+        <v>141</v>
       </c>
       <c r="E318" s="22">
         <f>IF(D318="?OLD","!!!","")</f>
@@ -13018,7 +13004,7 @@
     </row>
     <row r="319" spans="1:12">
       <c r="A319" s="20" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E319" s="22">
         <f>IF(D319="?OLD","!!!","")</f>
@@ -13052,16 +13038,7 @@
     </row>
     <row r="320" spans="1:12">
       <c r="A320" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="B320" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="C320" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D320" s="21" t="s">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="E320" s="22">
         <f>IF(D320="?OLD","!!!","")</f>
@@ -13095,13 +13072,7 @@
     </row>
     <row r="321" spans="1:12">
       <c r="A321" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="B321" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="C321" s="21" t="s">
-        <v>210</v>
+        <v>269</v>
       </c>
       <c r="E321" s="22">
         <f>IF(D321="?OLD","!!!","")</f>
@@ -13135,7 +13106,16 @@
     </row>
     <row r="322" spans="1:12">
       <c r="A322" s="20" t="s">
-        <v>130</v>
+        <v>129</v>
+      </c>
+      <c r="B322" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C322" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D322" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E322" s="22">
         <f>IF(D322="?OLD","!!!","")</f>
@@ -13169,7 +13149,13 @@
     </row>
     <row r="323" spans="1:12">
       <c r="A323" s="20" t="s">
-        <v>154</v>
+        <v>197</v>
+      </c>
+      <c r="B323" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="C323" s="21" t="s">
+        <v>215</v>
       </c>
       <c r="E323" s="22">
         <f>IF(D323="?OLD","!!!","")</f>
@@ -13203,16 +13189,7 @@
     </row>
     <row r="324" spans="1:12">
       <c r="A324" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="B324" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C324" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D324" s="21" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="E324" s="22">
         <f>IF(D324="?OLD","!!!","")</f>
@@ -13246,7 +13223,7 @@
     </row>
     <row r="325" spans="1:12">
       <c r="A325" s="20" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="E325" s="22">
         <f>IF(D325="?OLD","!!!","")</f>
@@ -13279,93 +13256,102 @@
       <c r="L325" s="27"/>
     </row>
     <row r="326" spans="1:12">
-      <c r="A326" s="20"/>
+      <c r="A326" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="B326" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C326" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D326" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="E326" s="22">
+        <f>IF(D326="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F326" s="23" t="str">
+        <f>IF(OR(E326="",E326="!!!"),"",IF(NOT(ISNA(VLOOKUP(E326,E$1:E325,1,FALSE()))),"OLD",IF(AND(E326&lt;&gt;"",E326&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G326" s="24" t="str">
+        <f>IF(OR(E326="",E326="!!!"),"",IF(OR(J326=0,AND(J326=1,K326=1),AND(J326=1,I326="SBJ"),AND(J326=1,I326=0)),"?IN_FOCUS",IF(J326&lt;=2,"?ACTIVATED",IF(J326&lt;&gt;"","?FAMILIAR",IF(F326="NEW",IF(ISNA(VLOOKUP(E326,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H326" s="25" t="str">
+        <f>IF(J326&lt;&gt;1,"",IF(I326="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I326" s="26" t="str">
+        <f>IF(OR(E326="",E326="!!!",F326="NEW"),"",INDEX(B325:B$2,-1+SUMPRODUCT(MAX(ROW(E325:E$2)*(E326=E325:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J326" s="26" t="str">
+        <f>IF(OR(E326="",E326="!!!",F326="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E326)*(E326=E$2:E326)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E325)*(E2=E$1:E325))))))</f>
+        <v> </v>
+      </c>
+      <c r="K326" s="26" t="str">
+        <f>IF(OR(E326="",E326="!!!",F326="NEW"),"",INDEX(J$1:J325,SUMPRODUCT(MAX(ROW(E$1:E325)*(E326=E$1:E325)))))</f>
+        <v> </v>
+      </c>
+      <c r="L326" s="27"/>
     </row>
     <row r="327" spans="1:12">
       <c r="A327" s="20" t="s">
-        <v>289</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="E327" s="22">
+        <f>IF(D327="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F327" s="23" t="str">
+        <f>IF(OR(E327="",E327="!!!"),"",IF(NOT(ISNA(VLOOKUP(E327,E$1:E326,1,FALSE()))),"OLD",IF(AND(E327&lt;&gt;"",E327&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G327" s="24" t="str">
+        <f>IF(OR(E327="",E327="!!!"),"",IF(OR(J327=0,AND(J327=1,K327=1),AND(J327=1,I327="SBJ"),AND(J327=1,I327=0)),"?IN_FOCUS",IF(J327&lt;=2,"?ACTIVATED",IF(J327&lt;&gt;"","?FAMILIAR",IF(F327="NEW",IF(ISNA(VLOOKUP(E327,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H327" s="25" t="str">
+        <f>IF(J327&lt;&gt;1,"",IF(I327="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I327" s="26" t="str">
+        <f>IF(OR(E327="",E327="!!!",F327="NEW"),"",INDEX(B326:B$2,-1+SUMPRODUCT(MAX(ROW(E326:E$2)*(E327=E326:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J327" s="26" t="str">
+        <f>IF(OR(E327="",E327="!!!",F327="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E327)*(E327=E$2:E327)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E326)*(E2=E$1:E326))))))</f>
+        <v> </v>
+      </c>
+      <c r="K327" s="26" t="str">
+        <f>IF(OR(E327="",E327="!!!",F327="NEW"),"",INDEX(J$1:J326,SUMPRODUCT(MAX(ROW(E$1:E326)*(E327=E$1:E326)))))</f>
+        <v> </v>
+      </c>
+      <c r="L327" s="27"/>
     </row>
     <row r="328" spans="1:12">
-      <c r="A328" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="B328" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="C328" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="D328" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="E328" s="22">
-        <f>IF(D328="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F328" s="23" t="str">
-        <f>IF(OR(E328="",E328="!!!"),"",IF(NOT(ISNA(VLOOKUP(E328,E$1:E327,1,FALSE()))),"OLD",IF(AND(E328&lt;&gt;"",E328&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G328" s="24" t="str">
-        <f>IF(OR(E328="",E328="!!!"),"",IF(OR(J328=0,AND(J328=1,K328=1),AND(J328=1,I328="SBJ"),AND(J328=1,I328=0)),"?IN_FOCUS",IF(J328&lt;=2,"?ACTIVATED",IF(J328&lt;&gt;"","?FAMILIAR",IF(F328="NEW",IF(ISNA(VLOOKUP(E328,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H328" s="25" t="str">
-        <f>IF(J328&lt;&gt;1,"",IF(I328="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I328" s="26" t="str">
-        <f>IF(OR(E328="",E328="!!!",F328="NEW"),"",INDEX(B327:B$2,-1+SUMPRODUCT(MAX(ROW(E327:E$2)*(E328=E327:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J328" s="26" t="str">
-        <f>IF(OR(E328="",E328="!!!",F328="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E328)*(E328=E$2:E328)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E327)*(E2=E$1:E327))))))</f>
-        <v> </v>
-      </c>
-      <c r="K328" s="26" t="str">
-        <f>IF(OR(E328="",E328="!!!",F328="NEW"),"",INDEX(J$1:J327,SUMPRODUCT(MAX(ROW(E$1:E327)*(E328=E$1:E327)))))</f>
-        <v> </v>
-      </c>
-      <c r="L328" s="27"/>
+      <c r="A328" s="20"/>
     </row>
     <row r="329" spans="1:12">
       <c r="A329" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="E329" s="22">
-        <f>IF(D329="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F329" s="23" t="str">
-        <f>IF(OR(E329="",E329="!!!"),"",IF(NOT(ISNA(VLOOKUP(E329,E$1:E328,1,FALSE()))),"OLD",IF(AND(E329&lt;&gt;"",E329&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G329" s="24" t="str">
-        <f>IF(OR(E329="",E329="!!!"),"",IF(OR(J329=0,AND(J329=1,K329=1),AND(J329=1,I329="SBJ"),AND(J329=1,I329=0)),"?IN_FOCUS",IF(J329&lt;=2,"?ACTIVATED",IF(J329&lt;&gt;"","?FAMILIAR",IF(F329="NEW",IF(ISNA(VLOOKUP(E329,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H329" s="25" t="str">
-        <f>IF(J329&lt;&gt;1,"",IF(I329="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I329" s="26" t="str">
-        <f>IF(OR(E329="",E329="!!!",F329="NEW"),"",INDEX(B328:B$2,-1+SUMPRODUCT(MAX(ROW(E328:E$2)*(E329=E328:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J329" s="26" t="str">
-        <f>IF(OR(E329="",E329="!!!",F329="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E329)*(E329=E$2:E329)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E328)*(E2=E$1:E328))))))</f>
-        <v> </v>
-      </c>
-      <c r="K329" s="26" t="str">
-        <f>IF(OR(E329="",E329="!!!",F329="NEW"),"",INDEX(J$1:J328,SUMPRODUCT(MAX(ROW(E$1:E328)*(E329=E$1:E328)))))</f>
-        <v> </v>
-      </c>
-      <c r="L329" s="27"/>
+        <v>294</v>
+      </c>
     </row>
     <row r="330" spans="1:12">
       <c r="A330" s="20" t="s">
-        <v>217</v>
+        <v>295</v>
+      </c>
+      <c r="B330" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C330" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="D330" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E330" s="22">
         <f>IF(D330="?OLD","!!!","")</f>
@@ -13399,7 +13385,7 @@
     </row>
     <row r="331" spans="1:12">
       <c r="A331" s="20" t="s">
-        <v>150</v>
+        <v>296</v>
       </c>
       <c r="E331" s="22">
         <f>IF(D331="?OLD","!!!","")</f>
@@ -13433,7 +13419,7 @@
     </row>
     <row r="332" spans="1:12">
       <c r="A332" s="20" t="s">
-        <v>151</v>
+        <v>222</v>
       </c>
       <c r="E332" s="22">
         <f>IF(D332="?OLD","!!!","")</f>
@@ -13467,16 +13453,7 @@
     </row>
     <row r="333" spans="1:12">
       <c r="A333" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="B333" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="C333" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="D333" s="21" t="s">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="E333" s="22">
         <f>IF(D333="?OLD","!!!","")</f>
@@ -13510,16 +13487,7 @@
     </row>
     <row r="334" spans="1:12">
       <c r="A334" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="B334" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="C334" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="D334" s="21" t="s">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="E334" s="22">
         <f>IF(D334="?OLD","!!!","")</f>
@@ -13553,7 +13521,16 @@
     </row>
     <row r="335" spans="1:12">
       <c r="A335" s="20" t="s">
-        <v>154</v>
+        <v>288</v>
+      </c>
+      <c r="B335" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="C335" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="D335" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E335" s="22">
         <f>IF(D335="?OLD","!!!","")</f>
@@ -13587,13 +13564,16 @@
     </row>
     <row r="336" spans="1:12">
       <c r="A336" s="20" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B336" s="21" t="s">
-        <v>190</v>
+        <v>122</v>
       </c>
       <c r="C336" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
+      </c>
+      <c r="D336" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E336" s="22">
         <f>IF(D336="?OLD","!!!","")</f>
@@ -13627,7 +13607,7 @@
     </row>
     <row r="337" spans="1:12">
       <c r="A337" s="20" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="E337" s="22">
         <f>IF(D337="?OLD","!!!","")</f>
@@ -13661,7 +13641,13 @@
     </row>
     <row r="338" spans="1:12">
       <c r="A338" s="20" t="s">
-        <v>294</v>
+        <v>298</v>
+      </c>
+      <c r="B338" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="C338" s="21" t="s">
+        <v>174</v>
       </c>
       <c r="E338" s="22">
         <f>IF(D338="?OLD","!!!","")</f>
@@ -13695,7 +13681,7 @@
     </row>
     <row r="339" spans="1:12">
       <c r="A339" s="20" t="s">
-        <v>295</v>
+        <v>155</v>
       </c>
       <c r="E339" s="22">
         <f>IF(D339="?OLD","!!!","")</f>
@@ -13729,13 +13715,7 @@
     </row>
     <row r="340" spans="1:12">
       <c r="A340" s="20" t="s">
-        <v>293</v>
-      </c>
-      <c r="B340" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="C340" s="21" t="s">
-        <v>191</v>
+        <v>299</v>
       </c>
       <c r="E340" s="22">
         <f>IF(D340="?OLD","!!!","")</f>
@@ -13769,7 +13749,7 @@
     </row>
     <row r="341" spans="1:12">
       <c r="A341" s="20" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E341" s="22">
         <f>IF(D341="?OLD","!!!","")</f>
@@ -13803,7 +13783,13 @@
     </row>
     <row r="342" spans="1:12">
       <c r="A342" s="20" t="s">
-        <v>138</v>
+        <v>298</v>
+      </c>
+      <c r="B342" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="C342" s="21" t="s">
+        <v>196</v>
       </c>
       <c r="E342" s="22">
         <f>IF(D342="?OLD","!!!","")</f>
@@ -13836,108 +13822,90 @@
       <c r="L342" s="27"/>
     </row>
     <row r="343" spans="1:12">
-      <c r="A343" s="20"/>
+      <c r="A343" s="20" t="s">
+        <v>301</v>
+      </c>
+      <c r="E343" s="22">
+        <f>IF(D343="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F343" s="23" t="str">
+        <f>IF(OR(E343="",E343="!!!"),"",IF(NOT(ISNA(VLOOKUP(E343,E$1:E342,1,FALSE()))),"OLD",IF(AND(E343&lt;&gt;"",E343&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G343" s="24" t="str">
+        <f>IF(OR(E343="",E343="!!!"),"",IF(OR(J343=0,AND(J343=1,K343=1),AND(J343=1,I343="SBJ"),AND(J343=1,I343=0)),"?IN_FOCUS",IF(J343&lt;=2,"?ACTIVATED",IF(J343&lt;&gt;"","?FAMILIAR",IF(F343="NEW",IF(ISNA(VLOOKUP(E343,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H343" s="25" t="str">
+        <f>IF(J343&lt;&gt;1,"",IF(I343="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I343" s="26" t="str">
+        <f>IF(OR(E343="",E343="!!!",F343="NEW"),"",INDEX(B342:B$2,-1+SUMPRODUCT(MAX(ROW(E342:E$2)*(E343=E342:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J343" s="26" t="str">
+        <f>IF(OR(E343="",E343="!!!",F343="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E343)*(E343=E$2:E343)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E342)*(E2=E$1:E342))))))</f>
+        <v> </v>
+      </c>
+      <c r="K343" s="26" t="str">
+        <f>IF(OR(E343="",E343="!!!",F343="NEW"),"",INDEX(J$1:J342,SUMPRODUCT(MAX(ROW(E$1:E342)*(E343=E$1:E342)))))</f>
+        <v> </v>
+      </c>
+      <c r="L343" s="27"/>
     </row>
     <row r="344" spans="1:12">
       <c r="A344" s="20" t="s">
-        <v>297</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="E344" s="22">
+        <f>IF(D344="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F344" s="23" t="str">
+        <f>IF(OR(E344="",E344="!!!"),"",IF(NOT(ISNA(VLOOKUP(E344,E$1:E343,1,FALSE()))),"OLD",IF(AND(E344&lt;&gt;"",E344&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G344" s="24" t="str">
+        <f>IF(OR(E344="",E344="!!!"),"",IF(OR(J344=0,AND(J344=1,K344=1),AND(J344=1,I344="SBJ"),AND(J344=1,I344=0)),"?IN_FOCUS",IF(J344&lt;=2,"?ACTIVATED",IF(J344&lt;&gt;"","?FAMILIAR",IF(F344="NEW",IF(ISNA(VLOOKUP(E344,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H344" s="25" t="str">
+        <f>IF(J344&lt;&gt;1,"",IF(I344="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I344" s="26" t="str">
+        <f>IF(OR(E344="",E344="!!!",F344="NEW"),"",INDEX(B343:B$2,-1+SUMPRODUCT(MAX(ROW(E343:E$2)*(E344=E343:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J344" s="26" t="str">
+        <f>IF(OR(E344="",E344="!!!",F344="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E344)*(E344=E$2:E344)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E343)*(E2=E$1:E343))))))</f>
+        <v> </v>
+      </c>
+      <c r="K344" s="26" t="str">
+        <f>IF(OR(E344="",E344="!!!",F344="NEW"),"",INDEX(J$1:J343,SUMPRODUCT(MAX(ROW(E$1:E343)*(E344=E$1:E343)))))</f>
+        <v> </v>
+      </c>
+      <c r="L344" s="27"/>
     </row>
     <row r="345" spans="1:12">
-      <c r="A345" s="20" t="s">
-        <v>298</v>
-      </c>
-      <c r="B345" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="C345" s="21" t="s">
-        <v>210</v>
-      </c>
-      <c r="E345" s="22">
-        <f>IF(D345="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F345" s="23" t="str">
-        <f>IF(OR(E345="",E345="!!!"),"",IF(NOT(ISNA(VLOOKUP(E345,E$1:E344,1,FALSE()))),"OLD",IF(AND(E345&lt;&gt;"",E345&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G345" s="24" t="str">
-        <f>IF(OR(E345="",E345="!!!"),"",IF(OR(J345=0,AND(J345=1,K345=1),AND(J345=1,I345="SBJ"),AND(J345=1,I345=0)),"?IN_FOCUS",IF(J345&lt;=2,"?ACTIVATED",IF(J345&lt;&gt;"","?FAMILIAR",IF(F345="NEW",IF(ISNA(VLOOKUP(E345,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H345" s="25" t="str">
-        <f>IF(J345&lt;&gt;1,"",IF(I345="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I345" s="26" t="str">
-        <f>IF(OR(E345="",E345="!!!",F345="NEW"),"",INDEX(B344:B$2,-1+SUMPRODUCT(MAX(ROW(E344:E$2)*(E345=E344:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J345" s="26" t="str">
-        <f>IF(OR(E345="",E345="!!!",F345="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E345)*(E345=E$2:E345)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E344)*(E2=E$1:E344))))))</f>
-        <v> </v>
-      </c>
-      <c r="K345" s="26" t="str">
-        <f>IF(OR(E345="",E345="!!!",F345="NEW"),"",INDEX(J$1:J344,SUMPRODUCT(MAX(ROW(E$1:E344)*(E345=E$1:E344)))))</f>
-        <v> </v>
-      </c>
-      <c r="L345" s="27"/>
+      <c r="A345" s="20"/>
     </row>
     <row r="346" spans="1:12">
       <c r="A346" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="B346" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="C346" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="D346" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="E346" s="22">
-        <f>IF(D346="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F346" s="23" t="str">
-        <f>IF(OR(E346="",E346="!!!"),"",IF(NOT(ISNA(VLOOKUP(E346,E$1:E345,1,FALSE()))),"OLD",IF(AND(E346&lt;&gt;"",E346&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G346" s="24" t="str">
-        <f>IF(OR(E346="",E346="!!!"),"",IF(OR(J346=0,AND(J346=1,K346=1),AND(J346=1,I346="SBJ"),AND(J346=1,I346=0)),"?IN_FOCUS",IF(J346&lt;=2,"?ACTIVATED",IF(J346&lt;&gt;"","?FAMILIAR",IF(F346="NEW",IF(ISNA(VLOOKUP(E346,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H346" s="25" t="str">
-        <f>IF(J346&lt;&gt;1,"",IF(I346="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I346" s="26" t="str">
-        <f>IF(OR(E346="",E346="!!!",F346="NEW"),"",INDEX(B345:B$2,-1+SUMPRODUCT(MAX(ROW(E345:E$2)*(E346=E345:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J346" s="26" t="str">
-        <f>IF(OR(E346="",E346="!!!",F346="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E346)*(E346=E$2:E346)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E345)*(E2=E$1:E345))))))</f>
-        <v> </v>
-      </c>
-      <c r="K346" s="26" t="str">
-        <f>IF(OR(E346="",E346="!!!",F346="NEW"),"",INDEX(J$1:J345,SUMPRODUCT(MAX(ROW(E$1:E345)*(E346=E$1:E345)))))</f>
-        <v> </v>
-      </c>
-      <c r="L346" s="27"/>
+        <v>302</v>
+      </c>
     </row>
     <row r="347" spans="1:12">
       <c r="A347" s="20" t="s">
-        <v>219</v>
+        <v>303</v>
       </c>
       <c r="B347" s="21" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C347" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="D347" s="21" t="s">
-        <v>108</v>
+        <v>215</v>
       </c>
       <c r="E347" s="22">
         <f>IF(D347="?OLD","!!!","")</f>
@@ -13971,7 +13939,16 @@
     </row>
     <row r="348" spans="1:12">
       <c r="A348" s="20" t="s">
-        <v>140</v>
+        <v>183</v>
+      </c>
+      <c r="B348" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="C348" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D348" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E348" s="22">
         <f>IF(D348="?OLD","!!!","")</f>
@@ -14005,7 +13982,16 @@
     </row>
     <row r="349" spans="1:12">
       <c r="A349" s="20" t="s">
-        <v>220</v>
+        <v>224</v>
+      </c>
+      <c r="B349" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C349" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="D349" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E349" s="22">
         <f>IF(D349="?OLD","!!!","")</f>
@@ -14039,7 +14025,7 @@
     </row>
     <row r="350" spans="1:12">
       <c r="A350" s="20" t="s">
-        <v>299</v>
+        <v>145</v>
       </c>
       <c r="E350" s="22">
         <f>IF(D350="?OLD","!!!","")</f>
@@ -14073,7 +14059,7 @@
     </row>
     <row r="351" spans="1:12">
       <c r="A351" s="20" t="s">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="E351" s="22">
         <f>IF(D351="?OLD","!!!","")</f>
@@ -14107,13 +14093,7 @@
     </row>
     <row r="352" spans="1:12">
       <c r="A352" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="B352" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="C352" s="21" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E352" s="22">
         <f>IF(D352="?OLD","!!!","")</f>
@@ -14147,7 +14127,7 @@
     </row>
     <row r="353" spans="1:12">
       <c r="A353" s="20" t="s">
-        <v>112</v>
+        <v>305</v>
       </c>
       <c r="E353" s="22">
         <f>IF(D353="?OLD","!!!","")</f>
@@ -14181,7 +14161,13 @@
     </row>
     <row r="354" spans="1:12">
       <c r="A354" s="20" t="s">
-        <v>303</v>
+        <v>306</v>
+      </c>
+      <c r="B354" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C354" s="21" t="s">
+        <v>307</v>
       </c>
       <c r="E354" s="22">
         <f>IF(D354="?OLD","!!!","")</f>
@@ -14215,7 +14201,7 @@
     </row>
     <row r="355" spans="1:12">
       <c r="A355" s="20" t="s">
-        <v>304</v>
+        <v>116</v>
       </c>
       <c r="E355" s="22">
         <f>IF(D355="?OLD","!!!","")</f>
@@ -14249,13 +14235,7 @@
     </row>
     <row r="356" spans="1:12">
       <c r="A356" s="20" t="s">
-        <v>305</v>
-      </c>
-      <c r="B356" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="C356" s="21" t="s">
-        <v>210</v>
+        <v>308</v>
       </c>
       <c r="E356" s="22">
         <f>IF(D356="?OLD","!!!","")</f>
@@ -14289,7 +14269,7 @@
     </row>
     <row r="357" spans="1:12">
       <c r="A357" s="20" t="s">
-        <v>71</v>
+        <v>309</v>
       </c>
       <c r="E357" s="22">
         <f>IF(D357="?OLD","!!!","")</f>
@@ -14323,7 +14303,13 @@
     </row>
     <row r="358" spans="1:12">
       <c r="A358" s="20" t="s">
-        <v>172</v>
+        <v>310</v>
+      </c>
+      <c r="B358" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C358" s="21" t="s">
+        <v>215</v>
       </c>
       <c r="E358" s="22">
         <f>IF(D358="?OLD","!!!","")</f>
@@ -14357,16 +14343,7 @@
     </row>
     <row r="359" spans="1:12">
       <c r="A359" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="B359" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="C359" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="D359" s="21" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="E359" s="22">
         <f>IF(D359="?OLD","!!!","")</f>
@@ -14400,13 +14377,7 @@
     </row>
     <row r="360" spans="1:12">
       <c r="A360" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="B360" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="C360" s="21" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="E360" s="22">
         <f>IF(D360="?OLD","!!!","")</f>
@@ -14440,7 +14411,16 @@
     </row>
     <row r="361" spans="1:12">
       <c r="A361" s="20" t="s">
-        <v>64</v>
+        <v>284</v>
+      </c>
+      <c r="B361" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="C361" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="D361" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E361" s="22">
         <f>IF(D361="?OLD","!!!","")</f>
@@ -14474,7 +14454,13 @@
     </row>
     <row r="362" spans="1:12">
       <c r="A362" s="20" t="s">
-        <v>278</v>
+        <v>285</v>
+      </c>
+      <c r="B362" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="C362" s="21" t="s">
+        <v>196</v>
       </c>
       <c r="E362" s="22">
         <f>IF(D362="?OLD","!!!","")</f>
@@ -14508,16 +14494,7 @@
     </row>
     <row r="363" spans="1:12">
       <c r="A363" s="20" t="s">
-        <v>306</v>
-      </c>
-      <c r="B363" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="C363" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="D363" s="21" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="E363" s="22">
         <f>IF(D363="?OLD","!!!","")</f>
@@ -14551,16 +14528,7 @@
     </row>
     <row r="364" spans="1:12">
       <c r="A364" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="B364" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C364" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="D364" s="21" t="s">
-        <v>108</v>
+        <v>283</v>
       </c>
       <c r="E364" s="22">
         <f>IF(D364="?OLD","!!!","")</f>
@@ -14594,7 +14562,16 @@
     </row>
     <row r="365" spans="1:12">
       <c r="A365" s="20" t="s">
-        <v>149</v>
+        <v>311</v>
+      </c>
+      <c r="B365" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="C365" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D365" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E365" s="22">
         <f>IF(D365="?OLD","!!!","")</f>
@@ -14628,7 +14605,16 @@
     </row>
     <row r="366" spans="1:12">
       <c r="A366" s="20" t="s">
-        <v>153</v>
+        <v>224</v>
+      </c>
+      <c r="B366" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C366" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="D366" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E366" s="22">
         <f>IF(D366="?OLD","!!!","")</f>
@@ -14662,16 +14648,7 @@
     </row>
     <row r="367" spans="1:12">
       <c r="A367" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="B367" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C367" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D367" s="21" t="s">
-        <v>108</v>
+        <v>154</v>
       </c>
       <c r="E367" s="22">
         <f>IF(D367="?OLD","!!!","")</f>
@@ -14705,7 +14682,7 @@
     </row>
     <row r="368" spans="1:12">
       <c r="A368" s="20" t="s">
-        <v>307</v>
+        <v>158</v>
       </c>
       <c r="E368" s="22">
         <f>IF(D368="?OLD","!!!","")</f>
@@ -14739,7 +14716,16 @@
     </row>
     <row r="369" spans="1:12">
       <c r="A369" s="20" t="s">
-        <v>138</v>
+        <v>117</v>
+      </c>
+      <c r="B369" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C369" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D369" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E369" s="22">
         <f>IF(D369="?OLD","!!!","")</f>
@@ -14772,93 +14758,93 @@
       <c r="L369" s="27"/>
     </row>
     <row r="370" spans="1:12">
-      <c r="A370" s="20"/>
+      <c r="A370" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="E370" s="22">
+        <f>IF(D370="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F370" s="23" t="str">
+        <f>IF(OR(E370="",E370="!!!"),"",IF(NOT(ISNA(VLOOKUP(E370,E$1:E369,1,FALSE()))),"OLD",IF(AND(E370&lt;&gt;"",E370&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G370" s="24" t="str">
+        <f>IF(OR(E370="",E370="!!!"),"",IF(OR(J370=0,AND(J370=1,K370=1),AND(J370=1,I370="SBJ"),AND(J370=1,I370=0)),"?IN_FOCUS",IF(J370&lt;=2,"?ACTIVATED",IF(J370&lt;&gt;"","?FAMILIAR",IF(F370="NEW",IF(ISNA(VLOOKUP(E370,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H370" s="25" t="str">
+        <f>IF(J370&lt;&gt;1,"",IF(I370="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I370" s="26" t="str">
+        <f>IF(OR(E370="",E370="!!!",F370="NEW"),"",INDEX(B369:B$2,-1+SUMPRODUCT(MAX(ROW(E369:E$2)*(E370=E369:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J370" s="26" t="str">
+        <f>IF(OR(E370="",E370="!!!",F370="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E370)*(E370=E$2:E370)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E369)*(E2=E$1:E369))))))</f>
+        <v> </v>
+      </c>
+      <c r="K370" s="26" t="str">
+        <f>IF(OR(E370="",E370="!!!",F370="NEW"),"",INDEX(J$1:J369,SUMPRODUCT(MAX(ROW(E$1:E369)*(E370=E$1:E369)))))</f>
+        <v> </v>
+      </c>
+      <c r="L370" s="27"/>
     </row>
     <row r="371" spans="1:12">
       <c r="A371" s="20" t="s">
-        <v>308</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="E371" s="22">
+        <f>IF(D371="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F371" s="23" t="str">
+        <f>IF(OR(E371="",E371="!!!"),"",IF(NOT(ISNA(VLOOKUP(E371,E$1:E370,1,FALSE()))),"OLD",IF(AND(E371&lt;&gt;"",E371&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G371" s="24" t="str">
+        <f>IF(OR(E371="",E371="!!!"),"",IF(OR(J371=0,AND(J371=1,K371=1),AND(J371=1,I371="SBJ"),AND(J371=1,I371=0)),"?IN_FOCUS",IF(J371&lt;=2,"?ACTIVATED",IF(J371&lt;&gt;"","?FAMILIAR",IF(F371="NEW",IF(ISNA(VLOOKUP(E371,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H371" s="25" t="str">
+        <f>IF(J371&lt;&gt;1,"",IF(I371="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I371" s="26" t="str">
+        <f>IF(OR(E371="",E371="!!!",F371="NEW"),"",INDEX(B370:B$2,-1+SUMPRODUCT(MAX(ROW(E370:E$2)*(E371=E370:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J371" s="26" t="str">
+        <f>IF(OR(E371="",E371="!!!",F371="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E371)*(E371=E$2:E371)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E370)*(E2=E$1:E370))))))</f>
+        <v> </v>
+      </c>
+      <c r="K371" s="26" t="str">
+        <f>IF(OR(E371="",E371="!!!",F371="NEW"),"",INDEX(J$1:J370,SUMPRODUCT(MAX(ROW(E$1:E370)*(E371=E$1:E370)))))</f>
+        <v> </v>
+      </c>
+      <c r="L371" s="27"/>
     </row>
     <row r="372" spans="1:12">
-      <c r="A372" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="B372" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="C372" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D372" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="E372" s="22">
-        <f>IF(D372="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F372" s="23" t="str">
-        <f>IF(OR(E372="",E372="!!!"),"",IF(NOT(ISNA(VLOOKUP(E372,E$1:E371,1,FALSE()))),"OLD",IF(AND(E372&lt;&gt;"",E372&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G372" s="24" t="str">
-        <f>IF(OR(E372="",E372="!!!"),"",IF(OR(J372=0,AND(J372=1,K372=1),AND(J372=1,I372="SBJ"),AND(J372=1,I372=0)),"?IN_FOCUS",IF(J372&lt;=2,"?ACTIVATED",IF(J372&lt;&gt;"","?FAMILIAR",IF(F372="NEW",IF(ISNA(VLOOKUP(E372,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H372" s="25" t="str">
-        <f>IF(J372&lt;&gt;1,"",IF(I372="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I372" s="26" t="str">
-        <f>IF(OR(E372="",E372="!!!",F372="NEW"),"",INDEX(B371:B$2,-1+SUMPRODUCT(MAX(ROW(E371:E$2)*(E372=E371:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J372" s="26" t="str">
-        <f>IF(OR(E372="",E372="!!!",F372="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E372)*(E372=E$2:E372)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E371)*(E2=E$1:E371))))))</f>
-        <v> </v>
-      </c>
-      <c r="K372" s="26" t="str">
-        <f>IF(OR(E372="",E372="!!!",F372="NEW"),"",INDEX(J$1:J371,SUMPRODUCT(MAX(ROW(E$1:E371)*(E372=E$1:E371)))))</f>
-        <v> </v>
-      </c>
-      <c r="L372" s="27"/>
+      <c r="A372" s="20"/>
     </row>
     <row r="373" spans="1:12">
       <c r="A373" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="E373" s="22">
-        <f>IF(D373="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F373" s="23" t="str">
-        <f>IF(OR(E373="",E373="!!!"),"",IF(NOT(ISNA(VLOOKUP(E373,E$1:E372,1,FALSE()))),"OLD",IF(AND(E373&lt;&gt;"",E373&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G373" s="24" t="str">
-        <f>IF(OR(E373="",E373="!!!"),"",IF(OR(J373=0,AND(J373=1,K373=1),AND(J373=1,I373="SBJ"),AND(J373=1,I373=0)),"?IN_FOCUS",IF(J373&lt;=2,"?ACTIVATED",IF(J373&lt;&gt;"","?FAMILIAR",IF(F373="NEW",IF(ISNA(VLOOKUP(E373,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H373" s="25" t="str">
-        <f>IF(J373&lt;&gt;1,"",IF(I373="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I373" s="26" t="str">
-        <f>IF(OR(E373="",E373="!!!",F373="NEW"),"",INDEX(B372:B$2,-1+SUMPRODUCT(MAX(ROW(E372:E$2)*(E373=E372:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J373" s="26" t="str">
-        <f>IF(OR(E373="",E373="!!!",F373="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E373)*(E373=E$2:E373)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E372)*(E2=E$1:E372))))))</f>
-        <v> </v>
-      </c>
-      <c r="K373" s="26" t="str">
-        <f>IF(OR(E373="",E373="!!!",F373="NEW"),"",INDEX(J$1:J372,SUMPRODUCT(MAX(ROW(E$1:E372)*(E373=E$1:E372)))))</f>
-        <v> </v>
-      </c>
-      <c r="L373" s="27"/>
+        <v>313</v>
+      </c>
     </row>
     <row r="374" spans="1:12">
       <c r="A374" s="20" t="s">
-        <v>240</v>
+        <v>129</v>
+      </c>
+      <c r="B374" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C374" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D374" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E374" s="22">
         <f>IF(D374="?OLD","!!!","")</f>
@@ -14892,7 +14878,7 @@
     </row>
     <row r="375" spans="1:12">
       <c r="A375" s="20" t="s">
-        <v>309</v>
+        <v>164</v>
       </c>
       <c r="E375" s="22">
         <f>IF(D375="?OLD","!!!","")</f>
@@ -14926,7 +14912,7 @@
     </row>
     <row r="376" spans="1:12">
       <c r="A376" s="20" t="s">
-        <v>150</v>
+        <v>245</v>
       </c>
       <c r="E376" s="22">
         <f>IF(D376="?OLD","!!!","")</f>
@@ -14960,7 +14946,7 @@
     </row>
     <row r="377" spans="1:12">
       <c r="A377" s="20" t="s">
-        <v>151</v>
+        <v>314</v>
       </c>
       <c r="E377" s="22">
         <f>IF(D377="?OLD","!!!","")</f>
@@ -14994,16 +14980,7 @@
     </row>
     <row r="378" spans="1:12">
       <c r="A378" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="B378" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="C378" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="D378" s="21" t="s">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="E378" s="22">
         <f>IF(D378="?OLD","!!!","")</f>
@@ -15037,7 +15014,7 @@
     </row>
     <row r="379" spans="1:12">
       <c r="A379" s="20" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="E379" s="22">
         <f>IF(D379="?OLD","!!!","")</f>
@@ -15071,13 +15048,16 @@
     </row>
     <row r="380" spans="1:12">
       <c r="A380" s="20" t="s">
-        <v>205</v>
+        <v>315</v>
       </c>
       <c r="B380" s="21" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="C380" s="21" t="s">
-        <v>302</v>
+        <v>201</v>
+      </c>
+      <c r="D380" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E380" s="22">
         <f>IF(D380="?OLD","!!!","")</f>
@@ -15111,16 +15091,7 @@
     </row>
     <row r="381" spans="1:12">
       <c r="A381" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="B381" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="C381" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D381" s="21" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="E381" s="22">
         <f>IF(D381="?OLD","!!!","")</f>
@@ -15154,7 +15125,13 @@
     </row>
     <row r="382" spans="1:12">
       <c r="A382" s="20" t="s">
-        <v>203</v>
+        <v>210</v>
+      </c>
+      <c r="B382" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="C382" s="21" t="s">
+        <v>307</v>
       </c>
       <c r="E382" s="22">
         <f>IF(D382="?OLD","!!!","")</f>
@@ -15188,7 +15165,16 @@
     </row>
     <row r="383" spans="1:12">
       <c r="A383" s="20" t="s">
-        <v>119</v>
+        <v>211</v>
+      </c>
+      <c r="B383" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="C383" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D383" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E383" s="22">
         <f>IF(D383="?OLD","!!!","")</f>
@@ -15222,7 +15208,7 @@
     </row>
     <row r="384" spans="1:12">
       <c r="A384" s="20" t="s">
-        <v>120</v>
+        <v>208</v>
       </c>
       <c r="E384" s="22">
         <f>IF(D384="?OLD","!!!","")</f>
@@ -15256,7 +15242,7 @@
     </row>
     <row r="385" spans="1:12">
       <c r="A385" s="20" t="s">
-        <v>311</v>
+        <v>123</v>
       </c>
       <c r="E385" s="22">
         <f>IF(D385="?OLD","!!!","")</f>
@@ -15290,7 +15276,7 @@
     </row>
     <row r="386" spans="1:12">
       <c r="A386" s="20" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="E386" s="22">
         <f>IF(D386="?OLD","!!!","")</f>
@@ -15324,7 +15310,7 @@
     </row>
     <row r="387" spans="1:12">
       <c r="A387" s="20" t="s">
-        <v>172</v>
+        <v>316</v>
       </c>
       <c r="E387" s="22">
         <f>IF(D387="?OLD","!!!","")</f>
@@ -15358,7 +15344,7 @@
     </row>
     <row r="388" spans="1:12">
       <c r="A388" s="20" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E388" s="22">
         <f>IF(D388="?OLD","!!!","")</f>
@@ -15392,7 +15378,7 @@
     </row>
     <row r="389" spans="1:12">
       <c r="A389" s="20" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="E389" s="22">
         <f>IF(D389="?OLD","!!!","")</f>
@@ -15426,16 +15412,7 @@
     </row>
     <row r="390" spans="1:12">
       <c r="A390" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="B390" s="21" t="s">
-        <v>284</v>
-      </c>
-      <c r="C390" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="D390" s="21" t="s">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="E390" s="22">
         <f>IF(D390="?OLD","!!!","")</f>
@@ -15469,7 +15446,7 @@
     </row>
     <row r="391" spans="1:12">
       <c r="A391" s="20" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E391" s="22">
         <f>IF(D391="?OLD","!!!","")</f>
@@ -15503,16 +15480,16 @@
     </row>
     <row r="392" spans="1:12">
       <c r="A392" s="20" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B392" s="21" t="s">
-        <v>313</v>
+        <v>289</v>
       </c>
       <c r="C392" s="21" t="s">
-        <v>124</v>
+        <v>201</v>
       </c>
       <c r="D392" s="21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E392" s="22">
         <f>IF(D392="?OLD","!!!","")</f>
@@ -15546,7 +15523,7 @@
     </row>
     <row r="393" spans="1:12">
       <c r="A393" s="20" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="E393" s="22">
         <f>IF(D393="?OLD","!!!","")</f>
@@ -15580,7 +15557,16 @@
     </row>
     <row r="394" spans="1:12">
       <c r="A394" s="20" t="s">
-        <v>314</v>
+        <v>317</v>
+      </c>
+      <c r="B394" s="21" t="s">
+        <v>318</v>
+      </c>
+      <c r="C394" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D394" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E394" s="22">
         <f>IF(D394="?OLD","!!!","")</f>
@@ -15614,16 +15600,7 @@
     </row>
     <row r="395" spans="1:12">
       <c r="A395" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="B395" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="C395" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D395" s="21" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="E395" s="22">
         <f>IF(D395="?OLD","!!!","")</f>
@@ -15657,7 +15634,7 @@
     </row>
     <row r="396" spans="1:12">
       <c r="A396" s="20" t="s">
-        <v>220</v>
+        <v>319</v>
       </c>
       <c r="E396" s="22">
         <f>IF(D396="?OLD","!!!","")</f>
@@ -15691,7 +15668,16 @@
     </row>
     <row r="397" spans="1:12">
       <c r="A397" s="20" t="s">
-        <v>315</v>
+        <v>224</v>
+      </c>
+      <c r="B397" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="C397" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D397" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E397" s="22">
         <f>IF(D397="?OLD","!!!","")</f>
@@ -15725,7 +15711,7 @@
     </row>
     <row r="398" spans="1:12">
       <c r="A398" s="20" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="E398" s="22">
         <f>IF(D398="?OLD","!!!","")</f>
@@ -15759,7 +15745,7 @@
     </row>
     <row r="399" spans="1:12">
       <c r="A399" s="20" t="s">
-        <v>12</v>
+        <v>320</v>
       </c>
       <c r="E399" s="22">
         <f>IF(D399="?OLD","!!!","")</f>
@@ -15793,13 +15779,7 @@
     </row>
     <row r="400" spans="1:12">
       <c r="A400" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="B400" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="C400" s="21" t="s">
-        <v>302</v>
+        <v>204</v>
       </c>
       <c r="E400" s="22">
         <f>IF(D400="?OLD","!!!","")</f>
@@ -15833,7 +15813,7 @@
     </row>
     <row r="401" spans="1:12">
       <c r="A401" s="20" t="s">
-        <v>316</v>
+        <v>12</v>
       </c>
       <c r="E401" s="22">
         <f>IF(D401="?OLD","!!!","")</f>
@@ -15867,7 +15847,13 @@
     </row>
     <row r="402" spans="1:12">
       <c r="A402" s="20" t="s">
-        <v>140</v>
+        <v>208</v>
+      </c>
+      <c r="B402" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="C402" s="21" t="s">
+        <v>307</v>
       </c>
       <c r="E402" s="22">
         <f>IF(D402="?OLD","!!!","")</f>
@@ -15901,7 +15887,7 @@
     </row>
     <row r="403" spans="1:12">
       <c r="A403" s="20" t="s">
-        <v>138</v>
+        <v>321</v>
       </c>
       <c r="E403" s="22">
         <f>IF(D403="?OLD","!!!","")</f>
@@ -15934,11 +15920,42 @@
       <c r="L403" s="27"/>
     </row>
     <row r="404" spans="1:12">
-      <c r="A404" s="20"/>
+      <c r="A404" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="E404" s="22">
+        <f>IF(D404="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F404" s="23" t="str">
+        <f>IF(OR(E404="",E404="!!!"),"",IF(NOT(ISNA(VLOOKUP(E404,E$1:E403,1,FALSE()))),"OLD",IF(AND(E404&lt;&gt;"",E404&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G404" s="24" t="str">
+        <f>IF(OR(E404="",E404="!!!"),"",IF(OR(J404=0,AND(J404=1,K404=1),AND(J404=1,I404="SBJ"),AND(J404=1,I404=0)),"?IN_FOCUS",IF(J404&lt;=2,"?ACTIVATED",IF(J404&lt;&gt;"","?FAMILIAR",IF(F404="NEW",IF(ISNA(VLOOKUP(E404,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H404" s="25" t="str">
+        <f>IF(J404&lt;&gt;1,"",IF(I404="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I404" s="26" t="str">
+        <f>IF(OR(E404="",E404="!!!",F404="NEW"),"",INDEX(B403:B$2,-1+SUMPRODUCT(MAX(ROW(E403:E$2)*(E404=E403:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J404" s="26" t="str">
+        <f>IF(OR(E404="",E404="!!!",F404="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E404)*(E404=E$2:E404)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E403)*(E2=E$1:E403))))))</f>
+        <v> </v>
+      </c>
+      <c r="K404" s="26" t="str">
+        <f>IF(OR(E404="",E404="!!!",F404="NEW"),"",INDEX(J$1:J403,SUMPRODUCT(MAX(ROW(E$1:E403)*(E404=E$1:E403)))))</f>
+        <v> </v>
+      </c>
+      <c r="L404" s="27"/>
     </row>
     <row r="405" spans="1:12">
       <c r="A405" s="20" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="E405" s="22">
         <f>IF(D405="?OLD","!!!","")</f>
@@ -15971,13 +15988,11 @@
       <c r="L405" s="27"/>
     </row>
     <row r="406" spans="1:12">
-      <c r="A406" s="20" t="s">
-        <v>317</v>
-      </c>
+      <c r="A406" s="20"/>
     </row>
     <row r="407" spans="1:12">
       <c r="A407" s="20" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E407" s="22">
         <f>IF(D407="?OLD","!!!","")</f>
@@ -16011,50 +16026,12 @@
     </row>
     <row r="408" spans="1:12">
       <c r="A408" s="20" t="s">
-        <v>245</v>
-      </c>
-      <c r="B408" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="C408" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="D408" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="E408" s="22">
-        <f>IF(D408="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F408" s="23" t="str">
-        <f>IF(OR(E408="",E408="!!!"),"",IF(NOT(ISNA(VLOOKUP(E408,E$1:E407,1,FALSE()))),"OLD",IF(AND(E408&lt;&gt;"",E408&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G408" s="24" t="str">
-        <f>IF(OR(E408="",E408="!!!"),"",IF(OR(J408=0,AND(J408=1,K408=1),AND(J408=1,I408="SBJ"),AND(J408=1,I408=0)),"?IN_FOCUS",IF(J408&lt;=2,"?ACTIVATED",IF(J408&lt;&gt;"","?FAMILIAR",IF(F408="NEW",IF(ISNA(VLOOKUP(E408,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H408" s="25" t="str">
-        <f>IF(J408&lt;&gt;1,"",IF(I408="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I408" s="26" t="str">
-        <f>IF(OR(E408="",E408="!!!",F408="NEW"),"",INDEX(B407:B$2,-1+SUMPRODUCT(MAX(ROW(E407:E$2)*(E408=E407:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J408" s="26" t="str">
-        <f>IF(OR(E408="",E408="!!!",F408="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E408)*(E408=E$2:E408)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E407)*(E2=E$1:E407))))))</f>
-        <v> </v>
-      </c>
-      <c r="K408" s="26" t="str">
-        <f>IF(OR(E408="",E408="!!!",F408="NEW"),"",INDEX(J$1:J407,SUMPRODUCT(MAX(ROW(E$1:E407)*(E408=E$1:E407)))))</f>
-        <v> </v>
-      </c>
-      <c r="L408" s="27"/>
+        <v>322</v>
+      </c>
     </row>
     <row r="409" spans="1:12">
       <c r="A409" s="20" t="s">
-        <v>318</v>
+        <v>189</v>
       </c>
       <c r="E409" s="22">
         <f>IF(D409="?OLD","!!!","")</f>
@@ -16088,13 +16065,16 @@
     </row>
     <row r="410" spans="1:12">
       <c r="A410" s="20" t="s">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="B410" s="21" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C410" s="21" t="s">
-        <v>191</v>
+        <v>201</v>
+      </c>
+      <c r="D410" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E410" s="22">
         <f>IF(D410="?OLD","!!!","")</f>
@@ -16128,7 +16108,7 @@
     </row>
     <row r="411" spans="1:12">
       <c r="A411" s="20" t="s">
-        <v>112</v>
+        <v>323</v>
       </c>
       <c r="E411" s="22">
         <f>IF(D411="?OLD","!!!","")</f>
@@ -16162,16 +16142,13 @@
     </row>
     <row r="412" spans="1:12">
       <c r="A412" s="20" t="s">
-        <v>319</v>
+        <v>185</v>
       </c>
       <c r="B412" s="21" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="C412" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="D412" s="21" t="s">
-        <v>108</v>
+        <v>196</v>
       </c>
       <c r="E412" s="22">
         <f>IF(D412="?OLD","!!!","")</f>
@@ -16205,7 +16182,7 @@
     </row>
     <row r="413" spans="1:12">
       <c r="A413" s="20" t="s">
-        <v>150</v>
+        <v>116</v>
       </c>
       <c r="E413" s="22">
         <f>IF(D413="?OLD","!!!","")</f>
@@ -16239,10 +16216,16 @@
     </row>
     <row r="414" spans="1:12">
       <c r="A414" s="20" t="s">
-        <v>160</v>
+        <v>324</v>
       </c>
       <c r="B414" s="21" t="s">
-        <v>313</v>
+        <v>118</v>
+      </c>
+      <c r="C414" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="D414" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E414" s="22">
         <f>IF(D414="?OLD","!!!","")</f>
@@ -16276,13 +16259,7 @@
     </row>
     <row r="415" spans="1:12">
       <c r="A415" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="B415" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="C415" s="21" t="s">
-        <v>210</v>
+        <v>155</v>
       </c>
       <c r="E415" s="22">
         <f>IF(D415="?OLD","!!!","")</f>
@@ -16316,7 +16293,10 @@
     </row>
     <row r="416" spans="1:12">
       <c r="A416" s="20" t="s">
-        <v>130</v>
+        <v>165</v>
+      </c>
+      <c r="B416" s="21" t="s">
+        <v>318</v>
       </c>
       <c r="E416" s="22">
         <f>IF(D416="?OLD","!!!","")</f>
@@ -16350,16 +16330,13 @@
     </row>
     <row r="417" spans="1:12">
       <c r="A417" s="20" t="s">
-        <v>109</v>
+        <v>197</v>
       </c>
       <c r="B417" s="21" t="s">
-        <v>118</v>
+        <v>290</v>
       </c>
       <c r="C417" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D417" s="21" t="s">
-        <v>108</v>
+        <v>215</v>
       </c>
       <c r="E417" s="22">
         <f>IF(D417="?OLD","!!!","")</f>
@@ -16393,7 +16370,7 @@
     </row>
     <row r="418" spans="1:12">
       <c r="A418" s="20" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E418" s="22">
         <f>IF(D418="?OLD","!!!","")</f>
@@ -16427,16 +16404,16 @@
     </row>
     <row r="419" spans="1:12">
       <c r="A419" s="20" t="s">
-        <v>219</v>
+        <v>113</v>
       </c>
       <c r="B419" s="21" t="s">
-        <v>285</v>
+        <v>122</v>
       </c>
       <c r="C419" s="21" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D419" s="21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E419" s="22">
         <f>IF(D419="?OLD","!!!","")</f>
@@ -16470,7 +16447,7 @@
     </row>
     <row r="420" spans="1:12">
       <c r="A420" s="20" t="s">
-        <v>192</v>
+        <v>135</v>
       </c>
       <c r="E420" s="22">
         <f>IF(D420="?OLD","!!!","")</f>
@@ -16504,7 +16481,16 @@
     </row>
     <row r="421" spans="1:12">
       <c r="A421" s="20" t="s">
-        <v>320</v>
+        <v>224</v>
+      </c>
+      <c r="B421" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="C421" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D421" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E421" s="22">
         <f>IF(D421="?OLD","!!!","")</f>
@@ -16538,7 +16524,7 @@
     </row>
     <row r="422" spans="1:12">
       <c r="A422" s="20" t="s">
-        <v>150</v>
+        <v>197</v>
       </c>
       <c r="E422" s="22">
         <f>IF(D422="?OLD","!!!","")</f>
@@ -16572,7 +16558,7 @@
     </row>
     <row r="423" spans="1:12">
       <c r="A423" s="20" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E423" s="22">
         <f>IF(D423="?OLD","!!!","")</f>
@@ -16606,7 +16592,7 @@
     </row>
     <row r="424" spans="1:12">
       <c r="A424" s="20" t="s">
-        <v>322</v>
+        <v>155</v>
       </c>
       <c r="E424" s="22">
         <f>IF(D424="?OLD","!!!","")</f>
@@ -16640,7 +16626,7 @@
     </row>
     <row r="425" spans="1:12">
       <c r="A425" s="20" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E425" s="22">
         <f>IF(D425="?OLD","!!!","")</f>
@@ -16674,16 +16660,7 @@
     </row>
     <row r="426" spans="1:12">
       <c r="A426" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="B426" s="21" t="s">
-        <v>284</v>
-      </c>
-      <c r="C426" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="D426" s="21" t="s">
-        <v>108</v>
+        <v>327</v>
       </c>
       <c r="E426" s="22">
         <f>IF(D426="?OLD","!!!","")</f>
@@ -16717,16 +16694,7 @@
     </row>
     <row r="427" spans="1:12">
       <c r="A427" s="20" t="s">
-        <v>319</v>
-      </c>
-      <c r="B427" s="21" t="s">
-        <v>313</v>
-      </c>
-      <c r="C427" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="D427" s="21" t="s">
-        <v>108</v>
+        <v>328</v>
       </c>
       <c r="E427" s="22">
         <f>IF(D427="?OLD","!!!","")</f>
@@ -16760,7 +16728,16 @@
     </row>
     <row r="428" spans="1:12">
       <c r="A428" s="20" t="s">
-        <v>220</v>
+        <v>288</v>
+      </c>
+      <c r="B428" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="C428" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="D428" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E428" s="22">
         <f>IF(D428="?OLD","!!!","")</f>
@@ -16794,7 +16771,16 @@
     </row>
     <row r="429" spans="1:12">
       <c r="A429" s="20" t="s">
-        <v>128</v>
+        <v>324</v>
+      </c>
+      <c r="B429" s="21" t="s">
+        <v>318</v>
+      </c>
+      <c r="C429" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="D429" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E429" s="22">
         <f>IF(D429="?OLD","!!!","")</f>
@@ -16828,16 +16814,7 @@
     </row>
     <row r="430" spans="1:12">
       <c r="A430" s="20" t="s">
-        <v>324</v>
-      </c>
-      <c r="B430" s="21" t="s">
-        <v>259</v>
-      </c>
-      <c r="C430" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D430" s="21" t="s">
-        <v>108</v>
+        <v>225</v>
       </c>
       <c r="E430" s="22">
         <f>IF(D430="?OLD","!!!","")</f>
@@ -16871,7 +16848,7 @@
     </row>
     <row r="431" spans="1:12">
       <c r="A431" s="20" t="s">
-        <v>325</v>
+        <v>132</v>
       </c>
       <c r="E431" s="22">
         <f>IF(D431="?OLD","!!!","")</f>
@@ -16905,16 +16882,16 @@
     </row>
     <row r="432" spans="1:12">
       <c r="A432" s="20" t="s">
-        <v>283</v>
+        <v>329</v>
       </c>
       <c r="B432" s="21" t="s">
-        <v>326</v>
+        <v>264</v>
       </c>
       <c r="C432" s="21" t="s">
-        <v>165</v>
+        <v>128</v>
       </c>
       <c r="D432" s="21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E432" s="22">
         <f>IF(D432="?OLD","!!!","")</f>
@@ -16948,7 +16925,7 @@
     </row>
     <row r="433" spans="1:12">
       <c r="A433" s="20" t="s">
-        <v>182</v>
+        <v>330</v>
       </c>
       <c r="E433" s="22">
         <f>IF(D433="?OLD","!!!","")</f>
@@ -16982,7 +16959,16 @@
     </row>
     <row r="434" spans="1:12">
       <c r="A434" s="20" t="s">
-        <v>327</v>
+        <v>288</v>
+      </c>
+      <c r="B434" s="21" t="s">
+        <v>331</v>
+      </c>
+      <c r="C434" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="D434" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E434" s="22">
         <f>IF(D434="?OLD","!!!","")</f>
@@ -17016,7 +17002,7 @@
     </row>
     <row r="435" spans="1:12">
       <c r="A435" s="20" t="s">
-        <v>328</v>
+        <v>187</v>
       </c>
       <c r="E435" s="22">
         <f>IF(D435="?OLD","!!!","")</f>
@@ -17050,16 +17036,7 @@
     </row>
     <row r="436" spans="1:12">
       <c r="A436" s="20" t="s">
-        <v>329</v>
-      </c>
-      <c r="B436" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="C436" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="D436" s="21" t="s">
-        <v>108</v>
+        <v>332</v>
       </c>
       <c r="E436" s="22">
         <f>IF(D436="?OLD","!!!","")</f>
@@ -17093,7 +17070,7 @@
     </row>
     <row r="437" spans="1:12">
       <c r="A437" s="20" t="s">
-        <v>150</v>
+        <v>333</v>
       </c>
       <c r="E437" s="22">
         <f>IF(D437="?OLD","!!!","")</f>
@@ -17127,16 +17104,16 @@
     </row>
     <row r="438" spans="1:12">
       <c r="A438" s="20" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B438" s="21" t="s">
-        <v>326</v>
+        <v>290</v>
       </c>
       <c r="C438" s="21" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="D438" s="21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E438" s="22">
         <f>IF(D438="?OLD","!!!","")</f>
@@ -17170,13 +17147,7 @@
     </row>
     <row r="439" spans="1:12">
       <c r="A439" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="B439" s="21" t="s">
-        <v>259</v>
-      </c>
-      <c r="C439" s="21" t="s">
-        <v>210</v>
+        <v>155</v>
       </c>
       <c r="E439" s="22">
         <f>IF(D439="?OLD","!!!","")</f>
@@ -17210,7 +17181,16 @@
     </row>
     <row r="440" spans="1:12">
       <c r="A440" s="20" t="s">
-        <v>266</v>
+        <v>335</v>
+      </c>
+      <c r="B440" s="21" t="s">
+        <v>331</v>
+      </c>
+      <c r="C440" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D440" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E440" s="22">
         <f>IF(D440="?OLD","!!!","")</f>
@@ -17244,7 +17224,13 @@
     </row>
     <row r="441" spans="1:12">
       <c r="A441" s="20" t="s">
-        <v>331</v>
+        <v>197</v>
+      </c>
+      <c r="B441" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="C441" s="21" t="s">
+        <v>215</v>
       </c>
       <c r="E441" s="22">
         <f>IF(D441="?OLD","!!!","")</f>
@@ -17278,13 +17264,7 @@
     </row>
     <row r="442" spans="1:12">
       <c r="A442" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="B442" s="21" t="s">
-        <v>256</v>
-      </c>
-      <c r="C442" s="21" t="s">
-        <v>136</v>
+        <v>271</v>
       </c>
       <c r="E442" s="22">
         <f>IF(D442="?OLD","!!!","")</f>
@@ -17318,7 +17298,7 @@
     </row>
     <row r="443" spans="1:12">
       <c r="A443" s="20" t="s">
-        <v>112</v>
+        <v>336</v>
       </c>
       <c r="E443" s="22">
         <f>IF(D443="?OLD","!!!","")</f>
@@ -17355,10 +17335,10 @@
         <v>113</v>
       </c>
       <c r="B444" s="21" t="s">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="C444" s="21" t="s">
-        <v>191</v>
+        <v>141</v>
       </c>
       <c r="E444" s="22">
         <f>IF(D444="?OLD","!!!","")</f>
@@ -17392,7 +17372,7 @@
     </row>
     <row r="445" spans="1:12">
       <c r="A445" s="20" t="s">
-        <v>192</v>
+        <v>116</v>
       </c>
       <c r="E445" s="22">
         <f>IF(D445="?OLD","!!!","")</f>
@@ -17426,7 +17406,13 @@
     </row>
     <row r="446" spans="1:12">
       <c r="A446" s="20" t="s">
-        <v>332</v>
+        <v>117</v>
+      </c>
+      <c r="B446" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="C446" s="21" t="s">
+        <v>196</v>
       </c>
       <c r="E446" s="22">
         <f>IF(D446="?OLD","!!!","")</f>
@@ -17460,7 +17446,7 @@
     </row>
     <row r="447" spans="1:12">
       <c r="A447" s="20" t="s">
-        <v>333</v>
+        <v>197</v>
       </c>
       <c r="E447" s="22">
         <f>IF(D447="?OLD","!!!","")</f>
@@ -17494,7 +17480,7 @@
     </row>
     <row r="448" spans="1:12">
       <c r="A448" s="20" t="s">
-        <v>184</v>
+        <v>337</v>
       </c>
       <c r="E448" s="22">
         <f>IF(D448="?OLD","!!!","")</f>
@@ -17528,7 +17514,7 @@
     </row>
     <row r="449" spans="1:12">
       <c r="A449" s="20" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="E449" s="22">
         <f>IF(D449="?OLD","!!!","")</f>
@@ -17562,7 +17548,7 @@
     </row>
     <row r="450" spans="1:12">
       <c r="A450" s="20" t="s">
-        <v>130</v>
+        <v>189</v>
       </c>
       <c r="E450" s="22">
         <f>IF(D450="?OLD","!!!","")</f>
@@ -17596,16 +17582,7 @@
     </row>
     <row r="451" spans="1:12">
       <c r="A451" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="B451" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="C451" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D451" s="21" t="s">
-        <v>108</v>
+        <v>339</v>
       </c>
       <c r="E451" s="22">
         <f>IF(D451="?OLD","!!!","")</f>
@@ -17639,7 +17616,7 @@
     </row>
     <row r="452" spans="1:12">
       <c r="A452" s="20" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E452" s="22">
         <f>IF(D452="?OLD","!!!","")</f>
@@ -17672,93 +17649,102 @@
       <c r="L452" s="27"/>
     </row>
     <row r="453" spans="1:12">
-      <c r="A453" s="20"/>
+      <c r="A453" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="B453" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C453" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D453" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="E453" s="22">
+        <f>IF(D453="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F453" s="23" t="str">
+        <f>IF(OR(E453="",E453="!!!"),"",IF(NOT(ISNA(VLOOKUP(E453,E$1:E452,1,FALSE()))),"OLD",IF(AND(E453&lt;&gt;"",E453&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G453" s="24" t="str">
+        <f>IF(OR(E453="",E453="!!!"),"",IF(OR(J453=0,AND(J453=1,K453=1),AND(J453=1,I453="SBJ"),AND(J453=1,I453=0)),"?IN_FOCUS",IF(J453&lt;=2,"?ACTIVATED",IF(J453&lt;&gt;"","?FAMILIAR",IF(F453="NEW",IF(ISNA(VLOOKUP(E453,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H453" s="25" t="str">
+        <f>IF(J453&lt;&gt;1,"",IF(I453="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I453" s="26" t="str">
+        <f>IF(OR(E453="",E453="!!!",F453="NEW"),"",INDEX(B452:B$2,-1+SUMPRODUCT(MAX(ROW(E452:E$2)*(E453=E452:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J453" s="26" t="str">
+        <f>IF(OR(E453="",E453="!!!",F453="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E453)*(E453=E$2:E453)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E452)*(E2=E$1:E452))))))</f>
+        <v> </v>
+      </c>
+      <c r="K453" s="26" t="str">
+        <f>IF(OR(E453="",E453="!!!",F453="NEW"),"",INDEX(J$1:J452,SUMPRODUCT(MAX(ROW(E$1:E452)*(E453=E$1:E452)))))</f>
+        <v> </v>
+      </c>
+      <c r="L453" s="27"/>
     </row>
     <row r="454" spans="1:12">
       <c r="A454" s="20" t="s">
-        <v>335</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="E454" s="22">
+        <f>IF(D454="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F454" s="23" t="str">
+        <f>IF(OR(E454="",E454="!!!"),"",IF(NOT(ISNA(VLOOKUP(E454,E$1:E453,1,FALSE()))),"OLD",IF(AND(E454&lt;&gt;"",E454&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G454" s="24" t="str">
+        <f>IF(OR(E454="",E454="!!!"),"",IF(OR(J454=0,AND(J454=1,K454=1),AND(J454=1,I454="SBJ"),AND(J454=1,I454=0)),"?IN_FOCUS",IF(J454&lt;=2,"?ACTIVATED",IF(J454&lt;&gt;"","?FAMILIAR",IF(F454="NEW",IF(ISNA(VLOOKUP(E454,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H454" s="25" t="str">
+        <f>IF(J454&lt;&gt;1,"",IF(I454="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I454" s="26" t="str">
+        <f>IF(OR(E454="",E454="!!!",F454="NEW"),"",INDEX(B453:B$2,-1+SUMPRODUCT(MAX(ROW(E453:E$2)*(E454=E453:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J454" s="26" t="str">
+        <f>IF(OR(E454="",E454="!!!",F454="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E454)*(E454=E$2:E454)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E453)*(E2=E$1:E453))))))</f>
+        <v> </v>
+      </c>
+      <c r="K454" s="26" t="str">
+        <f>IF(OR(E454="",E454="!!!",F454="NEW"),"",INDEX(J$1:J453,SUMPRODUCT(MAX(ROW(E$1:E453)*(E454=E$1:E453)))))</f>
+        <v> </v>
+      </c>
+      <c r="L454" s="27"/>
     </row>
     <row r="455" spans="1:12">
-      <c r="A455" s="20" t="s">
-        <v>245</v>
-      </c>
-      <c r="B455" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="C455" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="D455" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="E455" s="22">
-        <f>IF(D455="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F455" s="23" t="str">
-        <f>IF(OR(E455="",E455="!!!"),"",IF(NOT(ISNA(VLOOKUP(E455,E$1:E454,1,FALSE()))),"OLD",IF(AND(E455&lt;&gt;"",E455&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G455" s="24" t="str">
-        <f>IF(OR(E455="",E455="!!!"),"",IF(OR(J455=0,AND(J455=1,K455=1),AND(J455=1,I455="SBJ"),AND(J455=1,I455=0)),"?IN_FOCUS",IF(J455&lt;=2,"?ACTIVATED",IF(J455&lt;&gt;"","?FAMILIAR",IF(F455="NEW",IF(ISNA(VLOOKUP(E455,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H455" s="25" t="str">
-        <f>IF(J455&lt;&gt;1,"",IF(I455="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I455" s="26" t="str">
-        <f>IF(OR(E455="",E455="!!!",F455="NEW"),"",INDEX(B454:B$2,-1+SUMPRODUCT(MAX(ROW(E454:E$2)*(E455=E454:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J455" s="26" t="str">
-        <f>IF(OR(E455="",E455="!!!",F455="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E455)*(E455=E$2:E455)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E454)*(E2=E$1:E454))))))</f>
-        <v> </v>
-      </c>
-      <c r="K455" s="26" t="str">
-        <f>IF(OR(E455="",E455="!!!",F455="NEW"),"",INDEX(J$1:J454,SUMPRODUCT(MAX(ROW(E$1:E454)*(E455=E$1:E454)))))</f>
-        <v> </v>
-      </c>
-      <c r="L455" s="27"/>
+      <c r="A455" s="20"/>
     </row>
     <row r="456" spans="1:12">
       <c r="A456" s="20" t="s">
-        <v>336</v>
-      </c>
-      <c r="E456" s="22">
-        <f>IF(D456="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F456" s="23" t="str">
-        <f>IF(OR(E456="",E456="!!!"),"",IF(NOT(ISNA(VLOOKUP(E456,E$1:E455,1,FALSE()))),"OLD",IF(AND(E456&lt;&gt;"",E456&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G456" s="24" t="str">
-        <f>IF(OR(E456="",E456="!!!"),"",IF(OR(J456=0,AND(J456=1,K456=1),AND(J456=1,I456="SBJ"),AND(J456=1,I456=0)),"?IN_FOCUS",IF(J456&lt;=2,"?ACTIVATED",IF(J456&lt;&gt;"","?FAMILIAR",IF(F456="NEW",IF(ISNA(VLOOKUP(E456,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H456" s="25" t="str">
-        <f>IF(J456&lt;&gt;1,"",IF(I456="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I456" s="26" t="str">
-        <f>IF(OR(E456="",E456="!!!",F456="NEW"),"",INDEX(B455:B$2,-1+SUMPRODUCT(MAX(ROW(E455:E$2)*(E456=E455:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J456" s="26" t="str">
-        <f>IF(OR(E456="",E456="!!!",F456="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E456)*(E456=E$2:E456)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E455)*(E2=E$1:E455))))))</f>
-        <v> </v>
-      </c>
-      <c r="K456" s="26" t="str">
-        <f>IF(OR(E456="",E456="!!!",F456="NEW"),"",INDEX(J$1:J455,SUMPRODUCT(MAX(ROW(E$1:E455)*(E456=E$1:E455)))))</f>
-        <v> </v>
-      </c>
-      <c r="L456" s="27"/>
+        <v>340</v>
+      </c>
     </row>
     <row r="457" spans="1:12">
       <c r="A457" s="20" t="s">
-        <v>166</v>
+        <v>250</v>
+      </c>
+      <c r="B457" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C457" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="D457" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E457" s="22">
         <f>IF(D457="?OLD","!!!","")</f>
@@ -17792,7 +17778,7 @@
     </row>
     <row r="458" spans="1:12">
       <c r="A458" s="20" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E458" s="22">
         <f>IF(D458="?OLD","!!!","")</f>
@@ -17826,13 +17812,7 @@
     </row>
     <row r="459" spans="1:12">
       <c r="A459" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="B459" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="C459" s="21" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E459" s="22">
         <f>IF(D459="?OLD","!!!","")</f>
@@ -17866,7 +17846,7 @@
     </row>
     <row r="460" spans="1:12">
       <c r="A460" s="20" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E460" s="22">
         <f>IF(D460="?OLD","!!!","")</f>
@@ -17900,7 +17880,13 @@
     </row>
     <row r="461" spans="1:12">
       <c r="A461" s="20" t="s">
-        <v>339</v>
+        <v>173</v>
+      </c>
+      <c r="B461" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C461" s="21" t="s">
+        <v>174</v>
       </c>
       <c r="E461" s="22">
         <f>IF(D461="?OLD","!!!","")</f>
@@ -17934,7 +17920,7 @@
     </row>
     <row r="462" spans="1:12">
       <c r="A462" s="20" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E462" s="22">
         <f>IF(D462="?OLD","!!!","")</f>
@@ -17968,7 +17954,7 @@
     </row>
     <row r="463" spans="1:12">
       <c r="A463" s="20" t="s">
-        <v>150</v>
+        <v>344</v>
       </c>
       <c r="E463" s="22">
         <f>IF(D463="?OLD","!!!","")</f>
@@ -18002,7 +17988,7 @@
     </row>
     <row r="464" spans="1:12">
       <c r="A464" s="20" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E464" s="22">
         <f>IF(D464="?OLD","!!!","")</f>
@@ -18036,16 +18022,7 @@
     </row>
     <row r="465" spans="1:12">
       <c r="A465" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="B465" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="C465" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="D465" s="21" t="s">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="E465" s="22">
         <f>IF(D465="?OLD","!!!","")</f>
@@ -18079,7 +18056,7 @@
     </row>
     <row r="466" spans="1:12">
       <c r="A466" s="20" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="E466" s="22">
         <f>IF(D466="?OLD","!!!","")</f>
@@ -18113,7 +18090,16 @@
     </row>
     <row r="467" spans="1:12">
       <c r="A467" s="20" t="s">
-        <v>343</v>
+        <v>288</v>
+      </c>
+      <c r="B467" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="C467" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="D467" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E467" s="22">
         <f>IF(D467="?OLD","!!!","")</f>
@@ -18147,7 +18133,7 @@
     </row>
     <row r="468" spans="1:12">
       <c r="A468" s="20" t="s">
-        <v>150</v>
+        <v>347</v>
       </c>
       <c r="E468" s="22">
         <f>IF(D468="?OLD","!!!","")</f>
@@ -18181,7 +18167,7 @@
     </row>
     <row r="469" spans="1:12">
       <c r="A469" s="20" t="s">
-        <v>151</v>
+        <v>348</v>
       </c>
       <c r="E469" s="22">
         <f>IF(D469="?OLD","!!!","")</f>
@@ -18215,16 +18201,7 @@
     </row>
     <row r="470" spans="1:12">
       <c r="A470" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="B470" s="21" t="s">
-        <v>284</v>
-      </c>
-      <c r="C470" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="D470" s="21" t="s">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="E470" s="22">
         <f>IF(D470="?OLD","!!!","")</f>
@@ -18258,7 +18235,7 @@
     </row>
     <row r="471" spans="1:12">
       <c r="A471" s="20" t="s">
-        <v>112</v>
+        <v>156</v>
       </c>
       <c r="E471" s="22">
         <f>IF(D471="?OLD","!!!","")</f>
@@ -18292,16 +18269,16 @@
     </row>
     <row r="472" spans="1:12">
       <c r="A472" s="20" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="B472" s="21" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C472" s="21" t="s">
-        <v>275</v>
+        <v>170</v>
       </c>
       <c r="D472" s="21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E472" s="22">
         <f>IF(D472="?OLD","!!!","")</f>
@@ -18335,13 +18312,7 @@
     </row>
     <row r="473" spans="1:12">
       <c r="A473" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="B473" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="C473" s="21" t="s">
-        <v>191</v>
+        <v>116</v>
       </c>
       <c r="E473" s="22">
         <f>IF(D473="?OLD","!!!","")</f>
@@ -18375,7 +18346,16 @@
     </row>
     <row r="474" spans="1:12">
       <c r="A474" s="20" t="s">
-        <v>133</v>
+        <v>284</v>
+      </c>
+      <c r="B474" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="C474" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="D474" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E474" s="22">
         <f>IF(D474="?OLD","!!!","")</f>
@@ -18409,7 +18389,13 @@
     </row>
     <row r="475" spans="1:12">
       <c r="A475" s="20" t="s">
-        <v>344</v>
+        <v>117</v>
+      </c>
+      <c r="B475" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="C475" s="21" t="s">
+        <v>196</v>
       </c>
       <c r="E475" s="22">
         <f>IF(D475="?OLD","!!!","")</f>
@@ -18443,13 +18429,7 @@
     </row>
     <row r="476" spans="1:12">
       <c r="A476" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="B476" s="21" t="s">
-        <v>284</v>
-      </c>
-      <c r="C476" s="21" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E476" s="22">
         <f>IF(D476="?OLD","!!!","")</f>
@@ -18483,7 +18463,7 @@
     </row>
     <row r="477" spans="1:12">
       <c r="A477" s="20" t="s">
-        <v>142</v>
+        <v>349</v>
       </c>
       <c r="E477" s="22">
         <f>IF(D477="?OLD","!!!","")</f>
@@ -18517,7 +18497,13 @@
     </row>
     <row r="478" spans="1:12">
       <c r="A478" s="20" t="s">
-        <v>64</v>
+        <v>113</v>
+      </c>
+      <c r="B478" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="C478" s="21" t="s">
+        <v>141</v>
       </c>
       <c r="E478" s="22">
         <f>IF(D478="?OLD","!!!","")</f>
@@ -18551,7 +18537,7 @@
     </row>
     <row r="479" spans="1:12">
       <c r="A479" s="20" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="E479" s="22">
         <f>IF(D479="?OLD","!!!","")</f>
@@ -18585,16 +18571,7 @@
     </row>
     <row r="480" spans="1:12">
       <c r="A480" s="20" t="s">
-        <v>345</v>
-      </c>
-      <c r="B480" s="21" t="s">
-        <v>256</v>
-      </c>
-      <c r="C480" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="D480" s="21" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="E480" s="22">
         <f>IF(D480="?OLD","!!!","")</f>
@@ -18628,16 +18605,7 @@
     </row>
     <row r="481" spans="1:12">
       <c r="A481" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="B481" s="21" t="s">
-        <v>346</v>
-      </c>
-      <c r="C481" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="D481" s="21" t="s">
-        <v>108</v>
+        <v>177</v>
       </c>
       <c r="E481" s="22">
         <f>IF(D481="?OLD","!!!","")</f>
@@ -18671,7 +18639,16 @@
     </row>
     <row r="482" spans="1:12">
       <c r="A482" s="20" t="s">
-        <v>347</v>
+        <v>350</v>
+      </c>
+      <c r="B482" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="C482" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D482" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E482" s="22">
         <f>IF(D482="?OLD","!!!","")</f>
@@ -18705,7 +18682,16 @@
     </row>
     <row r="483" spans="1:12">
       <c r="A483" s="20" t="s">
-        <v>343</v>
+        <v>224</v>
+      </c>
+      <c r="B483" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="C483" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="D483" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E483" s="22">
         <f>IF(D483="?OLD","!!!","")</f>
@@ -18739,7 +18725,7 @@
     </row>
     <row r="484" spans="1:12">
       <c r="A484" s="20" t="s">
-        <v>138</v>
+        <v>352</v>
       </c>
       <c r="E484" s="22">
         <f>IF(D484="?OLD","!!!","")</f>
@@ -18772,84 +18758,84 @@
       <c r="L484" s="27"/>
     </row>
     <row r="485" spans="1:12">
-      <c r="A485" s="20"/>
+      <c r="A485" s="20" t="s">
+        <v>348</v>
+      </c>
+      <c r="E485" s="22">
+        <f>IF(D485="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F485" s="23" t="str">
+        <f>IF(OR(E485="",E485="!!!"),"",IF(NOT(ISNA(VLOOKUP(E485,E$1:E484,1,FALSE()))),"OLD",IF(AND(E485&lt;&gt;"",E485&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G485" s="24" t="str">
+        <f>IF(OR(E485="",E485="!!!"),"",IF(OR(J485=0,AND(J485=1,K485=1),AND(J485=1,I485="SBJ"),AND(J485=1,I485=0)),"?IN_FOCUS",IF(J485&lt;=2,"?ACTIVATED",IF(J485&lt;&gt;"","?FAMILIAR",IF(F485="NEW",IF(ISNA(VLOOKUP(E485,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H485" s="25" t="str">
+        <f>IF(J485&lt;&gt;1,"",IF(I485="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I485" s="26" t="str">
+        <f>IF(OR(E485="",E485="!!!",F485="NEW"),"",INDEX(B484:B$2,-1+SUMPRODUCT(MAX(ROW(E484:E$2)*(E485=E484:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J485" s="26" t="str">
+        <f>IF(OR(E485="",E485="!!!",F485="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E485)*(E485=E$2:E485)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E484)*(E2=E$1:E484))))))</f>
+        <v> </v>
+      </c>
+      <c r="K485" s="26" t="str">
+        <f>IF(OR(E485="",E485="!!!",F485="NEW"),"",INDEX(J$1:J484,SUMPRODUCT(MAX(ROW(E$1:E484)*(E485=E$1:E484)))))</f>
+        <v> </v>
+      </c>
+      <c r="L485" s="27"/>
     </row>
     <row r="486" spans="1:12">
       <c r="A486" s="20" t="s">
-        <v>348</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="E486" s="22">
+        <f>IF(D486="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F486" s="23" t="str">
+        <f>IF(OR(E486="",E486="!!!"),"",IF(NOT(ISNA(VLOOKUP(E486,E$1:E485,1,FALSE()))),"OLD",IF(AND(E486&lt;&gt;"",E486&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G486" s="24" t="str">
+        <f>IF(OR(E486="",E486="!!!"),"",IF(OR(J486=0,AND(J486=1,K486=1),AND(J486=1,I486="SBJ"),AND(J486=1,I486=0)),"?IN_FOCUS",IF(J486&lt;=2,"?ACTIVATED",IF(J486&lt;&gt;"","?FAMILIAR",IF(F486="NEW",IF(ISNA(VLOOKUP(E486,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H486" s="25" t="str">
+        <f>IF(J486&lt;&gt;1,"",IF(I486="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I486" s="26" t="str">
+        <f>IF(OR(E486="",E486="!!!",F486="NEW"),"",INDEX(B485:B$2,-1+SUMPRODUCT(MAX(ROW(E485:E$2)*(E486=E485:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J486" s="26" t="str">
+        <f>IF(OR(E486="",E486="!!!",F486="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E486)*(E486=E$2:E486)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E485)*(E2=E$1:E485))))))</f>
+        <v> </v>
+      </c>
+      <c r="K486" s="26" t="str">
+        <f>IF(OR(E486="",E486="!!!",F486="NEW"),"",INDEX(J$1:J485,SUMPRODUCT(MAX(ROW(E$1:E485)*(E486=E$1:E485)))))</f>
+        <v> </v>
+      </c>
+      <c r="L486" s="27"/>
     </row>
     <row r="487" spans="1:12">
-      <c r="A487" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="E487" s="22">
-        <f>IF(D487="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F487" s="23" t="str">
-        <f>IF(OR(E487="",E487="!!!"),"",IF(NOT(ISNA(VLOOKUP(E487,E$1:E486,1,FALSE()))),"OLD",IF(AND(E487&lt;&gt;"",E487&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G487" s="24" t="str">
-        <f>IF(OR(E487="",E487="!!!"),"",IF(OR(J487=0,AND(J487=1,K487=1),AND(J487=1,I487="SBJ"),AND(J487=1,I487=0)),"?IN_FOCUS",IF(J487&lt;=2,"?ACTIVATED",IF(J487&lt;&gt;"","?FAMILIAR",IF(F487="NEW",IF(ISNA(VLOOKUP(E487,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H487" s="25" t="str">
-        <f>IF(J487&lt;&gt;1,"",IF(I487="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I487" s="26" t="str">
-        <f>IF(OR(E487="",E487="!!!",F487="NEW"),"",INDEX(B486:B$2,-1+SUMPRODUCT(MAX(ROW(E486:E$2)*(E487=E486:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J487" s="26" t="str">
-        <f>IF(OR(E487="",E487="!!!",F487="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E487)*(E487=E$2:E487)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E486)*(E2=E$1:E486))))))</f>
-        <v> </v>
-      </c>
-      <c r="K487" s="26" t="str">
-        <f>IF(OR(E487="",E487="!!!",F487="NEW"),"",INDEX(J$1:J486,SUMPRODUCT(MAX(ROW(E$1:E486)*(E487=E$1:E486)))))</f>
-        <v> </v>
-      </c>
-      <c r="L487" s="27"/>
+      <c r="A487" s="20"/>
     </row>
     <row r="488" spans="1:12">
       <c r="A488" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="E488" s="22">
-        <f>IF(D488="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F488" s="23" t="str">
-        <f>IF(OR(E488="",E488="!!!"),"",IF(NOT(ISNA(VLOOKUP(E488,E$1:E487,1,FALSE()))),"OLD",IF(AND(E488&lt;&gt;"",E488&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G488" s="24" t="str">
-        <f>IF(OR(E488="",E488="!!!"),"",IF(OR(J488=0,AND(J488=1,K488=1),AND(J488=1,I488="SBJ"),AND(J488=1,I488=0)),"?IN_FOCUS",IF(J488&lt;=2,"?ACTIVATED",IF(J488&lt;&gt;"","?FAMILIAR",IF(F488="NEW",IF(ISNA(VLOOKUP(E488,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H488" s="25" t="str">
-        <f>IF(J488&lt;&gt;1,"",IF(I488="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I488" s="26" t="str">
-        <f>IF(OR(E488="",E488="!!!",F488="NEW"),"",INDEX(B487:B$2,-1+SUMPRODUCT(MAX(ROW(E487:E$2)*(E488=E487:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J488" s="26" t="str">
-        <f>IF(OR(E488="",E488="!!!",F488="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E488)*(E488=E$2:E488)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E487)*(E2=E$1:E487))))))</f>
-        <v> </v>
-      </c>
-      <c r="K488" s="26" t="str">
-        <f>IF(OR(E488="",E488="!!!",F488="NEW"),"",INDEX(J$1:J487,SUMPRODUCT(MAX(ROW(E$1:E487)*(E488=E$1:E487)))))</f>
-        <v> </v>
-      </c>
-      <c r="L488" s="27"/>
+        <v>353</v>
+      </c>
     </row>
     <row r="489" spans="1:12">
       <c r="A489" s="20" t="s">
-        <v>274</v>
+        <v>221</v>
       </c>
       <c r="E489" s="22">
         <f>IF(D489="?OLD","!!!","")</f>
@@ -18883,13 +18869,7 @@
     </row>
     <row r="490" spans="1:12">
       <c r="A490" s="20" t="s">
-        <v>349</v>
-      </c>
-      <c r="B490" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C490" s="21" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="E490" s="22">
         <f>IF(D490="?OLD","!!!","")</f>
@@ -18923,7 +18903,7 @@
     </row>
     <row r="491" spans="1:12">
       <c r="A491" s="20" t="s">
-        <v>150</v>
+        <v>279</v>
       </c>
       <c r="E491" s="22">
         <f>IF(D491="?OLD","!!!","")</f>
@@ -18957,7 +18937,13 @@
     </row>
     <row r="492" spans="1:12">
       <c r="A492" s="20" t="s">
-        <v>128</v>
+        <v>354</v>
+      </c>
+      <c r="B492" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C492" s="21" t="s">
+        <v>196</v>
       </c>
       <c r="E492" s="22">
         <f>IF(D492="?OLD","!!!","")</f>
@@ -18991,16 +18977,7 @@
     </row>
     <row r="493" spans="1:12">
       <c r="A493" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="B493" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="C493" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D493" s="21" t="s">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="E493" s="22">
         <f>IF(D493="?OLD","!!!","")</f>
@@ -19068,13 +19045,16 @@
     </row>
     <row r="495" spans="1:12">
       <c r="A495" s="20" t="s">
-        <v>350</v>
+        <v>226</v>
       </c>
       <c r="B495" s="21" t="s">
-        <v>285</v>
+        <v>122</v>
       </c>
       <c r="C495" s="21" t="s">
-        <v>191</v>
+        <v>128</v>
+      </c>
+      <c r="D495" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E495" s="22">
         <f>IF(D495="?OLD","!!!","")</f>
@@ -19108,7 +19088,7 @@
     </row>
     <row r="496" spans="1:12">
       <c r="A496" s="20" t="s">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="E496" s="22">
         <f>IF(D496="?OLD","!!!","")</f>
@@ -19142,7 +19122,13 @@
     </row>
     <row r="497" spans="1:12">
       <c r="A497" s="20" t="s">
-        <v>119</v>
+        <v>355</v>
+      </c>
+      <c r="B497" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="C497" s="21" t="s">
+        <v>196</v>
       </c>
       <c r="E497" s="22">
         <f>IF(D497="?OLD","!!!","")</f>
@@ -19176,16 +19162,7 @@
     </row>
     <row r="498" spans="1:12">
       <c r="A498" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="B498" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="C498" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="D498" s="21" t="s">
-        <v>108</v>
+        <v>177</v>
       </c>
       <c r="E498" s="22">
         <f>IF(D498="?OLD","!!!","")</f>
@@ -19219,7 +19196,7 @@
     </row>
     <row r="499" spans="1:12">
       <c r="A499" s="20" t="s">
-        <v>300</v>
+        <v>123</v>
       </c>
       <c r="E499" s="22">
         <f>IF(D499="?OLD","!!!","")</f>
@@ -19253,7 +19230,16 @@
     </row>
     <row r="500" spans="1:12">
       <c r="A500" s="20" t="s">
-        <v>150</v>
+        <v>284</v>
+      </c>
+      <c r="B500" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="C500" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="D500" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E500" s="22">
         <f>IF(D500="?OLD","!!!","")</f>
@@ -19287,7 +19273,7 @@
     </row>
     <row r="501" spans="1:12">
       <c r="A501" s="20" t="s">
-        <v>351</v>
+        <v>305</v>
       </c>
       <c r="E501" s="22">
         <f>IF(D501="?OLD","!!!","")</f>
@@ -19321,16 +19307,7 @@
     </row>
     <row r="502" spans="1:12">
       <c r="A502" s="20" t="s">
-        <v>352</v>
-      </c>
-      <c r="B502" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="C502" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="D502" s="21" t="s">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="E502" s="22">
         <f>IF(D502="?OLD","!!!","")</f>
@@ -19364,7 +19341,7 @@
     </row>
     <row r="503" spans="1:12">
       <c r="A503" s="20" t="s">
-        <v>150</v>
+        <v>356</v>
       </c>
       <c r="E503" s="22">
         <f>IF(D503="?OLD","!!!","")</f>
@@ -19398,7 +19375,16 @@
     </row>
     <row r="504" spans="1:12">
       <c r="A504" s="20" t="s">
-        <v>140</v>
+        <v>357</v>
+      </c>
+      <c r="B504" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="C504" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="D504" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E504" s="22">
         <f>IF(D504="?OLD","!!!","")</f>
@@ -19432,13 +19418,7 @@
     </row>
     <row r="505" spans="1:12">
       <c r="A505" s="20" t="s">
-        <v>353</v>
-      </c>
-      <c r="B505" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="C505" s="21" t="s">
-        <v>210</v>
+        <v>155</v>
       </c>
       <c r="E505" s="22">
         <f>IF(D505="?OLD","!!!","")</f>
@@ -19472,7 +19452,7 @@
     </row>
     <row r="506" spans="1:12">
       <c r="A506" s="20" t="s">
-        <v>354</v>
+        <v>145</v>
       </c>
       <c r="E506" s="22">
         <f>IF(D506="?OLD","!!!","")</f>
@@ -19506,13 +19486,13 @@
     </row>
     <row r="507" spans="1:12">
       <c r="A507" s="20" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B507" s="21" t="s">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="C507" s="21" t="s">
-        <v>169</v>
+        <v>215</v>
       </c>
       <c r="E507" s="22">
         <f>IF(D507="?OLD","!!!","")</f>
@@ -19546,7 +19526,7 @@
     </row>
     <row r="508" spans="1:12">
       <c r="A508" s="20" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E508" s="22">
         <f>IF(D508="?OLD","!!!","")</f>
@@ -19580,7 +19560,13 @@
     </row>
     <row r="509" spans="1:12">
       <c r="A509" s="20" t="s">
-        <v>138</v>
+        <v>360</v>
+      </c>
+      <c r="B509" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="C509" s="21" t="s">
+        <v>174</v>
       </c>
       <c r="E509" s="22">
         <f>IF(D509="?OLD","!!!","")</f>
@@ -19613,102 +19599,93 @@
       <c r="L509" s="27"/>
     </row>
     <row r="510" spans="1:12">
-      <c r="A510" s="20"/>
+      <c r="A510" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="E510" s="22">
+        <f>IF(D510="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F510" s="23" t="str">
+        <f>IF(OR(E510="",E510="!!!"),"",IF(NOT(ISNA(VLOOKUP(E510,E$1:E509,1,FALSE()))),"OLD",IF(AND(E510&lt;&gt;"",E510&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G510" s="24" t="str">
+        <f>IF(OR(E510="",E510="!!!"),"",IF(OR(J510=0,AND(J510=1,K510=1),AND(J510=1,I510="SBJ"),AND(J510=1,I510=0)),"?IN_FOCUS",IF(J510&lt;=2,"?ACTIVATED",IF(J510&lt;&gt;"","?FAMILIAR",IF(F510="NEW",IF(ISNA(VLOOKUP(E510,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H510" s="25" t="str">
+        <f>IF(J510&lt;&gt;1,"",IF(I510="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I510" s="26" t="str">
+        <f>IF(OR(E510="",E510="!!!",F510="NEW"),"",INDEX(B509:B$2,-1+SUMPRODUCT(MAX(ROW(E509:E$2)*(E510=E509:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J510" s="26" t="str">
+        <f>IF(OR(E510="",E510="!!!",F510="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E510)*(E510=E$2:E510)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E509)*(E2=E$1:E509))))))</f>
+        <v> </v>
+      </c>
+      <c r="K510" s="26" t="str">
+        <f>IF(OR(E510="",E510="!!!",F510="NEW"),"",INDEX(J$1:J509,SUMPRODUCT(MAX(ROW(E$1:E509)*(E510=E$1:E509)))))</f>
+        <v> </v>
+      </c>
+      <c r="L510" s="27"/>
     </row>
     <row r="511" spans="1:12">
       <c r="A511" s="20" t="s">
-        <v>357</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="E511" s="22">
+        <f>IF(D511="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F511" s="23" t="str">
+        <f>IF(OR(E511="",E511="!!!"),"",IF(NOT(ISNA(VLOOKUP(E511,E$1:E510,1,FALSE()))),"OLD",IF(AND(E511&lt;&gt;"",E511&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G511" s="24" t="str">
+        <f>IF(OR(E511="",E511="!!!"),"",IF(OR(J511=0,AND(J511=1,K511=1),AND(J511=1,I511="SBJ"),AND(J511=1,I511=0)),"?IN_FOCUS",IF(J511&lt;=2,"?ACTIVATED",IF(J511&lt;&gt;"","?FAMILIAR",IF(F511="NEW",IF(ISNA(VLOOKUP(E511,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H511" s="25" t="str">
+        <f>IF(J511&lt;&gt;1,"",IF(I511="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I511" s="26" t="str">
+        <f>IF(OR(E511="",E511="!!!",F511="NEW"),"",INDEX(B510:B$2,-1+SUMPRODUCT(MAX(ROW(E510:E$2)*(E511=E510:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J511" s="26" t="str">
+        <f>IF(OR(E511="",E511="!!!",F511="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E511)*(E511=E$2:E511)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E510)*(E2=E$1:E510))))))</f>
+        <v> </v>
+      </c>
+      <c r="K511" s="26" t="str">
+        <f>IF(OR(E511="",E511="!!!",F511="NEW"),"",INDEX(J$1:J510,SUMPRODUCT(MAX(ROW(E$1:E510)*(E511=E$1:E510)))))</f>
+        <v> </v>
+      </c>
+      <c r="L511" s="27"/>
     </row>
     <row r="512" spans="1:12">
-      <c r="A512" s="20" t="s">
-        <v>358</v>
-      </c>
-      <c r="B512" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="C512" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="D512" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="E512" s="22">
-        <f>IF(D512="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F512" s="23" t="str">
-        <f>IF(OR(E512="",E512="!!!"),"",IF(NOT(ISNA(VLOOKUP(E512,E$1:E511,1,FALSE()))),"OLD",IF(AND(E512&lt;&gt;"",E512&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G512" s="24" t="str">
-        <f>IF(OR(E512="",E512="!!!"),"",IF(OR(J512=0,AND(J512=1,K512=1),AND(J512=1,I512="SBJ"),AND(J512=1,I512=0)),"?IN_FOCUS",IF(J512&lt;=2,"?ACTIVATED",IF(J512&lt;&gt;"","?FAMILIAR",IF(F512="NEW",IF(ISNA(VLOOKUP(E512,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H512" s="25" t="str">
-        <f>IF(J512&lt;&gt;1,"",IF(I512="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I512" s="26" t="str">
-        <f>IF(OR(E512="",E512="!!!",F512="NEW"),"",INDEX(B511:B$2,-1+SUMPRODUCT(MAX(ROW(E511:E$2)*(E512=E511:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J512" s="26" t="str">
-        <f>IF(OR(E512="",E512="!!!",F512="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E512)*(E512=E$2:E512)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E511)*(E2=E$1:E511))))))</f>
-        <v> </v>
-      </c>
-      <c r="K512" s="26" t="str">
-        <f>IF(OR(E512="",E512="!!!",F512="NEW"),"",INDEX(J$1:J511,SUMPRODUCT(MAX(ROW(E$1:E511)*(E512=E$1:E511)))))</f>
-        <v> </v>
-      </c>
-      <c r="L512" s="27"/>
+      <c r="A512" s="20"/>
     </row>
     <row r="513" spans="1:12">
       <c r="A513" s="20" t="s">
-        <v>359</v>
-      </c>
-      <c r="E513" s="22">
-        <f>IF(D513="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F513" s="23" t="str">
-        <f>IF(OR(E513="",E513="!!!"),"",IF(NOT(ISNA(VLOOKUP(E513,E$1:E512,1,FALSE()))),"OLD",IF(AND(E513&lt;&gt;"",E513&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G513" s="24" t="str">
-        <f>IF(OR(E513="",E513="!!!"),"",IF(OR(J513=0,AND(J513=1,K513=1),AND(J513=1,I513="SBJ"),AND(J513=1,I513=0)),"?IN_FOCUS",IF(J513&lt;=2,"?ACTIVATED",IF(J513&lt;&gt;"","?FAMILIAR",IF(F513="NEW",IF(ISNA(VLOOKUP(E513,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H513" s="25" t="str">
-        <f>IF(J513&lt;&gt;1,"",IF(I513="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I513" s="26" t="str">
-        <f>IF(OR(E513="",E513="!!!",F513="NEW"),"",INDEX(B512:B$2,-1+SUMPRODUCT(MAX(ROW(E512:E$2)*(E513=E512:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J513" s="26" t="str">
-        <f>IF(OR(E513="",E513="!!!",F513="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E513)*(E513=E$2:E513)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E512)*(E2=E$1:E512))))))</f>
-        <v> </v>
-      </c>
-      <c r="K513" s="26" t="str">
-        <f>IF(OR(E513="",E513="!!!",F513="NEW"),"",INDEX(J$1:J512,SUMPRODUCT(MAX(ROW(E$1:E512)*(E513=E$1:E512)))))</f>
-        <v> </v>
-      </c>
-      <c r="L513" s="27"/>
+        <v>362</v>
+      </c>
     </row>
     <row r="514" spans="1:12">
       <c r="A514" s="20" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="B514" s="21" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C514" s="21" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D514" s="21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E514" s="22">
         <f>IF(D514="?OLD","!!!","")</f>
@@ -19742,16 +19719,7 @@
     </row>
     <row r="515" spans="1:12">
       <c r="A515" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="B515" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="C515" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="D515" s="21" t="s">
-        <v>108</v>
+        <v>364</v>
       </c>
       <c r="E515" s="22">
         <f>IF(D515="?OLD","!!!","")</f>
@@ -19785,7 +19753,16 @@
     </row>
     <row r="516" spans="1:12">
       <c r="A516" s="20" t="s">
-        <v>360</v>
+        <v>350</v>
+      </c>
+      <c r="B516" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C516" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D516" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E516" s="22">
         <f>IF(D516="?OLD","!!!","")</f>
@@ -19819,7 +19796,16 @@
     </row>
     <row r="517" spans="1:12">
       <c r="A517" s="20" t="s">
-        <v>90</v>
+        <v>224</v>
+      </c>
+      <c r="B517" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="C517" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="D517" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E517" s="22">
         <f>IF(D517="?OLD","!!!","")</f>
@@ -19853,7 +19839,7 @@
     </row>
     <row r="518" spans="1:12">
       <c r="A518" s="20" t="s">
-        <v>150</v>
+        <v>365</v>
       </c>
       <c r="E518" s="22">
         <f>IF(D518="?OLD","!!!","")</f>
@@ -19887,7 +19873,7 @@
     </row>
     <row r="519" spans="1:12">
       <c r="A519" s="20" t="s">
-        <v>361</v>
+        <v>94</v>
       </c>
       <c r="E519" s="22">
         <f>IF(D519="?OLD","!!!","")</f>
@@ -19921,7 +19907,7 @@
     </row>
     <row r="520" spans="1:12">
       <c r="A520" s="20" t="s">
-        <v>351</v>
+        <v>155</v>
       </c>
       <c r="E520" s="22">
         <f>IF(D520="?OLD","!!!","")</f>
@@ -19955,16 +19941,7 @@
     </row>
     <row r="521" spans="1:12">
       <c r="A521" s="20" t="s">
-        <v>352</v>
-      </c>
-      <c r="B521" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="C521" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="D521" s="21" t="s">
-        <v>108</v>
+        <v>366</v>
       </c>
       <c r="E521" s="22">
         <f>IF(D521="?OLD","!!!","")</f>
@@ -19998,7 +19975,7 @@
     </row>
     <row r="522" spans="1:12">
       <c r="A522" s="20" t="s">
-        <v>150</v>
+        <v>356</v>
       </c>
       <c r="E522" s="22">
         <f>IF(D522="?OLD","!!!","")</f>
@@ -20032,7 +20009,16 @@
     </row>
     <row r="523" spans="1:12">
       <c r="A523" s="20" t="s">
-        <v>151</v>
+        <v>357</v>
+      </c>
+      <c r="B523" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="C523" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="D523" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E523" s="22">
         <f>IF(D523="?OLD","!!!","")</f>
@@ -20066,7 +20052,7 @@
     </row>
     <row r="524" spans="1:12">
       <c r="A524" s="20" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E524" s="22">
         <f>IF(D524="?OLD","!!!","")</f>
@@ -20100,16 +20086,7 @@
     </row>
     <row r="525" spans="1:12">
       <c r="A525" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="B525" s="21" t="s">
-        <v>284</v>
-      </c>
-      <c r="C525" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D525" s="21" t="s">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="E525" s="22">
         <f>IF(D525="?OLD","!!!","")</f>
@@ -20143,7 +20120,7 @@
     </row>
     <row r="526" spans="1:12">
       <c r="A526" s="20" t="s">
-        <v>362</v>
+        <v>157</v>
       </c>
       <c r="E526" s="22">
         <f>IF(D526="?OLD","!!!","")</f>
@@ -20177,7 +20154,16 @@
     </row>
     <row r="527" spans="1:12">
       <c r="A527" s="20" t="s">
-        <v>318</v>
+        <v>185</v>
+      </c>
+      <c r="B527" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="C527" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D527" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="E527" s="22">
         <f>IF(D527="?OLD","!!!","")</f>
@@ -20211,7 +20197,7 @@
     </row>
     <row r="528" spans="1:12">
       <c r="A528" s="20" t="s">
-        <v>138</v>
+        <v>367</v>
       </c>
       <c r="E528" s="22">
         <f>IF(D528="?OLD","!!!","")</f>
@@ -20243,8 +20229,76 @@
       </c>
       <c r="L528" s="27"/>
     </row>
-    <row r="529" spans="1:1">
-      <c r="A529" s="20"/>
+    <row r="529" spans="1:12">
+      <c r="A529" s="20" t="s">
+        <v>323</v>
+      </c>
+      <c r="E529" s="22">
+        <f>IF(D529="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F529" s="23" t="str">
+        <f>IF(OR(E529="",E529="!!!"),"",IF(NOT(ISNA(VLOOKUP(E529,E$1:E528,1,FALSE()))),"OLD",IF(AND(E529&lt;&gt;"",E529&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G529" s="24" t="str">
+        <f>IF(OR(E529="",E529="!!!"),"",IF(OR(J529=0,AND(J529=1,K529=1),AND(J529=1,I529="SBJ"),AND(J529=1,I529=0)),"?IN_FOCUS",IF(J529&lt;=2,"?ACTIVATED",IF(J529&lt;&gt;"","?FAMILIAR",IF(F529="NEW",IF(ISNA(VLOOKUP(E529,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H529" s="25" t="str">
+        <f>IF(J529&lt;&gt;1,"",IF(I529="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I529" s="26" t="str">
+        <f>IF(OR(E529="",E529="!!!",F529="NEW"),"",INDEX(B528:B$2,-1+SUMPRODUCT(MAX(ROW(E528:E$2)*(E529=E528:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J529" s="26" t="str">
+        <f>IF(OR(E529="",E529="!!!",F529="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E529)*(E529=E$2:E529)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E528)*(E2=E$1:E528))))))</f>
+        <v> </v>
+      </c>
+      <c r="K529" s="26" t="str">
+        <f>IF(OR(E529="",E529="!!!",F529="NEW"),"",INDEX(J$1:J528,SUMPRODUCT(MAX(ROW(E$1:E528)*(E529=E$1:E528)))))</f>
+        <v> </v>
+      </c>
+      <c r="L529" s="27"/>
+    </row>
+    <row r="530" spans="1:12">
+      <c r="A530" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E530" s="22">
+        <f>IF(D530="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F530" s="23" t="str">
+        <f>IF(OR(E530="",E530="!!!"),"",IF(NOT(ISNA(VLOOKUP(E530,E$1:E529,1,FALSE()))),"OLD",IF(AND(E530&lt;&gt;"",E530&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G530" s="24" t="str">
+        <f>IF(OR(E530="",E530="!!!"),"",IF(OR(J530=0,AND(J530=1,K530=1),AND(J530=1,I530="SBJ"),AND(J530=1,I530=0)),"?IN_FOCUS",IF(J530&lt;=2,"?ACTIVATED",IF(J530&lt;&gt;"","?FAMILIAR",IF(F530="NEW",IF(ISNA(VLOOKUP(E530,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H530" s="25" t="str">
+        <f>IF(J530&lt;&gt;1,"",IF(I530="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I530" s="26" t="str">
+        <f>IF(OR(E530="",E530="!!!",F530="NEW"),"",INDEX(B529:B$2,-1+SUMPRODUCT(MAX(ROW(E529:E$2)*(E530=E529:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J530" s="26" t="str">
+        <f>IF(OR(E530="",E530="!!!",F530="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E530)*(E530=E$2:E530)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E529)*(E2=E$1:E529))))))</f>
+        <v> </v>
+      </c>
+      <c r="K530" s="26" t="str">
+        <f>IF(OR(E530="",E530="!!!",F530="NEW"),"",INDEX(J$1:J529,SUMPRODUCT(MAX(ROW(E$1:E529)*(E530=E$1:E529)))))</f>
+        <v> </v>
+      </c>
+      <c r="L530" s="27"/>
+    </row>
+    <row r="531" spans="1:12">
+      <c r="A531" s="20"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
